--- a/2026/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
+++ b/2026/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB583894-03A5-42F7-A7A6-05F09C0F77AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC346251-CABA-481B-AE3D-0DAA043D19BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="163">
   <si>
     <t>U.F.</t>
   </si>
@@ -348,9 +348,6 @@
     <t>Gabriel</t>
   </si>
   <si>
-    <t>Miriam</t>
-  </si>
-  <si>
     <t>Leonel</t>
   </si>
   <si>
@@ -478,39 +475,6 @@
   </si>
   <si>
     <t>subidos en jul10</t>
-  </si>
-  <si>
-    <t>VTO: 17/9</t>
-  </si>
-  <si>
-    <t>AGOSTO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - AGOSTO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - AGOSTO</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de transformador 220volts a A24 volts</t>
-  </si>
-  <si>
-    <t>Colcoacion de termotanque - Materiales + Mano de obra</t>
-  </si>
-  <si>
-    <t>Cuota 5 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
-  </si>
-  <si>
-    <t>Doartero Julio - Cambio de cañeria de entrada</t>
-  </si>
-  <si>
-    <t>Ezequiel Sarro Murillo -  Sr. Abogado - Presentacion de escrito</t>
-  </si>
-  <si>
-    <t>Cetrogar - Compra de termotanque escorial multigas Col 45L</t>
-  </si>
-  <si>
-    <t>Sr. Andres Jose - Electricista - Campio de termica - Materiales + mano de obra</t>
   </si>
   <si>
     <t>SINDICATOS - SUTHER, FATHERY, SERACARH</t>
@@ -530,6 +494,48 @@
       </rPr>
       <t>SUELDO ENCARGADA</t>
     </r>
+  </si>
+  <si>
+    <t>VTO: 16/10</t>
+  </si>
+  <si>
+    <t>SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - SEPTIEMBRE</t>
+  </si>
+  <si>
+    <t>Kromacolor - compra de pintura: cielos rasos siteplast, caablanca sellador fijador y lija al agua sinteplast</t>
+  </si>
+  <si>
+    <t>Doartero AGOSTO - Reparacion automatizacion de bomba</t>
+  </si>
+  <si>
+    <t>Oscar Cordoba - Arreglo desague Dpto. 4.16</t>
+  </si>
+  <si>
+    <t>Sr. Facundo - Mano de obra pintura Dpto. (techos baño) 1.7</t>
+  </si>
+  <si>
+    <t>Kromacolor - compra de enduido</t>
+  </si>
+  <si>
+    <t>Desratizacion - Servicio Septiembre</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>AYSA Destapacion caja de PB</t>
+  </si>
+  <si>
+    <t>Ezequiel Sarro Murillo -  Sr. Abogado - Audiencia prescencial en el juzgado 22/09</t>
+  </si>
+  <si>
+    <t>Compra termotanque porteria - Cuota 1/12</t>
   </si>
 </sst>
 </file>
@@ -546,7 +552,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,6 +767,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1341,7 +1354,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="244">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1532,9 +1545,6 @@
     <xf numFmtId="164" fontId="15" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1582,78 +1592,9 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1667,126 +1608,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="6" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1796,14 +1658,174 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="21" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="20" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="31" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="31" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2250,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -2275,92 +2297,92 @@
     </row>
     <row r="2" spans="1:11" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="144"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="194"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="164"/>
-      <c r="B3" s="165"/>
-      <c r="C3" s="165"/>
+      <c r="A3" s="142"/>
+      <c r="B3" s="143"/>
+      <c r="C3" s="143"/>
       <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="166">
+      <c r="E3" s="195">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="166"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="167"/>
-      <c r="I3" s="165"/>
-      <c r="J3" s="165"/>
-      <c r="K3" s="165"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="196"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="164"/>
-      <c r="B4" s="165"/>
-      <c r="C4" s="165"/>
+      <c r="A4" s="142"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
       <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="E4" s="144" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="165"/>
-      <c r="G4" s="165"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="165"/>
-      <c r="J4" s="165"/>
-      <c r="K4" s="165"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="164"/>
-      <c r="B5" s="165"/>
-      <c r="C5" s="165"/>
+      <c r="A5" s="142"/>
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
       <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="170">
+      <c r="E5" s="146">
         <v>30707328890</v>
       </c>
-      <c r="F5" s="165"/>
-      <c r="G5" s="165"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="165"/>
-      <c r="J5" s="165"/>
-      <c r="K5" s="165"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="145"/>
+      <c r="I5" s="143"/>
+      <c r="J5" s="143"/>
+      <c r="K5" s="143"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="164"/>
-      <c r="B6" s="165"/>
-      <c r="C6" s="165"/>
+      <c r="A6" s="142"/>
+      <c r="B6" s="143"/>
+      <c r="C6" s="143"/>
       <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="165"/>
-      <c r="F6" s="165"/>
-      <c r="G6" s="165" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="169"/>
-      <c r="I6" s="165"/>
-      <c r="J6" s="165"/>
-      <c r="K6" s="165"/>
+      <c r="E6" s="143"/>
+      <c r="F6" s="143"/>
+      <c r="G6" s="143" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="145"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="164"/>
-      <c r="B7" s="165"/>
-      <c r="C7" s="165"/>
-      <c r="D7" s="165"/>
-      <c r="E7" s="165"/>
-      <c r="F7" s="165"/>
-      <c r="G7" s="165"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="165"/>
-      <c r="J7" s="165"/>
-      <c r="K7" s="165"/>
+      <c r="A7" s="142"/>
+      <c r="B7" s="143"/>
+      <c r="C7" s="143"/>
+      <c r="D7" s="143"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="143"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="15" t="s">
@@ -2373,1459 +2395,1510 @@
         <v>66</v>
       </c>
       <c r="F8" s="75" t="s">
+        <v>150</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>148</v>
-      </c>
       <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="171"/>
-      <c r="B9" s="172"/>
-      <c r="C9" s="172"/>
-      <c r="D9" s="172"/>
-      <c r="E9" s="172"/>
-      <c r="F9" s="172"/>
-      <c r="G9" s="172"/>
-      <c r="H9" s="173"/>
-      <c r="I9" s="165"/>
-      <c r="J9" s="165"/>
-      <c r="K9" s="165"/>
+      <c r="A9" s="147"/>
+      <c r="B9" s="148"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="165"/>
-      <c r="C10" s="165"/>
-      <c r="D10" s="165"/>
+      <c r="B10" s="143"/>
+      <c r="C10" s="143"/>
+      <c r="D10" s="143"/>
       <c r="E10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="165"/>
-      <c r="G10" s="165"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="165"/>
-      <c r="J10" s="165"/>
-      <c r="K10" s="165"/>
+      <c r="F10" s="143"/>
+      <c r="G10" s="143"/>
+      <c r="H10" s="145"/>
+      <c r="I10" s="143"/>
+      <c r="J10" s="143"/>
+      <c r="K10" s="143"/>
     </row>
     <row r="11" spans="1:11" ht="14.25" customHeight="1">
       <c r="A11" s="12"/>
-      <c r="B11" s="165"/>
-      <c r="C11" s="165"/>
-      <c r="D11" s="165"/>
+      <c r="B11" s="143"/>
+      <c r="C11" s="143"/>
+      <c r="D11" s="143"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="165"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="169"/>
-      <c r="I11" s="165"/>
-      <c r="J11" s="165"/>
-      <c r="K11" s="165"/>
+      <c r="F11" s="143"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
     </row>
     <row r="12" spans="1:11" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="145"/>
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="147"/>
-      <c r="I12" s="165"/>
-      <c r="J12" s="165"/>
-      <c r="K12" s="165"/>
+      <c r="A12" s="201"/>
+      <c r="B12" s="176"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="176"/>
+      <c r="F12" s="176"/>
+      <c r="G12" s="176"/>
+      <c r="H12" s="202"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
     </row>
     <row r="13" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A13" s="174"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
-      <c r="D13" s="175"/>
-      <c r="E13" s="175"/>
-      <c r="F13" s="175"/>
-      <c r="G13" s="175"/>
-      <c r="H13" s="176"/>
-      <c r="I13" s="165"/>
-      <c r="J13" s="165"/>
-      <c r="K13" s="165"/>
+      <c r="A13" s="150"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
+      <c r="H13" s="152"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
     </row>
     <row r="14" spans="1:11" ht="15.75">
-      <c r="A14" s="177" t="s">
-        <v>160</v>
-      </c>
-      <c r="B14" s="177"/>
-      <c r="C14" s="177"/>
-      <c r="D14" s="177"/>
-      <c r="E14" s="177"/>
-      <c r="F14" s="177"/>
-      <c r="G14" s="177"/>
-      <c r="H14" s="177"/>
-      <c r="I14" s="165"/>
-      <c r="J14" s="165"/>
-      <c r="K14" s="165"/>
+      <c r="A14" s="203" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" s="203"/>
+      <c r="C14" s="203"/>
+      <c r="D14" s="203"/>
+      <c r="E14" s="203"/>
+      <c r="F14" s="203"/>
+      <c r="G14" s="203"/>
+      <c r="H14" s="203"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="178" t="s">
-        <v>133</v>
-      </c>
-      <c r="B15" s="179"/>
-      <c r="C15" s="179"/>
-      <c r="D15" s="179"/>
-      <c r="E15" s="179"/>
-      <c r="F15" s="179"/>
-      <c r="G15" s="179"/>
-      <c r="H15" s="110">
-        <v>433458.65</v>
-      </c>
-      <c r="I15" s="165"/>
-      <c r="J15" s="165"/>
-      <c r="K15" s="165"/>
+      <c r="A15" s="217" t="s">
+        <v>132</v>
+      </c>
+      <c r="B15" s="218"/>
+      <c r="C15" s="218"/>
+      <c r="D15" s="218"/>
+      <c r="E15" s="218"/>
+      <c r="F15" s="218"/>
+      <c r="G15" s="218"/>
+      <c r="H15" s="219">
+        <v>442956.59</v>
+      </c>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="178" t="s">
+      <c r="A16" s="217" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="179"/>
-      <c r="C16" s="179"/>
-      <c r="D16" s="179"/>
-      <c r="E16" s="179"/>
-      <c r="F16" s="179"/>
-      <c r="G16" s="179"/>
-      <c r="H16" s="110">
-        <v>-68269.649999999994</v>
-      </c>
-      <c r="I16" s="180"/>
-      <c r="J16" s="165"/>
-      <c r="K16" s="165"/>
+      <c r="B16" s="218"/>
+      <c r="C16" s="218"/>
+      <c r="D16" s="218"/>
+      <c r="E16" s="218"/>
+      <c r="F16" s="218"/>
+      <c r="G16" s="218"/>
+      <c r="H16" s="219">
+        <v>69765.59</v>
+      </c>
+      <c r="I16" s="154"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="178" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" s="179"/>
-      <c r="C17" s="179"/>
-      <c r="D17" s="179"/>
-      <c r="E17" s="179"/>
-      <c r="F17" s="179"/>
-      <c r="G17" s="179"/>
-      <c r="H17" s="110">
-        <v>0</v>
-      </c>
-      <c r="I17" s="180"/>
-      <c r="J17" s="165"/>
-      <c r="K17" s="165"/>
+      <c r="A17" s="217" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="218"/>
+      <c r="C17" s="218"/>
+      <c r="D17" s="218"/>
+      <c r="E17" s="218"/>
+      <c r="F17" s="218"/>
+      <c r="G17" s="218"/>
+      <c r="H17" s="219">
+        <v>0</v>
+      </c>
+      <c r="I17" s="154"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="143"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="178" t="s">
+      <c r="A18" s="217" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="179"/>
-      <c r="C18" s="179"/>
-      <c r="D18" s="179"/>
-      <c r="E18" s="179"/>
-      <c r="F18" s="179"/>
-      <c r="G18" s="179"/>
-      <c r="H18" s="181">
+      <c r="B18" s="218"/>
+      <c r="C18" s="218"/>
+      <c r="D18" s="218"/>
+      <c r="E18" s="218"/>
+      <c r="F18" s="218"/>
+      <c r="G18" s="218"/>
+      <c r="H18" s="220">
         <f>SUM(H15:H17)</f>
-        <v>365189</v>
-      </c>
-      <c r="I18" s="180"/>
-      <c r="J18" s="165"/>
-      <c r="K18" s="165"/>
+        <v>512722.18000000005</v>
+      </c>
+      <c r="I18" s="154"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="143"/>
     </row>
     <row r="19" spans="1:11" hidden="1">
-      <c r="A19" s="182" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" s="182"/>
-      <c r="C19" s="182"/>
-      <c r="D19" s="182"/>
-      <c r="E19" s="182"/>
-      <c r="F19" s="182"/>
-      <c r="G19" s="182"/>
-      <c r="H19" s="182"/>
-      <c r="I19" s="165"/>
-      <c r="J19" s="165"/>
-      <c r="K19" s="165"/>
+      <c r="A19" s="221" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="221"/>
+      <c r="C19" s="221"/>
+      <c r="D19" s="221"/>
+      <c r="E19" s="221"/>
+      <c r="F19" s="221"/>
+      <c r="G19" s="221"/>
+      <c r="H19" s="221"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="143"/>
     </row>
     <row r="20" spans="1:11" hidden="1">
-      <c r="A20" s="178" t="s">
+      <c r="A20" s="217" t="s">
+        <v>143</v>
+      </c>
+      <c r="B20" s="218"/>
+      <c r="C20" s="218"/>
+      <c r="D20" s="218"/>
+      <c r="E20" s="218"/>
+      <c r="F20" s="218"/>
+      <c r="G20" s="218"/>
+      <c r="H20" s="219">
+        <v>0</v>
+      </c>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="143"/>
+    </row>
+    <row r="21" spans="1:11" hidden="1">
+      <c r="A21" s="217" t="s">
         <v>144</v>
       </c>
-      <c r="B20" s="179"/>
-      <c r="C20" s="179"/>
-      <c r="D20" s="179"/>
-      <c r="E20" s="179"/>
-      <c r="F20" s="179"/>
-      <c r="G20" s="179"/>
-      <c r="H20" s="110">
-        <v>0</v>
-      </c>
-      <c r="I20" s="165"/>
-      <c r="J20" s="165"/>
-      <c r="K20" s="165"/>
-    </row>
-    <row r="21" spans="1:11" hidden="1">
-      <c r="A21" s="178" t="s">
-        <v>145</v>
-      </c>
-      <c r="B21" s="179"/>
-      <c r="C21" s="179"/>
-      <c r="D21" s="179"/>
-      <c r="E21" s="179"/>
-      <c r="F21" s="179"/>
-      <c r="G21" s="179"/>
-      <c r="H21" s="110">
-        <v>0</v>
-      </c>
-      <c r="I21" s="165"/>
-      <c r="J21" s="165"/>
-      <c r="K21" s="165"/>
+      <c r="B21" s="218"/>
+      <c r="C21" s="218"/>
+      <c r="D21" s="218"/>
+      <c r="E21" s="218"/>
+      <c r="F21" s="218"/>
+      <c r="G21" s="218"/>
+      <c r="H21" s="219">
+        <v>0</v>
+      </c>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="143"/>
     </row>
     <row r="22" spans="1:11" hidden="1">
-      <c r="A22" s="178" t="s">
+      <c r="A22" s="217" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="179"/>
-      <c r="C22" s="179"/>
-      <c r="D22" s="179"/>
-      <c r="E22" s="179"/>
-      <c r="F22" s="179"/>
-      <c r="G22" s="179"/>
-      <c r="H22" s="181">
+      <c r="B22" s="218"/>
+      <c r="C22" s="218"/>
+      <c r="D22" s="218"/>
+      <c r="E22" s="218"/>
+      <c r="F22" s="218"/>
+      <c r="G22" s="218"/>
+      <c r="H22" s="220">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="165"/>
-      <c r="J22" s="165"/>
-      <c r="K22" s="165"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="143"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="183" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" s="183"/>
-      <c r="C23" s="183"/>
-      <c r="D23" s="183"/>
-      <c r="E23" s="183"/>
-      <c r="F23" s="183"/>
-      <c r="G23" s="183"/>
-      <c r="H23" s="183"/>
-      <c r="I23" s="165"/>
-      <c r="J23" s="165"/>
-      <c r="K23" s="165"/>
+      <c r="A23" s="222" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="222"/>
+      <c r="C23" s="222"/>
+      <c r="D23" s="222"/>
+      <c r="E23" s="222"/>
+      <c r="F23" s="222"/>
+      <c r="G23" s="222"/>
+      <c r="H23" s="222"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="179" t="s">
-        <v>131</v>
-      </c>
-      <c r="B24" s="179"/>
-      <c r="C24" s="179"/>
-      <c r="D24" s="179"/>
-      <c r="E24" s="179"/>
-      <c r="F24" s="179"/>
-      <c r="G24" s="179"/>
-      <c r="H24" s="110">
+      <c r="A24" s="218" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="218"/>
+      <c r="C24" s="218"/>
+      <c r="D24" s="218"/>
+      <c r="E24" s="218"/>
+      <c r="F24" s="218"/>
+      <c r="G24" s="218"/>
+      <c r="H24" s="219">
         <f>(17000+32000)/2</f>
         <v>24500</v>
       </c>
-      <c r="I24" s="165"/>
-      <c r="J24" s="165"/>
-      <c r="K24" s="165"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="143"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="179"/>
-      <c r="B25" s="179"/>
-      <c r="C25" s="179"/>
-      <c r="D25" s="179"/>
-      <c r="E25" s="179"/>
-      <c r="F25" s="179"/>
-      <c r="G25" s="179"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="165"/>
-      <c r="J25" s="165"/>
-      <c r="K25" s="165"/>
+      <c r="A25" s="218"/>
+      <c r="B25" s="218"/>
+      <c r="C25" s="218"/>
+      <c r="D25" s="218"/>
+      <c r="E25" s="218"/>
+      <c r="F25" s="218"/>
+      <c r="G25" s="218"/>
+      <c r="H25" s="219"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="179" t="s">
+      <c r="A26" s="218" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="179"/>
-      <c r="C26" s="179"/>
-      <c r="D26" s="179"/>
-      <c r="E26" s="179"/>
-      <c r="F26" s="179"/>
-      <c r="G26" s="179"/>
-      <c r="H26" s="181">
+      <c r="B26" s="218"/>
+      <c r="C26" s="218"/>
+      <c r="D26" s="218"/>
+      <c r="E26" s="218"/>
+      <c r="F26" s="218"/>
+      <c r="G26" s="218"/>
+      <c r="H26" s="220">
         <f>SUM(H24:H25)</f>
         <v>24500</v>
       </c>
-      <c r="I26" s="165"/>
-      <c r="J26" s="165"/>
-      <c r="K26" s="165"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="184" t="s">
+      <c r="A27" s="223" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="184"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
-      <c r="F27" s="184"/>
-      <c r="G27" s="184"/>
-      <c r="H27" s="184"/>
-      <c r="I27" s="165"/>
-      <c r="J27" s="165"/>
-      <c r="K27" s="165"/>
+      <c r="B27" s="223"/>
+      <c r="C27" s="223"/>
+      <c r="D27" s="223"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="223"/>
+      <c r="I27" s="143"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="143"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="178"/>
-      <c r="B28" s="179"/>
-      <c r="C28" s="179"/>
-      <c r="D28" s="179"/>
-      <c r="E28" s="179"/>
-      <c r="F28" s="179"/>
-      <c r="G28" s="179"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="165"/>
-      <c r="J28" s="165"/>
-      <c r="K28" s="165"/>
+      <c r="A28" s="217"/>
+      <c r="B28" s="218"/>
+      <c r="C28" s="218"/>
+      <c r="D28" s="218"/>
+      <c r="E28" s="218"/>
+      <c r="F28" s="218"/>
+      <c r="G28" s="218"/>
+      <c r="H28" s="219"/>
+      <c r="I28" s="143"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="143"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="178" t="s">
+      <c r="A29" s="217" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="224"/>
+      <c r="C29" s="218"/>
+      <c r="D29" s="218"/>
+      <c r="E29" s="218"/>
+      <c r="F29" s="218"/>
+      <c r="G29" s="218"/>
+      <c r="H29" s="219">
+        <f>19505.61+2167.29+34214.38</f>
+        <v>55887.28</v>
+      </c>
+      <c r="I29" s="143"/>
+      <c r="J29" s="143"/>
+      <c r="K29" s="143"/>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="218" t="s">
+        <v>131</v>
+      </c>
+      <c r="B30" s="218"/>
+      <c r="C30" s="218"/>
+      <c r="D30" s="218"/>
+      <c r="E30" s="218"/>
+      <c r="F30" s="218"/>
+      <c r="G30" s="218"/>
+      <c r="H30" s="219">
+        <v>0</v>
+      </c>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="218" t="s">
+        <v>72</v>
+      </c>
+      <c r="B31" s="218"/>
+      <c r="C31" s="218"/>
+      <c r="D31" s="218"/>
+      <c r="E31" s="218"/>
+      <c r="F31" s="218"/>
+      <c r="G31" s="218"/>
+      <c r="H31" s="220">
+        <f>SUM(H28:H30)</f>
+        <v>55887.28</v>
+      </c>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="223" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="223"/>
+      <c r="C32" s="223"/>
+      <c r="D32" s="223"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="223"/>
+      <c r="I32" s="143"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="143"/>
+    </row>
+    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A33" s="218" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="218"/>
+      <c r="C33" s="218"/>
+      <c r="D33" s="218"/>
+      <c r="E33" s="218"/>
+      <c r="F33" s="218"/>
+      <c r="G33" s="218"/>
+      <c r="H33" s="219">
+        <v>1555264.54</v>
+      </c>
+      <c r="I33" s="143"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="143"/>
+    </row>
+    <row r="34" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A34" s="218" t="s">
+        <v>160</v>
+      </c>
+      <c r="B34" s="218"/>
+      <c r="C34" s="218"/>
+      <c r="D34" s="218"/>
+      <c r="E34" s="218"/>
+      <c r="F34" s="218"/>
+      <c r="G34" s="218"/>
+      <c r="H34" s="219">
+        <v>95000</v>
+      </c>
+      <c r="I34" s="143"/>
+      <c r="J34" s="143"/>
+      <c r="K34" s="143"/>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="225" t="s">
+        <v>97</v>
+      </c>
+      <c r="B35" s="218"/>
+      <c r="C35" s="218"/>
+      <c r="D35" s="218"/>
+      <c r="E35" s="218"/>
+      <c r="F35" s="218"/>
+      <c r="G35" s="218"/>
+      <c r="H35" s="219">
+        <v>88487.35</v>
+      </c>
+      <c r="I35" s="143"/>
+      <c r="J35" s="143"/>
+      <c r="K35" s="143"/>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="218" t="s">
+        <v>73</v>
+      </c>
+      <c r="B36" s="218"/>
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="226">
+        <f>SUM(H33:H35)</f>
+        <v>1738751.8900000001</v>
+      </c>
+      <c r="I36" s="143"/>
+      <c r="J36" s="143"/>
+      <c r="K36" s="143"/>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="227" t="s">
+        <v>125</v>
+      </c>
+      <c r="B37" s="227"/>
+      <c r="C37" s="227"/>
+      <c r="D37" s="227"/>
+      <c r="E37" s="227"/>
+      <c r="F37" s="227"/>
+      <c r="G37" s="227"/>
+      <c r="H37" s="227"/>
+      <c r="I37" s="143"/>
+      <c r="J37" s="143"/>
+      <c r="K37" s="143"/>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="228" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="218"/>
+      <c r="C38" s="218"/>
+      <c r="D38" s="218"/>
+      <c r="E38" s="218"/>
+      <c r="F38" s="218"/>
+      <c r="G38" s="218"/>
+      <c r="H38" s="219">
+        <v>102500</v>
+      </c>
+      <c r="I38" s="143"/>
+      <c r="J38" s="143"/>
+      <c r="K38" s="143"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="218" t="s">
+        <v>69</v>
+      </c>
+      <c r="B39" s="218"/>
+      <c r="C39" s="218"/>
+      <c r="D39" s="218"/>
+      <c r="E39" s="218"/>
+      <c r="F39" s="218"/>
+      <c r="G39" s="218"/>
+      <c r="H39" s="219">
+        <v>36480.69</v>
+      </c>
+      <c r="I39" s="143"/>
+      <c r="J39" s="143"/>
+      <c r="K39" s="143"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="229" t="s">
+        <v>162</v>
+      </c>
+      <c r="B40" s="230"/>
+      <c r="C40" s="230"/>
+      <c r="D40" s="230"/>
+      <c r="E40" s="230"/>
+      <c r="F40" s="230"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="219">
+        <v>29600</v>
+      </c>
+      <c r="I40" s="143"/>
+      <c r="J40" s="143"/>
+      <c r="K40" s="143"/>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="229" t="s">
+        <v>154</v>
+      </c>
+      <c r="B41" s="230"/>
+      <c r="C41" s="230"/>
+      <c r="D41" s="230"/>
+      <c r="E41" s="230"/>
+      <c r="F41" s="230"/>
+      <c r="G41" s="231"/>
+      <c r="H41" s="219">
+        <v>160000</v>
+      </c>
+      <c r="I41" s="143"/>
+      <c r="J41" s="143"/>
+      <c r="K41" s="143"/>
+    </row>
+    <row r="42" spans="1:11">
+      <c r="A42" s="229" t="s">
+        <v>156</v>
+      </c>
+      <c r="B42" s="230"/>
+      <c r="C42" s="230"/>
+      <c r="D42" s="230"/>
+      <c r="E42" s="230"/>
+      <c r="F42" s="230"/>
+      <c r="G42" s="231"/>
+      <c r="H42" s="219">
+        <v>280000</v>
+      </c>
+      <c r="I42" s="143"/>
+      <c r="J42" s="143"/>
+      <c r="K42" s="143"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="A43" s="229" t="s">
+        <v>155</v>
+      </c>
+      <c r="B43" s="230"/>
+      <c r="C43" s="230"/>
+      <c r="D43" s="230"/>
+      <c r="E43" s="230"/>
+      <c r="F43" s="230"/>
+      <c r="G43" s="231"/>
+      <c r="H43" s="219">
+        <v>215000</v>
+      </c>
+      <c r="I43" s="143"/>
+      <c r="J43" s="143"/>
+      <c r="K43" s="143"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="A44" s="232" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="230"/>
+      <c r="C44" s="230"/>
+      <c r="D44" s="230"/>
+      <c r="E44" s="230"/>
+      <c r="F44" s="230"/>
+      <c r="G44" s="231"/>
+      <c r="H44" s="219">
+        <v>31939.11</v>
+      </c>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="A45" s="232" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" s="230"/>
+      <c r="C45" s="230"/>
+      <c r="D45" s="230"/>
+      <c r="E45" s="230"/>
+      <c r="F45" s="230"/>
+      <c r="G45" s="231"/>
+      <c r="H45" s="219">
+        <v>14500</v>
+      </c>
+      <c r="I45" s="143"/>
+      <c r="J45" s="143"/>
+      <c r="K45" s="143"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="A46" s="218" t="s">
+        <v>151</v>
+      </c>
+      <c r="B46" s="218"/>
+      <c r="C46" s="218"/>
+      <c r="D46" s="218"/>
+      <c r="E46" s="218"/>
+      <c r="F46" s="218"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="219">
+        <v>75000</v>
+      </c>
+      <c r="I46" s="143"/>
+      <c r="J46" s="143"/>
+      <c r="K46" s="143"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="218" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="218"/>
+      <c r="C47" s="218"/>
+      <c r="D47" s="218"/>
+      <c r="E47" s="218"/>
+      <c r="F47" s="218"/>
+      <c r="G47" s="218"/>
+      <c r="H47" s="219">
+        <v>200000</v>
+      </c>
+      <c r="I47" s="143"/>
+      <c r="J47" s="143"/>
+      <c r="K47" s="143"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="A48" s="218" t="s">
         <v>159</v>
       </c>
-      <c r="B29" s="185"/>
-      <c r="C29" s="179"/>
-      <c r="D29" s="179"/>
-      <c r="E29" s="179"/>
-      <c r="F29" s="179"/>
-      <c r="G29" s="179"/>
-      <c r="H29" s="110">
-        <f>18001.98+2000.22+31929.89</f>
-        <v>51932.09</v>
-      </c>
-      <c r="I29" s="165"/>
-      <c r="J29" s="165"/>
-      <c r="K29" s="165"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="179" t="s">
-        <v>132</v>
-      </c>
-      <c r="B30" s="179"/>
-      <c r="C30" s="179"/>
-      <c r="D30" s="179"/>
-      <c r="E30" s="179"/>
-      <c r="F30" s="179"/>
-      <c r="G30" s="179"/>
-      <c r="H30" s="110">
-        <v>0</v>
-      </c>
-      <c r="I30" s="165"/>
-      <c r="J30" s="165"/>
-      <c r="K30" s="165"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="179" t="s">
+      <c r="B48" s="218"/>
+      <c r="C48" s="218"/>
+      <c r="D48" s="218"/>
+      <c r="E48" s="218"/>
+      <c r="F48" s="218"/>
+      <c r="G48" s="218"/>
+      <c r="H48" s="219">
+        <f>120000+55000+23500+41500</f>
+        <v>240000</v>
+      </c>
+      <c r="I48" s="143"/>
+      <c r="J48" s="143"/>
+      <c r="K48" s="143"/>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="218" t="s">
+        <v>73</v>
+      </c>
+      <c r="B49" s="218"/>
+      <c r="C49" s="218"/>
+      <c r="D49" s="218"/>
+      <c r="E49" s="218"/>
+      <c r="F49" s="218"/>
+      <c r="G49" s="218"/>
+      <c r="H49" s="220">
+        <f>SUM(H38:H47)</f>
+        <v>1145019.7999999998</v>
+      </c>
+      <c r="I49" s="143"/>
+      <c r="J49" s="143"/>
+      <c r="K49" s="143"/>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" s="227" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="227"/>
+      <c r="C50" s="227"/>
+      <c r="D50" s="227"/>
+      <c r="E50" s="227"/>
+      <c r="F50" s="227"/>
+      <c r="G50" s="227"/>
+      <c r="H50" s="227"/>
+      <c r="I50" s="143"/>
+      <c r="J50" s="143"/>
+      <c r="K50" s="143"/>
+    </row>
+    <row r="51" spans="1:11">
+      <c r="A51" s="228" t="s">
+        <v>70</v>
+      </c>
+      <c r="B51" s="228"/>
+      <c r="C51" s="228"/>
+      <c r="D51" s="228"/>
+      <c r="E51" s="228"/>
+      <c r="F51" s="228"/>
+      <c r="G51" s="228"/>
+      <c r="H51" s="219">
+        <v>209000</v>
+      </c>
+      <c r="I51" s="143"/>
+      <c r="J51" s="143" t="s">
+        <v>146</v>
+      </c>
+      <c r="K51" s="143"/>
+    </row>
+    <row r="52" spans="1:11">
+      <c r="A52" s="228" t="s">
+        <v>112</v>
+      </c>
+      <c r="B52" s="228"/>
+      <c r="C52" s="228"/>
+      <c r="D52" s="228"/>
+      <c r="E52" s="228"/>
+      <c r="F52" s="228"/>
+      <c r="G52" s="228"/>
+      <c r="H52" s="219">
+        <v>50000</v>
+      </c>
+      <c r="I52" s="143"/>
+      <c r="J52" s="143"/>
+      <c r="K52" s="143"/>
+    </row>
+    <row r="53" spans="1:11">
+      <c r="A53" s="218" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="179"/>
-      <c r="C31" s="179"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="179"/>
-      <c r="H31" s="181">
-        <f>SUM(H28:H30)</f>
-        <v>51932.09</v>
-      </c>
-      <c r="I31" s="165"/>
-      <c r="J31" s="165"/>
-      <c r="K31" s="165"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="184" t="s">
-        <v>125</v>
-      </c>
-      <c r="B32" s="184"/>
-      <c r="C32" s="184"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
-      <c r="F32" s="184"/>
-      <c r="G32" s="184"/>
-      <c r="H32" s="184"/>
-      <c r="I32" s="165"/>
-      <c r="J32" s="165"/>
-      <c r="K32" s="165"/>
-    </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A33" s="179" t="s">
-        <v>134</v>
-      </c>
-      <c r="B33" s="179"/>
-      <c r="C33" s="179"/>
-      <c r="D33" s="179"/>
-      <c r="E33" s="179"/>
-      <c r="F33" s="179"/>
-      <c r="G33" s="179"/>
-      <c r="H33" s="110">
-        <v>283260.5</v>
-      </c>
-      <c r="I33" s="165"/>
-      <c r="J33" s="165"/>
-      <c r="K33" s="165"/>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" s="186" t="s">
-        <v>97</v>
-      </c>
-      <c r="B34" s="179"/>
-      <c r="C34" s="179"/>
-      <c r="D34" s="179"/>
-      <c r="E34" s="179"/>
-      <c r="F34" s="179"/>
-      <c r="G34" s="179"/>
-      <c r="H34" s="110">
-        <v>81399.570000000007</v>
-      </c>
-      <c r="I34" s="165"/>
-      <c r="J34" s="165"/>
-      <c r="K34" s="165"/>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" s="179" t="s">
+      <c r="B53" s="218"/>
+      <c r="C53" s="218"/>
+      <c r="D53" s="218"/>
+      <c r="E53" s="218"/>
+      <c r="F53" s="218"/>
+      <c r="G53" s="218"/>
+      <c r="H53" s="226">
+        <f>SUM(H51:H52)</f>
+        <v>259000</v>
+      </c>
+      <c r="I53" s="143"/>
+      <c r="J53" s="143"/>
+      <c r="K53" s="154"/>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
+      <c r="A54" s="233" t="s">
+        <v>127</v>
+      </c>
+      <c r="B54" s="234"/>
+      <c r="C54" s="234"/>
+      <c r="D54" s="234"/>
+      <c r="E54" s="234"/>
+      <c r="F54" s="234"/>
+      <c r="G54" s="234"/>
+      <c r="H54" s="235"/>
+      <c r="I54" s="159"/>
+      <c r="J54" s="159"/>
+      <c r="K54" s="159"/>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1">
+      <c r="A55" s="228" t="s">
+        <v>114</v>
+      </c>
+      <c r="B55" s="228"/>
+      <c r="C55" s="228"/>
+      <c r="D55" s="228"/>
+      <c r="E55" s="228"/>
+      <c r="F55" s="228"/>
+      <c r="G55" s="228"/>
+      <c r="H55" s="219">
+        <v>28834</v>
+      </c>
+      <c r="I55" s="160"/>
+      <c r="J55" s="159"/>
+      <c r="K55" s="159"/>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1">
+      <c r="A56" s="228" t="s">
         <v>73</v>
       </c>
-      <c r="B35" s="179"/>
-      <c r="C35" s="179"/>
-      <c r="D35" s="179"/>
-      <c r="E35" s="179"/>
-      <c r="F35" s="179"/>
-      <c r="G35" s="179"/>
-      <c r="H35" s="187">
-        <f>SUM(H33:H34)</f>
-        <v>364660.07</v>
-      </c>
-      <c r="I35" s="165"/>
-      <c r="J35" s="165"/>
-      <c r="K35" s="165"/>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="177" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="177"/>
-      <c r="C36" s="177"/>
-      <c r="D36" s="177"/>
-      <c r="E36" s="177"/>
-      <c r="F36" s="177"/>
-      <c r="G36" s="177"/>
-      <c r="H36" s="177"/>
-      <c r="I36" s="165"/>
-      <c r="J36" s="165"/>
-      <c r="K36" s="165"/>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" s="188" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="179"/>
-      <c r="C37" s="179"/>
-      <c r="D37" s="179"/>
-      <c r="E37" s="179"/>
-      <c r="F37" s="179"/>
-      <c r="G37" s="179"/>
-      <c r="H37" s="110">
-        <v>102500</v>
-      </c>
-      <c r="I37" s="165"/>
-      <c r="J37" s="165"/>
-      <c r="K37" s="165"/>
-    </row>
-    <row r="38" spans="1:11">
-      <c r="A38" s="179" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" s="179"/>
-      <c r="C38" s="179"/>
-      <c r="D38" s="179"/>
-      <c r="E38" s="179"/>
-      <c r="F38" s="179"/>
-      <c r="G38" s="179"/>
-      <c r="H38" s="110">
-        <v>35247.839999999997</v>
-      </c>
-      <c r="I38" s="165"/>
-      <c r="J38" s="165"/>
-      <c r="K38" s="165"/>
-    </row>
-    <row r="39" spans="1:11">
-      <c r="A39" s="189" t="s">
+      <c r="B56" s="228"/>
+      <c r="C56" s="228"/>
+      <c r="D56" s="228"/>
+      <c r="E56" s="228"/>
+      <c r="F56" s="228"/>
+      <c r="G56" s="228"/>
+      <c r="H56" s="220">
+        <f>SUM(H55)</f>
+        <v>28834</v>
+      </c>
+      <c r="I56" s="159"/>
+      <c r="J56" s="159"/>
+      <c r="K56" s="159"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1">
+      <c r="A57" s="227" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="227"/>
+      <c r="C57" s="227"/>
+      <c r="D57" s="227"/>
+      <c r="E57" s="227"/>
+      <c r="F57" s="227"/>
+      <c r="G57" s="227"/>
+      <c r="H57" s="227"/>
+      <c r="I57" s="159"/>
+      <c r="J57" s="159"/>
+      <c r="K57" s="159"/>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1">
+      <c r="A58" s="228" t="s">
+        <v>161</v>
+      </c>
+      <c r="B58" s="228"/>
+      <c r="C58" s="228"/>
+      <c r="D58" s="228"/>
+      <c r="E58" s="228"/>
+      <c r="F58" s="228"/>
+      <c r="G58" s="228"/>
+      <c r="H58" s="219">
+        <v>160000</v>
+      </c>
+      <c r="I58" s="159"/>
+      <c r="J58" s="159"/>
+      <c r="K58" s="159"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A59" s="228" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="228"/>
+      <c r="C59" s="228"/>
+      <c r="D59" s="228"/>
+      <c r="E59" s="228"/>
+      <c r="F59" s="228"/>
+      <c r="G59" s="228"/>
+      <c r="H59" s="220">
+        <f>SUM(H58:H58)</f>
+        <v>160000</v>
+      </c>
+      <c r="I59" s="160"/>
+      <c r="J59" s="159"/>
+      <c r="K59" s="159"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A60" s="233"/>
+      <c r="B60" s="234"/>
+      <c r="C60" s="234"/>
+      <c r="D60" s="234"/>
+      <c r="E60" s="234"/>
+      <c r="F60" s="234"/>
+      <c r="G60" s="234"/>
+      <c r="H60" s="235"/>
+      <c r="I60" s="159"/>
+      <c r="J60" s="159"/>
+      <c r="K60" s="159"/>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A61" s="229"/>
+      <c r="B61" s="230"/>
+      <c r="C61" s="230"/>
+      <c r="D61" s="230"/>
+      <c r="E61" s="230"/>
+      <c r="F61" s="230"/>
+      <c r="G61" s="230"/>
+      <c r="H61" s="236">
+        <v>0</v>
+      </c>
+      <c r="I61" s="159"/>
+      <c r="J61" s="159"/>
+      <c r="K61" s="159"/>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A62" s="237"/>
+      <c r="B62" s="238"/>
+      <c r="C62" s="238"/>
+      <c r="D62" s="238"/>
+      <c r="E62" s="238"/>
+      <c r="F62" s="238"/>
+      <c r="G62" s="238"/>
+      <c r="H62" s="239">
+        <v>0</v>
+      </c>
+      <c r="I62" s="159"/>
+      <c r="J62" s="159"/>
+      <c r="K62" s="159"/>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A63" s="232"/>
+      <c r="B63" s="240"/>
+      <c r="C63" s="240"/>
+      <c r="D63" s="240"/>
+      <c r="E63" s="240"/>
+      <c r="F63" s="240"/>
+      <c r="G63" s="240"/>
+      <c r="H63" s="236">
+        <f>H61+H62</f>
+        <v>0</v>
+      </c>
+      <c r="I63" s="159"/>
+      <c r="J63" s="159"/>
+      <c r="K63" s="159"/>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A64" s="241" t="s">
+        <v>79</v>
+      </c>
+      <c r="B64" s="242"/>
+      <c r="C64" s="242"/>
+      <c r="D64" s="242"/>
+      <c r="E64" s="242"/>
+      <c r="F64" s="242"/>
+      <c r="G64" s="242"/>
+      <c r="H64" s="243">
+        <f>H59</f>
+        <v>160000</v>
+      </c>
+      <c r="I64" s="159"/>
+      <c r="J64" s="159"/>
+      <c r="K64" s="159"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A65" s="244"/>
+      <c r="B65" s="244"/>
+      <c r="C65" s="244"/>
+      <c r="D65" s="244"/>
+      <c r="E65" s="244"/>
+      <c r="F65" s="244"/>
+      <c r="G65" s="244"/>
+      <c r="H65" s="244"/>
+      <c r="I65" s="159"/>
+      <c r="J65" s="159"/>
+      <c r="K65" s="159"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A66" s="245"/>
+      <c r="B66" s="245"/>
+      <c r="C66" s="245"/>
+      <c r="D66" s="245"/>
+      <c r="E66" s="245"/>
+      <c r="F66" s="245"/>
+      <c r="G66" s="245"/>
+      <c r="H66" s="245"/>
+      <c r="I66" s="159"/>
+      <c r="J66" s="159"/>
+      <c r="K66" s="159"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A67" s="246" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="246"/>
+      <c r="C67" s="246"/>
+      <c r="D67" s="246"/>
+      <c r="E67" s="246"/>
+      <c r="F67" s="246"/>
+      <c r="G67" s="246"/>
+      <c r="H67" s="247"/>
+      <c r="I67" s="159"/>
+      <c r="J67" s="159"/>
+      <c r="K67" s="159"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A68" s="248" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" s="249"/>
+      <c r="C68" s="249"/>
+      <c r="D68" s="249"/>
+      <c r="E68" s="249"/>
+      <c r="F68" s="249"/>
+      <c r="G68" s="250"/>
+      <c r="H68" s="219">
+        <f>108397.71+759533.45</f>
+        <v>867931.15999999992</v>
+      </c>
+      <c r="I68" s="159"/>
+      <c r="J68" s="159"/>
+      <c r="K68" s="159"/>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1">
+      <c r="A69" s="161" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69" s="156"/>
+      <c r="C69" s="156"/>
+      <c r="D69" s="156"/>
+      <c r="E69" s="156"/>
+      <c r="F69" s="156"/>
+      <c r="G69" s="156"/>
+      <c r="H69" s="155">
+        <f>SUM(H68)</f>
+        <v>867931.15999999992</v>
+      </c>
+      <c r="I69" s="159"/>
+      <c r="J69" s="159"/>
+      <c r="K69" s="159"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="159"/>
+      <c r="B70" s="159"/>
+      <c r="C70" s="159"/>
+      <c r="D70" s="159"/>
+      <c r="E70" s="159"/>
+      <c r="F70" s="159"/>
+      <c r="G70" s="159"/>
+      <c r="H70" s="162"/>
+      <c r="I70" s="159"/>
+      <c r="J70" s="159"/>
+      <c r="K70" s="159"/>
+    </row>
+    <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A71" s="183" t="s">
+        <v>80</v>
+      </c>
+      <c r="B71" s="184"/>
+      <c r="C71" s="184"/>
+      <c r="D71" s="184"/>
+      <c r="E71" s="184"/>
+      <c r="F71" s="184"/>
+      <c r="G71" s="184"/>
+      <c r="H71" s="163">
+        <f>H69</f>
+        <v>867931.15999999992</v>
+      </c>
+      <c r="I71" s="159"/>
+      <c r="J71" s="159"/>
+      <c r="K71" s="159"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="198" t="s">
+        <v>86</v>
+      </c>
+      <c r="B72" s="199"/>
+      <c r="C72" s="199"/>
+      <c r="D72" s="199"/>
+      <c r="E72" s="199"/>
+      <c r="F72" s="199"/>
+      <c r="G72" s="200"/>
+      <c r="H72" s="163">
+        <v>0</v>
+      </c>
+      <c r="I72" s="159"/>
+      <c r="J72" s="159"/>
+      <c r="K72" s="159"/>
+    </row>
+    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A73" s="198" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" s="199"/>
+      <c r="C73" s="199"/>
+      <c r="D73" s="199"/>
+      <c r="E73" s="199"/>
+      <c r="F73" s="199"/>
+      <c r="G73" s="200"/>
+      <c r="H73" s="163"/>
+      <c r="I73" s="159"/>
+      <c r="J73" s="159"/>
+      <c r="K73" s="159"/>
+    </row>
+    <row r="74" spans="1:11" ht="18.75">
+      <c r="A74" s="183" t="s">
+        <v>87</v>
+      </c>
+      <c r="B74" s="184"/>
+      <c r="C74" s="184"/>
+      <c r="D74" s="184"/>
+      <c r="E74" s="184"/>
+      <c r="F74" s="184"/>
+      <c r="G74" s="184"/>
+      <c r="H74" s="163">
+        <f>H26+H36+H49+H53+H56+H31+H18+H22</f>
+        <v>3764715.15</v>
+      </c>
+      <c r="I74" s="143"/>
+      <c r="J74" s="164"/>
+      <c r="K74" s="165"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="189" t="s">
+        <v>117</v>
+      </c>
+      <c r="B75" s="190"/>
+      <c r="C75" s="190"/>
+      <c r="D75" s="190"/>
+      <c r="E75" s="190"/>
+      <c r="F75" s="190"/>
+      <c r="G75" s="191"/>
+      <c r="H75" s="166">
+        <f>H72+H74</f>
+        <v>3764715.15</v>
+      </c>
+      <c r="I75" s="110"/>
+      <c r="J75" s="197"/>
+      <c r="K75" s="197"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75">
+      <c r="A76" s="189" t="s">
+        <v>92</v>
+      </c>
+      <c r="B76" s="190"/>
+      <c r="C76" s="190"/>
+      <c r="D76" s="190"/>
+      <c r="E76" s="190"/>
+      <c r="F76" s="190"/>
+      <c r="G76" s="191"/>
+      <c r="H76" s="167">
+        <f>H73+H71</f>
+        <v>867931.15999999992</v>
+      </c>
+      <c r="I76" s="143"/>
+      <c r="J76" s="165"/>
+      <c r="K76" s="143"/>
+    </row>
+    <row r="77" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A77" s="187" t="s">
+        <v>82</v>
+      </c>
+      <c r="B77" s="188"/>
+      <c r="C77" s="188"/>
+      <c r="D77" s="188"/>
+      <c r="E77" s="188"/>
+      <c r="F77" s="188"/>
+      <c r="G77" s="188"/>
+      <c r="H77" s="168">
+        <f>H74+H71</f>
+        <v>4632646.3099999996</v>
+      </c>
+      <c r="I77" s="143"/>
+      <c r="J77" s="154"/>
+      <c r="K77" s="143"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
+      <c r="A78" s="185" t="s">
+        <v>17</v>
+      </c>
+      <c r="B78" s="186"/>
+      <c r="C78" s="186"/>
+      <c r="D78" s="186"/>
+      <c r="E78" s="186"/>
+      <c r="F78" s="186"/>
+      <c r="G78" s="186"/>
+      <c r="H78" s="169">
+        <f>H63</f>
+        <v>0</v>
+      </c>
+      <c r="I78" s="143"/>
+      <c r="J78" s="154"/>
+      <c r="K78" s="143"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
+      <c r="A79" s="170"/>
+      <c r="B79" s="170"/>
+      <c r="C79" s="170"/>
+      <c r="D79" s="170"/>
+      <c r="E79" s="170"/>
+      <c r="F79" s="170"/>
+      <c r="G79" s="170"/>
+      <c r="H79" s="171"/>
+      <c r="I79" s="143"/>
+      <c r="J79" s="154"/>
+      <c r="K79" s="143"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75" hidden="1">
+      <c r="A80" s="170"/>
+      <c r="B80" s="170"/>
+      <c r="C80" s="170"/>
+      <c r="D80" s="170"/>
+      <c r="E80" s="170"/>
+      <c r="F80" s="170"/>
+      <c r="G80" s="170"/>
+      <c r="H80" s="171"/>
+      <c r="I80" s="143"/>
+      <c r="J80" s="154"/>
+      <c r="K80" s="143"/>
+    </row>
+    <row r="81" spans="1:11" ht="18.75" hidden="1">
+      <c r="A81" s="170"/>
+      <c r="B81" s="170"/>
+      <c r="C81" s="170"/>
+      <c r="D81" s="170"/>
+      <c r="E81" s="170"/>
+      <c r="F81" s="170"/>
+      <c r="G81" s="170"/>
+      <c r="H81" s="171"/>
+      <c r="I81" s="143"/>
+      <c r="J81" s="154"/>
+      <c r="K81" s="143"/>
+    </row>
+    <row r="82" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A82" s="153"/>
+      <c r="B82" s="153"/>
+      <c r="C82" s="153"/>
+      <c r="D82" s="153"/>
+      <c r="E82" s="153"/>
+      <c r="F82" s="153"/>
+      <c r="G82" s="153"/>
+      <c r="H82" s="153"/>
+      <c r="I82" s="143"/>
+      <c r="J82" s="143"/>
+      <c r="K82" s="143"/>
+    </row>
+    <row r="83" spans="1:11" ht="18.75">
+      <c r="A83" s="180" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" s="181"/>
+      <c r="C83" s="181"/>
+      <c r="D83" s="181"/>
+      <c r="E83" s="181"/>
+      <c r="F83" s="181"/>
+      <c r="G83" s="181"/>
+      <c r="H83" s="182"/>
+      <c r="I83" s="143"/>
+      <c r="J83" s="143"/>
+      <c r="K83" s="143"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75">
+      <c r="A84" s="172" t="s">
+        <v>12</v>
+      </c>
+      <c r="B84" s="173"/>
+      <c r="C84" s="173"/>
+      <c r="D84" s="173"/>
+      <c r="E84" s="173"/>
+      <c r="F84" s="173"/>
+      <c r="G84" s="173"/>
+      <c r="H84" s="174">
+        <v>4157321.54</v>
+      </c>
+      <c r="I84" s="143"/>
+      <c r="J84" s="143"/>
+      <c r="K84" s="143"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" s="157" t="s">
+        <v>141</v>
+      </c>
+      <c r="B85" s="158"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
+      <c r="E85" s="158"/>
+      <c r="F85" s="158"/>
+      <c r="G85" s="158"/>
+      <c r="H85" s="18">
+        <f>Planilla!G32</f>
+        <v>2271965.5230871504</v>
+      </c>
+      <c r="I85" s="143"/>
+      <c r="J85" s="143"/>
+      <c r="K85" s="143"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="150" t="s">
         <v>152</v>
       </c>
-      <c r="B39" s="190"/>
-      <c r="C39" s="190"/>
-      <c r="D39" s="190"/>
-      <c r="E39" s="190"/>
-      <c r="F39" s="190"/>
-      <c r="G39" s="191"/>
-      <c r="H39" s="110">
-        <v>85000</v>
-      </c>
-      <c r="I39" s="165"/>
-      <c r="J39" s="165"/>
-      <c r="K39" s="165"/>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" s="189" t="s">
-        <v>155</v>
-      </c>
-      <c r="B40" s="190"/>
-      <c r="C40" s="190"/>
-      <c r="D40" s="190"/>
-      <c r="E40" s="190"/>
-      <c r="F40" s="190"/>
-      <c r="G40" s="191"/>
-      <c r="H40" s="110">
-        <v>250000</v>
-      </c>
-      <c r="I40" s="165"/>
-      <c r="J40" s="165"/>
-      <c r="K40" s="165"/>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="189" t="s">
-        <v>153</v>
-      </c>
-      <c r="B41" s="190"/>
-      <c r="C41" s="190"/>
-      <c r="D41" s="190"/>
-      <c r="E41" s="190"/>
-      <c r="F41" s="190"/>
-      <c r="G41" s="191"/>
-      <c r="H41" s="110">
-        <v>207000</v>
-      </c>
-      <c r="I41" s="165"/>
-      <c r="J41" s="165"/>
-      <c r="K41" s="165"/>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="189" t="s">
-        <v>157</v>
-      </c>
-      <c r="B42" s="190"/>
-      <c r="C42" s="190"/>
-      <c r="D42" s="190"/>
-      <c r="E42" s="190"/>
-      <c r="F42" s="190"/>
-      <c r="G42" s="191"/>
-      <c r="H42" s="110">
-        <v>355999</v>
-      </c>
-      <c r="I42" s="165"/>
-      <c r="J42" s="165"/>
-      <c r="K42" s="165"/>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" s="192" t="s">
-        <v>158</v>
-      </c>
-      <c r="B43" s="190"/>
-      <c r="C43" s="190"/>
-      <c r="D43" s="190"/>
-      <c r="E43" s="190"/>
-      <c r="F43" s="190"/>
-      <c r="G43" s="191"/>
-      <c r="H43" s="110">
-        <f>110000+12700</f>
-        <v>122700</v>
-      </c>
-      <c r="I43" s="165"/>
-      <c r="J43" s="165"/>
-      <c r="K43" s="165"/>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" s="179" t="s">
-        <v>150</v>
-      </c>
-      <c r="B44" s="179"/>
-      <c r="C44" s="179"/>
-      <c r="D44" s="179"/>
-      <c r="E44" s="179"/>
-      <c r="F44" s="179"/>
-      <c r="G44" s="179"/>
-      <c r="H44" s="110">
-        <v>75000</v>
-      </c>
-      <c r="I44" s="165"/>
-      <c r="J44" s="165"/>
-      <c r="K44" s="165"/>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="179" t="s">
-        <v>154</v>
-      </c>
-      <c r="B45" s="179"/>
-      <c r="C45" s="179"/>
-      <c r="D45" s="179"/>
-      <c r="E45" s="179"/>
-      <c r="F45" s="179"/>
-      <c r="G45" s="179"/>
-      <c r="H45" s="110">
-        <v>413700</v>
-      </c>
-      <c r="I45" s="165"/>
-      <c r="J45" s="165"/>
-      <c r="K45" s="165"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="179" t="s">
-        <v>73</v>
-      </c>
-      <c r="B46" s="179"/>
-      <c r="C46" s="179"/>
-      <c r="D46" s="179"/>
-      <c r="E46" s="179"/>
-      <c r="F46" s="179"/>
-      <c r="G46" s="179"/>
-      <c r="H46" s="181">
-        <f>SUM(H37:H45)</f>
-        <v>1647146.8399999999</v>
-      </c>
-      <c r="I46" s="165"/>
-      <c r="J46" s="165"/>
-      <c r="K46" s="165"/>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="177" t="s">
-        <v>127</v>
-      </c>
-      <c r="B47" s="177"/>
-      <c r="C47" s="177"/>
-      <c r="D47" s="177"/>
-      <c r="E47" s="177"/>
-      <c r="F47" s="177"/>
-      <c r="G47" s="177"/>
-      <c r="H47" s="177"/>
-      <c r="I47" s="165"/>
-      <c r="J47" s="165"/>
-      <c r="K47" s="165"/>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" s="188" t="s">
-        <v>70</v>
-      </c>
-      <c r="B48" s="188"/>
-      <c r="C48" s="188"/>
-      <c r="D48" s="188"/>
-      <c r="E48" s="188"/>
-      <c r="F48" s="188"/>
-      <c r="G48" s="188"/>
-      <c r="H48" s="110">
-        <v>209000</v>
-      </c>
-      <c r="I48" s="165"/>
-      <c r="J48" s="165" t="s">
-        <v>147</v>
-      </c>
-      <c r="K48" s="165"/>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" s="188" t="s">
-        <v>113</v>
-      </c>
-      <c r="B49" s="188"/>
-      <c r="C49" s="188"/>
-      <c r="D49" s="188"/>
-      <c r="E49" s="188"/>
-      <c r="F49" s="188"/>
-      <c r="G49" s="188"/>
-      <c r="H49" s="110">
-        <v>50000</v>
-      </c>
-      <c r="I49" s="165"/>
-      <c r="J49" s="165"/>
-      <c r="K49" s="165"/>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" s="179" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" s="179"/>
-      <c r="C50" s="179"/>
-      <c r="D50" s="179"/>
-      <c r="E50" s="179"/>
-      <c r="F50" s="179"/>
-      <c r="G50" s="179"/>
-      <c r="H50" s="187">
-        <f>SUM(H48:H49)</f>
-        <v>259000</v>
-      </c>
-      <c r="I50" s="165"/>
-      <c r="J50" s="165"/>
-      <c r="K50" s="180"/>
-    </row>
-    <row r="51" spans="1:11" s="6" customFormat="1">
-      <c r="A51" s="193" t="s">
-        <v>128</v>
-      </c>
-      <c r="B51" s="194"/>
-      <c r="C51" s="194"/>
-      <c r="D51" s="194"/>
-      <c r="E51" s="194"/>
-      <c r="F51" s="194"/>
-      <c r="G51" s="194"/>
-      <c r="H51" s="195"/>
-      <c r="I51" s="196"/>
-      <c r="J51" s="196"/>
-      <c r="K51" s="196"/>
-    </row>
-    <row r="52" spans="1:11" s="6" customFormat="1">
-      <c r="A52" s="188" t="s">
+      <c r="B86" s="151"/>
+      <c r="C86" s="151"/>
+      <c r="D86" s="151"/>
+      <c r="E86" s="151"/>
+      <c r="F86" s="151"/>
+      <c r="G86" s="151"/>
+      <c r="H86" s="14">
+        <f>-(H77)</f>
+        <v>-4632646.3099999996</v>
+      </c>
+      <c r="I86" s="143"/>
+      <c r="J86" s="143"/>
+      <c r="K86" s="143"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="150" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87" s="151"/>
+      <c r="C87" s="151"/>
+      <c r="D87" s="151"/>
+      <c r="E87" s="151"/>
+      <c r="F87" s="151"/>
+      <c r="G87" s="151"/>
+      <c r="H87" s="14">
+        <f>-H64</f>
+        <v>-160000</v>
+      </c>
+      <c r="I87" s="143"/>
+      <c r="J87" s="143"/>
+      <c r="K87" s="159"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="150" t="s">
+        <v>140</v>
+      </c>
+      <c r="B88" s="151"/>
+      <c r="C88" s="151"/>
+      <c r="D88" s="151"/>
+      <c r="E88" s="151"/>
+      <c r="F88" s="151"/>
+      <c r="G88" s="151"/>
+      <c r="H88" s="84">
+        <f>217300-H89</f>
+        <v>154086</v>
+      </c>
+      <c r="I88" s="143"/>
+      <c r="J88" s="154"/>
+      <c r="K88" s="143"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="150" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89" s="151"/>
+      <c r="C89" s="151"/>
+      <c r="D89" s="151"/>
+      <c r="E89" s="151"/>
+      <c r="F89" s="151"/>
+      <c r="G89" s="151"/>
+      <c r="H89" s="84">
+        <v>63214</v>
+      </c>
+      <c r="I89" s="165"/>
+      <c r="J89" s="154"/>
+      <c r="K89" s="143"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="150" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="188"/>
-      <c r="C52" s="188"/>
-      <c r="D52" s="188"/>
-      <c r="E52" s="188"/>
-      <c r="F52" s="188"/>
-      <c r="G52" s="188"/>
-      <c r="H52" s="110">
-        <v>28834</v>
-      </c>
-      <c r="I52" s="197"/>
-      <c r="J52" s="196"/>
-      <c r="K52" s="196"/>
-    </row>
-    <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="188" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" s="188"/>
-      <c r="C53" s="188"/>
-      <c r="D53" s="188"/>
-      <c r="E53" s="188"/>
-      <c r="F53" s="188"/>
-      <c r="G53" s="188"/>
-      <c r="H53" s="181">
-        <f>SUM(H52)</f>
-        <v>28834</v>
-      </c>
-      <c r="I53" s="196"/>
-      <c r="J53" s="196"/>
-      <c r="K53" s="196"/>
-    </row>
-    <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="177" t="s">
-        <v>129</v>
-      </c>
-      <c r="B54" s="177"/>
-      <c r="C54" s="177"/>
-      <c r="D54" s="177"/>
-      <c r="E54" s="177"/>
-      <c r="F54" s="177"/>
-      <c r="G54" s="177"/>
-      <c r="H54" s="177"/>
-      <c r="I54" s="196"/>
-      <c r="J54" s="196"/>
-      <c r="K54" s="196"/>
-    </row>
-    <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="188" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" s="188"/>
-      <c r="C55" s="188"/>
-      <c r="D55" s="188"/>
-      <c r="E55" s="188"/>
-      <c r="F55" s="188"/>
-      <c r="G55" s="188"/>
-      <c r="H55" s="110">
-        <v>110000</v>
-      </c>
-      <c r="I55" s="196"/>
-      <c r="J55" s="196"/>
-      <c r="K55" s="196"/>
-    </row>
-    <row r="56" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A56" s="188" t="s">
-        <v>74</v>
-      </c>
-      <c r="B56" s="188"/>
-      <c r="C56" s="188"/>
-      <c r="D56" s="188"/>
-      <c r="E56" s="188"/>
-      <c r="F56" s="188"/>
-      <c r="G56" s="188"/>
-      <c r="H56" s="181">
-        <f>SUM(H55:H55)</f>
-        <v>110000</v>
-      </c>
-      <c r="I56" s="197"/>
-      <c r="J56" s="196"/>
-      <c r="K56" s="196"/>
-    </row>
-    <row r="57" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="193"/>
-      <c r="B57" s="194"/>
-      <c r="C57" s="194"/>
-      <c r="D57" s="194"/>
-      <c r="E57" s="194"/>
-      <c r="F57" s="194"/>
-      <c r="G57" s="194"/>
-      <c r="H57" s="195"/>
-      <c r="I57" s="196"/>
-      <c r="J57" s="196"/>
-      <c r="K57" s="196"/>
-    </row>
-    <row r="58" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A58" s="189"/>
-      <c r="B58" s="190"/>
-      <c r="C58" s="190"/>
-      <c r="D58" s="190"/>
-      <c r="E58" s="190"/>
-      <c r="F58" s="190"/>
-      <c r="G58" s="190"/>
-      <c r="H58" s="198">
-        <v>0</v>
-      </c>
-      <c r="I58" s="196"/>
-      <c r="J58" s="196"/>
-      <c r="K58" s="196"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A59" s="199"/>
-      <c r="B59" s="200"/>
-      <c r="C59" s="200"/>
-      <c r="D59" s="200"/>
-      <c r="E59" s="200"/>
-      <c r="F59" s="200"/>
-      <c r="G59" s="200"/>
-      <c r="H59" s="201">
-        <v>0</v>
-      </c>
-      <c r="I59" s="196"/>
-      <c r="J59" s="196"/>
-      <c r="K59" s="196"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A60" s="192"/>
-      <c r="B60" s="202"/>
-      <c r="C60" s="202"/>
-      <c r="D60" s="202"/>
-      <c r="E60" s="202"/>
-      <c r="F60" s="202"/>
-      <c r="G60" s="202"/>
-      <c r="H60" s="198">
-        <f>H58+H59</f>
-        <v>0</v>
-      </c>
-      <c r="I60" s="196"/>
-      <c r="J60" s="196"/>
-      <c r="K60" s="196"/>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A61" s="203" t="s">
-        <v>79</v>
-      </c>
-      <c r="B61" s="204"/>
-      <c r="C61" s="204"/>
-      <c r="D61" s="204"/>
-      <c r="E61" s="204"/>
-      <c r="F61" s="204"/>
-      <c r="G61" s="204"/>
-      <c r="H61" s="205">
-        <f>H56</f>
-        <v>110000</v>
-      </c>
-      <c r="I61" s="196"/>
-      <c r="J61" s="196"/>
-      <c r="K61" s="196"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="206"/>
-      <c r="B62" s="206"/>
-      <c r="C62" s="206"/>
-      <c r="D62" s="206"/>
-      <c r="E62" s="206"/>
-      <c r="F62" s="206"/>
-      <c r="G62" s="206"/>
-      <c r="H62" s="206"/>
-      <c r="I62" s="196"/>
-      <c r="J62" s="196"/>
-      <c r="K62" s="196"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A63" s="207"/>
-      <c r="B63" s="207"/>
-      <c r="C63" s="207"/>
-      <c r="D63" s="207"/>
-      <c r="E63" s="207"/>
-      <c r="F63" s="207"/>
-      <c r="G63" s="207"/>
-      <c r="H63" s="207"/>
-      <c r="I63" s="196"/>
-      <c r="J63" s="196"/>
-      <c r="K63" s="196"/>
-    </row>
-    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="208" t="s">
-        <v>81</v>
-      </c>
-      <c r="B64" s="208"/>
-      <c r="C64" s="208"/>
-      <c r="D64" s="208"/>
-      <c r="E64" s="208"/>
-      <c r="F64" s="208"/>
-      <c r="G64" s="208"/>
-      <c r="H64" s="209"/>
-      <c r="I64" s="196"/>
-      <c r="J64" s="196"/>
-      <c r="K64" s="196"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A65" s="210" t="s">
-        <v>146</v>
-      </c>
-      <c r="B65" s="211"/>
-      <c r="C65" s="211"/>
-      <c r="D65" s="211"/>
-      <c r="E65" s="211"/>
-      <c r="F65" s="211"/>
-      <c r="G65" s="212"/>
-      <c r="H65" s="110">
-        <f>67896.29+809224.86+120072.2</f>
-        <v>997193.35</v>
-      </c>
-      <c r="I65" s="196"/>
-      <c r="J65" s="196"/>
-      <c r="K65" s="196"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1">
-      <c r="A66" s="213" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="188"/>
-      <c r="C66" s="188"/>
-      <c r="D66" s="188"/>
-      <c r="E66" s="188"/>
-      <c r="F66" s="188"/>
-      <c r="G66" s="188"/>
-      <c r="H66" s="181">
-        <f>SUM(H65)</f>
-        <v>997193.35</v>
-      </c>
-      <c r="I66" s="196"/>
-      <c r="J66" s="196"/>
-      <c r="K66" s="196"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="196"/>
-      <c r="B67" s="196"/>
-      <c r="C67" s="196"/>
-      <c r="D67" s="196"/>
-      <c r="E67" s="196"/>
-      <c r="F67" s="196"/>
-      <c r="G67" s="196"/>
-      <c r="H67" s="214"/>
-      <c r="I67" s="196"/>
-      <c r="J67" s="196"/>
-      <c r="K67" s="196"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="215" t="s">
-        <v>80</v>
-      </c>
-      <c r="B68" s="216"/>
-      <c r="C68" s="216"/>
-      <c r="D68" s="216"/>
-      <c r="E68" s="216"/>
-      <c r="F68" s="216"/>
-      <c r="G68" s="216"/>
-      <c r="H68" s="217">
-        <f>H66</f>
-        <v>997193.35</v>
-      </c>
-      <c r="I68" s="196"/>
-      <c r="J68" s="196"/>
-      <c r="K68" s="196"/>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="218" t="s">
-        <v>86</v>
-      </c>
-      <c r="B69" s="219"/>
-      <c r="C69" s="219"/>
-      <c r="D69" s="219"/>
-      <c r="E69" s="219"/>
-      <c r="F69" s="219"/>
-      <c r="G69" s="220"/>
-      <c r="H69" s="217">
-        <v>1500000</v>
-      </c>
-      <c r="I69" s="196"/>
-      <c r="J69" s="196"/>
-      <c r="K69" s="196"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="218" t="s">
-        <v>91</v>
-      </c>
-      <c r="B70" s="219"/>
-      <c r="C70" s="219"/>
-      <c r="D70" s="219"/>
-      <c r="E70" s="219"/>
-      <c r="F70" s="219"/>
-      <c r="G70" s="220"/>
-      <c r="H70" s="217"/>
-      <c r="I70" s="196"/>
-      <c r="J70" s="196"/>
-      <c r="K70" s="196"/>
-    </row>
-    <row r="71" spans="1:11" ht="18.75">
-      <c r="A71" s="215" t="s">
-        <v>87</v>
-      </c>
-      <c r="B71" s="216"/>
-      <c r="C71" s="216"/>
-      <c r="D71" s="216"/>
-      <c r="E71" s="216"/>
-      <c r="F71" s="216"/>
-      <c r="G71" s="216"/>
-      <c r="H71" s="217">
-        <f>H26+H35+H46+H50+H53+H31+H18+H22</f>
-        <v>2741262</v>
-      </c>
-      <c r="I71" s="165"/>
-      <c r="J71" s="221"/>
-      <c r="K71" s="222"/>
-    </row>
-    <row r="72" spans="1:11" ht="18.75">
-      <c r="A72" s="223" t="s">
-        <v>118</v>
-      </c>
-      <c r="B72" s="224"/>
-      <c r="C72" s="224"/>
-      <c r="D72" s="224"/>
-      <c r="E72" s="224"/>
-      <c r="F72" s="224"/>
-      <c r="G72" s="225"/>
-      <c r="H72" s="226">
-        <f>H69+H71</f>
-        <v>4241262</v>
-      </c>
-      <c r="I72" s="111"/>
-      <c r="J72" s="227"/>
-      <c r="K72" s="227"/>
-    </row>
-    <row r="73" spans="1:11" ht="18.75">
-      <c r="A73" s="223" t="s">
-        <v>92</v>
-      </c>
-      <c r="B73" s="224"/>
-      <c r="C73" s="224"/>
-      <c r="D73" s="224"/>
-      <c r="E73" s="224"/>
-      <c r="F73" s="224"/>
-      <c r="G73" s="225"/>
-      <c r="H73" s="228">
-        <f>H70+H68</f>
-        <v>997193.35</v>
-      </c>
-      <c r="I73" s="165"/>
-      <c r="J73" s="222"/>
-      <c r="K73" s="165"/>
-    </row>
-    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A74" s="229" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="230"/>
-      <c r="C74" s="230"/>
-      <c r="D74" s="230"/>
-      <c r="E74" s="230"/>
-      <c r="F74" s="230"/>
-      <c r="G74" s="230"/>
-      <c r="H74" s="231">
-        <f>H71+H68</f>
-        <v>3738455.35</v>
-      </c>
-      <c r="I74" s="165"/>
-      <c r="J74" s="180"/>
-      <c r="K74" s="165"/>
-    </row>
-    <row r="75" spans="1:11" ht="18.75" hidden="1">
-      <c r="A75" s="232" t="s">
-        <v>17</v>
-      </c>
-      <c r="B75" s="233"/>
-      <c r="C75" s="233"/>
-      <c r="D75" s="233"/>
-      <c r="E75" s="233"/>
-      <c r="F75" s="233"/>
-      <c r="G75" s="233"/>
-      <c r="H75" s="234">
-        <f>H60</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="165"/>
-      <c r="J75" s="180"/>
-      <c r="K75" s="165"/>
-    </row>
-    <row r="76" spans="1:11" ht="18.75" hidden="1">
-      <c r="A76" s="235"/>
-      <c r="B76" s="235"/>
-      <c r="C76" s="235"/>
-      <c r="D76" s="235"/>
-      <c r="E76" s="235"/>
-      <c r="F76" s="235"/>
-      <c r="G76" s="235"/>
-      <c r="H76" s="236"/>
-      <c r="I76" s="165"/>
-      <c r="J76" s="180"/>
-      <c r="K76" s="165"/>
-    </row>
-    <row r="77" spans="1:11" ht="18.75" hidden="1">
-      <c r="A77" s="235"/>
-      <c r="B77" s="235"/>
-      <c r="C77" s="235"/>
-      <c r="D77" s="235"/>
-      <c r="E77" s="235"/>
-      <c r="F77" s="235"/>
-      <c r="G77" s="235"/>
-      <c r="H77" s="236"/>
-      <c r="I77" s="165"/>
-      <c r="J77" s="180"/>
-      <c r="K77" s="165"/>
-    </row>
-    <row r="78" spans="1:11" ht="18.75" hidden="1">
-      <c r="A78" s="235"/>
-      <c r="B78" s="235"/>
-      <c r="C78" s="235"/>
-      <c r="D78" s="235"/>
-      <c r="E78" s="235"/>
-      <c r="F78" s="235"/>
-      <c r="G78" s="235"/>
-      <c r="H78" s="236"/>
-      <c r="I78" s="165"/>
-      <c r="J78" s="180"/>
-      <c r="K78" s="165"/>
-    </row>
-    <row r="79" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A79" s="179"/>
-      <c r="B79" s="179"/>
-      <c r="C79" s="179"/>
-      <c r="D79" s="179"/>
-      <c r="E79" s="179"/>
-      <c r="F79" s="179"/>
-      <c r="G79" s="179"/>
-      <c r="H79" s="179"/>
-      <c r="I79" s="165"/>
-      <c r="J79" s="165"/>
-      <c r="K79" s="165"/>
-    </row>
-    <row r="80" spans="1:11" ht="18.75">
-      <c r="A80" s="237" t="s">
-        <v>10</v>
-      </c>
-      <c r="B80" s="238"/>
-      <c r="C80" s="238"/>
-      <c r="D80" s="238"/>
-      <c r="E80" s="238"/>
-      <c r="F80" s="238"/>
-      <c r="G80" s="238"/>
-      <c r="H80" s="239"/>
-      <c r="I80" s="165"/>
-      <c r="J80" s="165"/>
-      <c r="K80" s="165"/>
-    </row>
-    <row r="81" spans="1:11" ht="18.75">
-      <c r="A81" s="240" t="s">
+      <c r="B90" s="175"/>
+      <c r="C90" s="151"/>
+      <c r="D90" s="151"/>
+      <c r="E90" s="151"/>
+      <c r="F90" s="151"/>
+      <c r="G90" s="151"/>
+      <c r="H90" s="84"/>
+      <c r="I90" s="143"/>
+      <c r="J90" s="143"/>
+      <c r="K90" s="143"/>
+    </row>
+    <row r="91" spans="1:11" ht="18.75">
+      <c r="A91" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B91" s="20"/>
+      <c r="C91" s="20"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+      <c r="F91" s="20"/>
+      <c r="G91" s="20"/>
+      <c r="H91" s="70">
+        <f>SUM(H84:H90)</f>
+        <v>1853940.7530871509</v>
+      </c>
+      <c r="I91" s="143"/>
+      <c r="J91" s="143"/>
+      <c r="K91" s="143"/>
+    </row>
+    <row r="92" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="93" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A93" s="177" t="s">
+        <v>96</v>
+      </c>
+      <c r="B93" s="178"/>
+      <c r="C93" s="178"/>
+      <c r="D93" s="178"/>
+      <c r="E93" s="178"/>
+      <c r="F93" s="178"/>
+      <c r="G93" s="178"/>
+      <c r="H93" s="179"/>
+    </row>
+    <row r="94" spans="1:11" ht="15.75">
+      <c r="A94" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B81" s="241"/>
-      <c r="C81" s="241"/>
-      <c r="D81" s="241"/>
-      <c r="E81" s="241"/>
-      <c r="F81" s="241"/>
-      <c r="G81" s="241"/>
-      <c r="H81" s="242">
-        <v>5631401.1872961279</v>
-      </c>
-      <c r="I81" s="165"/>
-      <c r="J81" s="165"/>
-      <c r="K81" s="165"/>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="189" t="s">
-        <v>142</v>
-      </c>
-      <c r="B82" s="190"/>
-      <c r="C82" s="190"/>
-      <c r="D82" s="190"/>
-      <c r="E82" s="190"/>
-      <c r="F82" s="190"/>
-      <c r="G82" s="190"/>
-      <c r="H82" s="18">
-        <f>Planilla!G32</f>
-        <v>2157075.7076916099</v>
-      </c>
-      <c r="I82" s="165"/>
-      <c r="J82" s="165"/>
-      <c r="K82" s="165"/>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" s="174" t="s">
-        <v>151</v>
-      </c>
-      <c r="B83" s="175"/>
-      <c r="C83" s="175"/>
-      <c r="D83" s="175"/>
-      <c r="E83" s="175"/>
-      <c r="F83" s="175"/>
-      <c r="G83" s="175"/>
-      <c r="H83" s="14">
-        <f>-(H74)</f>
-        <v>-3738455.35</v>
-      </c>
-      <c r="I83" s="165"/>
-      <c r="J83" s="165"/>
-      <c r="K83" s="165"/>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" s="174" t="s">
-        <v>83</v>
-      </c>
-      <c r="B84" s="175"/>
-      <c r="C84" s="175"/>
-      <c r="D84" s="175"/>
-      <c r="E84" s="175"/>
-      <c r="F84" s="175"/>
-      <c r="G84" s="175"/>
-      <c r="H84" s="14">
-        <f>-H61</f>
-        <v>-110000</v>
-      </c>
-      <c r="I84" s="165"/>
-      <c r="J84" s="165"/>
-      <c r="K84" s="196"/>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="174" t="s">
-        <v>141</v>
-      </c>
-      <c r="B85" s="175"/>
-      <c r="C85" s="175"/>
-      <c r="D85" s="175"/>
-      <c r="E85" s="175"/>
-      <c r="F85" s="175"/>
-      <c r="G85" s="175"/>
-      <c r="H85" s="84">
-        <f>217300-H86</f>
-        <v>154086</v>
-      </c>
-      <c r="I85" s="165"/>
-      <c r="J85" s="180"/>
-      <c r="K85" s="165"/>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="174" t="s">
-        <v>71</v>
-      </c>
-      <c r="B86" s="175"/>
-      <c r="C86" s="175"/>
-      <c r="D86" s="175"/>
-      <c r="E86" s="175"/>
-      <c r="F86" s="175"/>
-      <c r="G86" s="175"/>
-      <c r="H86" s="84">
-        <v>63214</v>
-      </c>
-      <c r="I86" s="222"/>
-      <c r="J86" s="180"/>
-      <c r="K86" s="165"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="174" t="s">
+      <c r="B94" s="73"/>
+      <c r="C94" s="73"/>
+      <c r="D94" s="73"/>
+      <c r="E94" s="73"/>
+      <c r="F94" s="73"/>
+      <c r="G94" s="73"/>
+      <c r="H94" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="B87" s="243"/>
-      <c r="C87" s="175"/>
-      <c r="D87" s="175"/>
-      <c r="E87" s="175"/>
-      <c r="F87" s="175"/>
-      <c r="G87" s="175"/>
-      <c r="H87" s="84"/>
-      <c r="I87" s="165"/>
-      <c r="J87" s="165"/>
-      <c r="K87" s="165"/>
-    </row>
-    <row r="88" spans="1:11" ht="18.75">
-      <c r="A88" s="19" t="s">
+      <c r="B95" s="77"/>
+      <c r="C95" s="4"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="109"/>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" s="55"/>
+      <c r="B96" s="83"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="55"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="55"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="18"/>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="55"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="18"/>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B88" s="20"/>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-      <c r="H88" s="70">
-        <f>SUM(H81:H87)</f>
-        <v>4157321.5449877377</v>
-      </c>
-      <c r="I88" s="165"/>
-      <c r="J88" s="165"/>
-      <c r="K88" s="165"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="90" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A90" s="148" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="149"/>
-      <c r="C90" s="149"/>
-      <c r="D90" s="149"/>
-      <c r="E90" s="149"/>
-      <c r="F90" s="149"/>
-      <c r="G90" s="149"/>
-      <c r="H90" s="150"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.75">
-      <c r="A91" s="73" t="s">
-        <v>12</v>
-      </c>
-      <c r="B91" s="73"/>
-      <c r="C91" s="73"/>
-      <c r="D91" s="73"/>
-      <c r="E91" s="73"/>
-      <c r="F91" s="73"/>
-      <c r="G91" s="73"/>
-      <c r="H91" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="55" t="s">
-        <v>117</v>
-      </c>
-      <c r="B92" s="77"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="55"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="55"/>
-      <c r="G92" s="55"/>
-      <c r="H92" s="110"/>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" s="55"/>
-      <c r="B93" s="83"/>
-      <c r="C93" s="55"/>
-      <c r="D93" s="55"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="55"/>
-      <c r="G93" s="55"/>
-      <c r="H93" s="18"/>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" s="55"/>
-      <c r="B94" s="55"/>
-      <c r="C94" s="55"/>
-      <c r="D94" s="55"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="55"/>
-      <c r="G94" s="55"/>
-      <c r="H94" s="18"/>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="71" t="s">
-        <v>11</v>
-      </c>
-      <c r="B95" s="71"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="71"/>
-      <c r="E95" s="71"/>
-      <c r="F95" s="71"/>
-      <c r="G95" s="71"/>
-      <c r="H95" s="72">
-        <f>SUM(H91:H94)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="146"/>
-      <c r="B98" s="146"/>
-      <c r="C98" s="146"/>
-      <c r="D98" s="146"/>
-      <c r="E98" s="146"/>
-      <c r="F98" s="146"/>
-      <c r="G98" s="146"/>
-      <c r="H98" s="146"/>
-    </row>
-    <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="146"/>
-      <c r="B99" s="146"/>
-      <c r="C99" s="146"/>
-      <c r="D99" s="146"/>
-      <c r="E99" s="146"/>
-      <c r="F99" s="146"/>
-      <c r="G99" s="146"/>
-      <c r="H99" s="146"/>
-    </row>
-    <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="146"/>
-      <c r="B100" s="146"/>
-      <c r="C100" s="146"/>
-      <c r="D100" s="146"/>
-      <c r="E100" s="146"/>
-      <c r="F100" s="146"/>
-      <c r="G100" s="146"/>
-      <c r="H100" s="146"/>
+      <c r="B98" s="71"/>
+      <c r="C98" s="71"/>
+      <c r="D98" s="71"/>
+      <c r="E98" s="71"/>
+      <c r="F98" s="71"/>
+      <c r="G98" s="71"/>
+      <c r="H98" s="72">
+        <f>SUM(H94:H97)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="146"/>
-      <c r="B101" s="146"/>
-      <c r="C101" s="146"/>
-      <c r="D101" s="146"/>
-      <c r="E101" s="146"/>
-      <c r="F101" s="146"/>
-      <c r="G101" s="146"/>
-      <c r="H101" s="146"/>
+      <c r="A101" s="176"/>
+      <c r="B101" s="176"/>
+      <c r="C101" s="176"/>
+      <c r="D101" s="176"/>
+      <c r="E101" s="176"/>
+      <c r="F101" s="176"/>
+      <c r="G101" s="176"/>
+      <c r="H101" s="176"/>
+    </row>
+    <row r="102" spans="1:8" hidden="1">
+      <c r="A102" s="176"/>
+      <c r="B102" s="176"/>
+      <c r="C102" s="176"/>
+      <c r="D102" s="176"/>
+      <c r="E102" s="176"/>
+      <c r="F102" s="176"/>
+      <c r="G102" s="176"/>
+      <c r="H102" s="176"/>
+    </row>
+    <row r="103" spans="1:8" hidden="1">
+      <c r="A103" s="176"/>
+      <c r="B103" s="176"/>
+      <c r="C103" s="176"/>
+      <c r="D103" s="176"/>
+      <c r="E103" s="176"/>
+      <c r="F103" s="176"/>
+      <c r="G103" s="176"/>
+      <c r="H103" s="176"/>
+    </row>
+    <row r="104" spans="1:8" hidden="1">
+      <c r="A104" s="176"/>
+      <c r="B104" s="176"/>
+      <c r="C104" s="176"/>
+      <c r="D104" s="176"/>
+      <c r="E104" s="176"/>
+      <c r="F104" s="176"/>
+      <c r="G104" s="176"/>
+      <c r="H104" s="176"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A98:H101"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A64:G64"/>
     <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A65:H66"/>
+    <mergeCell ref="A68:G68"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J72:K72"/>
-    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="J75:K75"/>
+    <mergeCell ref="A73:G73"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A54:H54"/>
     <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A62:H63"/>
-    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A101:H104"/>
+    <mergeCell ref="A93:H93"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="A77:G77"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="A75:G75"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3866,12 +3939,12 @@
       </c>
       <c r="F1" s="91" t="str">
         <f>RESUMEN!F8</f>
-        <v>AGOSTO</v>
+        <v>SEPTIEMBRE</v>
       </c>
       <c r="G1" s="92"/>
       <c r="H1" s="90" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 17/9</v>
+        <v>VTO: 16/10</v>
       </c>
       <c r="I1" s="89"/>
       <c r="J1" s="89"/>
@@ -3884,8 +3957,8 @@
     <row r="2" spans="1:17">
       <c r="A2" s="55"/>
       <c r="B2" s="55"/>
-      <c r="C2" s="109">
-        <v>1934410.7</v>
+      <c r="C2" s="108">
+        <v>3764715.15</v>
       </c>
       <c r="D2" s="55"/>
       <c r="E2" s="55"/>
@@ -3908,8 +3981,8 @@
       </c>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
-      <c r="F3" s="163">
-        <v>997193.35</v>
+      <c r="F3" s="141">
+        <v>867931.15999999992</v>
       </c>
       <c r="G3" s="103"/>
       <c r="H3" s="103"/>
@@ -3926,14 +3999,14 @@
     <row r="4" spans="1:17" ht="18.75" customHeight="1">
       <c r="A4" s="104"/>
       <c r="B4" s="105" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C4" s="55"/>
       <c r="D4" s="55"/>
       <c r="E4" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="141">
+      <c r="F4" s="140">
         <f>278067+10000+9000-3000-520+225+12</f>
         <v>293784</v>
       </c>
@@ -3951,16 +4024,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="106"/>
-      <c r="B5" s="152">
-        <f>C2</f>
-        <v>1934410.7</v>
-      </c>
-      <c r="C5" s="152"/>
+      <c r="B5" s="205">
+        <f>C2-E5</f>
+        <v>3604715.15</v>
+      </c>
+      <c r="C5" s="205"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="158">
-        <v>110000</v>
-      </c>
-      <c r="F5" s="159"/>
+      <c r="E5" s="211">
+        <v>160000</v>
+      </c>
+      <c r="F5" s="212"/>
       <c r="G5" s="100"/>
       <c r="H5" s="100"/>
       <c r="I5" s="100"/>
@@ -3973,13 +4046,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="106"/>
-      <c r="B6" s="154"/>
-      <c r="C6" s="155"/>
+      <c r="B6" s="207"/>
+      <c r="C6" s="208"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="154" t="s">
-        <v>143</v>
-      </c>
-      <c r="F6" s="155"/>
+      <c r="E6" s="207" t="s">
+        <v>142</v>
+      </c>
+      <c r="F6" s="208"/>
       <c r="G6" s="100"/>
       <c r="H6" s="100"/>
       <c r="I6" s="100"/>
@@ -3992,14 +4065,14 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="106"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="152"/>
+      <c r="B7" s="205"/>
+      <c r="C7" s="205"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="156">
+      <c r="E7" s="209">
         <f>F3</f>
-        <v>997193.35</v>
-      </c>
-      <c r="F7" s="157"/>
+        <v>867931.15999999992</v>
+      </c>
+      <c r="F7" s="210"/>
       <c r="G7" s="100"/>
       <c r="H7" s="100"/>
       <c r="I7" s="100"/>
@@ -4030,19 +4103,19 @@
         <v>16</v>
       </c>
       <c r="G8" s="98" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H8" s="98" t="s">
         <v>63</v>
       </c>
       <c r="I8" s="98" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J8" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="108" t="s">
-        <v>122</v>
+      <c r="K8" s="216" t="s">
+        <v>121</v>
       </c>
       <c r="L8" s="95" t="s">
         <v>81</v>
@@ -4051,34 +4124,34 @@
         <v>7</v>
       </c>
       <c r="N8" s="95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="O8" s="99" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="15" customHeight="1">
-      <c r="A9" s="130">
+      <c r="A9" s="129">
         <v>1</v>
       </c>
-      <c r="B9" s="126" t="s">
+      <c r="B9" s="125" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="127" t="s">
+      <c r="C9" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="127" t="s">
+      <c r="D9" s="126" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="128">
+      <c r="E9" s="127">
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="84">
-        <v>285440.19193161</v>
-      </c>
-      <c r="G9" s="133">
+        <v>123184.96402499999</v>
+      </c>
+      <c r="G9" s="132">
         <f>F9</f>
-        <v>285440.19193161</v>
+        <v>123184.96402499999</v>
       </c>
       <c r="H9" s="62">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
@@ -4094,23 +4167,23 @@
       </c>
       <c r="K9" s="62">
         <f>E$5*E9</f>
-        <v>4455</v>
+        <v>6480</v>
       </c>
       <c r="L9" s="62">
         <f>E$7*E9</f>
-        <v>40386.330674999997</v>
-      </c>
-      <c r="M9" s="129">
+        <v>35151.21198</v>
+      </c>
+      <c r="M9" s="128">
         <f>B$5*E9</f>
-        <v>78343.633350000004</v>
-      </c>
-      <c r="N9" s="129">
+        <v>145990.963575</v>
+      </c>
+      <c r="N9" s="128">
         <f>B$7*E9</f>
         <v>0</v>
       </c>
-      <c r="O9" s="139">
+      <c r="O9" s="138">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>123184.96402499999</v>
+        <v>187622.17555499999</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -4128,11 +4201,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="14">
-        <v>162318.86135999998</v>
-      </c>
-      <c r="G10" s="133">
+        <v>197095.94243999996</v>
+      </c>
+      <c r="G10" s="132">
         <f>F10</f>
-        <v>162318.86135999998</v>
+        <v>197095.94243999996</v>
       </c>
       <c r="H10" s="21">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -4148,47 +4221,47 @@
       </c>
       <c r="K10" s="62">
         <f t="shared" ref="K10:K31" si="2">E$5*E10</f>
-        <v>7128</v>
+        <v>10368</v>
       </c>
       <c r="L10" s="62">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
-        <v>64618.129079999992</v>
+        <v>56241.93916799999</v>
       </c>
       <c r="M10" s="22">
         <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
-        <v>125349.81335999999</v>
+        <v>233585.54171999998</v>
       </c>
       <c r="N10" s="22">
         <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
         <v>0</v>
       </c>
-      <c r="O10" s="139">
+      <c r="O10" s="138">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>197095.94243999996</v>
+        <v>300195.48088799999</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
-      <c r="A11" s="125">
+      <c r="A11" s="124">
         <v>3</v>
       </c>
-      <c r="B11" s="126" t="s">
+      <c r="B11" s="125" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="127" t="s">
+      <c r="C11" s="126" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="127" t="s">
+      <c r="D11" s="126" t="s">
         <v>102</v>
       </c>
-      <c r="E11" s="128">
+      <c r="E11" s="127">
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="84">
-        <v>120737.17774</v>
-      </c>
-      <c r="G11" s="133">
+        <v>146605.31521</v>
+      </c>
+      <c r="G11" s="132">
         <f>F11</f>
-        <v>120737.17774</v>
+        <v>146605.31521</v>
       </c>
       <c r="H11" s="62">
         <f t="shared" si="0"/>
@@ -4204,77 +4277,77 @@
       </c>
       <c r="K11" s="62">
         <f t="shared" si="2"/>
-        <v>5302</v>
+        <v>7712</v>
       </c>
       <c r="L11" s="62">
         <f t="shared" si="3"/>
-        <v>48064.719469999996</v>
-      </c>
-      <c r="M11" s="129">
+        <v>41834.281911999999</v>
+      </c>
+      <c r="M11" s="128">
         <f t="shared" si="4"/>
-        <v>93238.595740000004</v>
-      </c>
-      <c r="N11" s="129">
+        <v>173747.27022999999</v>
+      </c>
+      <c r="N11" s="128">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="139">
+      <c r="O11" s="138">
         <f t="shared" si="6"/>
-        <v>146605.31521</v>
-      </c>
-      <c r="P11" s="132"/>
+        <v>223293.552142</v>
+      </c>
+      <c r="P11" s="131"/>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
-      <c r="A12" s="112">
+      <c r="A12" s="111">
         <v>4</v>
       </c>
-      <c r="B12" s="124" t="s">
+      <c r="B12" s="123" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="122" t="s">
+      <c r="C12" s="121" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="122" t="s">
+      <c r="D12" s="121" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="123">
+      <c r="E12" s="122">
         <v>5.3499999999999999E-2</v>
       </c>
-      <c r="F12" s="116">
-        <v>6319161.1107881349</v>
-      </c>
-      <c r="G12" s="134"/>
-      <c r="H12" s="117">
+      <c r="F12" s="115">
+        <v>6715695.8885622956</v>
+      </c>
+      <c r="G12" s="133"/>
+      <c r="H12" s="116">
         <f t="shared" si="0"/>
-        <v>6319161.1107881349</v>
-      </c>
-      <c r="I12" s="117">
+        <v>6715695.8885622956</v>
+      </c>
+      <c r="I12" s="116">
         <f t="shared" si="7"/>
-        <v>233808.96109916101</v>
-      </c>
-      <c r="J12" s="117">
+        <v>248480.74787680496</v>
+      </c>
+      <c r="J12" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K12" s="117">
+      <c r="K12" s="116">
         <f t="shared" si="2"/>
-        <v>5885</v>
-      </c>
-      <c r="L12" s="117">
+        <v>8560</v>
+      </c>
+      <c r="L12" s="116">
         <f t="shared" si="3"/>
-        <v>53349.844225000001</v>
-      </c>
-      <c r="M12" s="118">
+        <v>46434.317059999994</v>
+      </c>
+      <c r="M12" s="117">
         <f t="shared" si="4"/>
-        <v>103490.97245</v>
-      </c>
-      <c r="N12" s="118">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="N12" s="117">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="139">
         <f t="shared" si="6"/>
-        <v>6715695.8885622956</v>
+        <v>7212023.2140241014</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -4292,11 +4365,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="14">
-        <v>96439.446949999998</v>
-      </c>
-      <c r="G13" s="133">
+        <v>117101.755925</v>
+      </c>
+      <c r="G13" s="132">
         <f>F13</f>
-        <v>96439.446949999998</v>
+        <v>117101.755925</v>
       </c>
       <c r="H13" s="21">
         <f t="shared" si="0"/>
@@ -4312,23 +4385,23 @@
       </c>
       <c r="K13" s="62">
         <f t="shared" si="2"/>
-        <v>4235</v>
+        <v>6160</v>
       </c>
       <c r="L13" s="62">
         <f t="shared" si="3"/>
-        <v>38391.943975000002</v>
+        <v>33415.34966</v>
       </c>
       <c r="M13" s="22">
         <f t="shared" si="4"/>
-        <v>74474.811950000003</v>
+        <v>138781.53327499999</v>
       </c>
       <c r="N13" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O13" s="139">
+      <c r="O13" s="138">
         <f t="shared" si="6"/>
-        <v>117101.755925</v>
+        <v>178356.882935</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4346,19 +4419,18 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="14">
-        <v>89926.653129999992</v>
-      </c>
-      <c r="G14" s="133">
-        <f>F14</f>
-        <v>89926.653129999992</v>
+        <v>109193.585395</v>
+      </c>
+      <c r="G14" s="132">
+        <v>0</v>
       </c>
       <c r="H14" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>109193.585395</v>
       </c>
       <c r="I14" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>4040.1626596150008</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="1"/>
@@ -4366,23 +4438,23 @@
       </c>
       <c r="K14" s="62">
         <f t="shared" si="2"/>
-        <v>3949</v>
+        <v>5744</v>
       </c>
       <c r="L14" s="62">
         <f t="shared" si="3"/>
-        <v>35799.241264999997</v>
+        <v>31158.728643999999</v>
       </c>
       <c r="M14" s="22">
         <f t="shared" si="4"/>
-        <v>69445.344129999998</v>
+        <v>129409.273885</v>
       </c>
       <c r="N14" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O14" s="139">
+      <c r="O14" s="138">
         <f t="shared" si="6"/>
-        <v>109193.585395</v>
+        <v>279545.75058361504</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4393,20 +4465,18 @@
         <v>46</v>
       </c>
       <c r="C15" s="79" t="s">
-        <v>135</v>
-      </c>
-      <c r="D15" s="78" t="s">
-        <v>104</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="D15" s="78"/>
       <c r="E15" s="42">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="14">
-        <v>103703.71698</v>
-      </c>
-      <c r="G15" s="133">
+        <v>125922.40766999999</v>
+      </c>
+      <c r="G15" s="132">
         <f>F15</f>
-        <v>103703.71698</v>
+        <v>125922.40766999999</v>
       </c>
       <c r="H15" s="21">
         <f t="shared" si="0"/>
@@ -4422,24 +4492,24 @@
       </c>
       <c r="K15" s="62">
         <f t="shared" si="2"/>
-        <v>4554</v>
+        <v>6624</v>
       </c>
       <c r="L15" s="62">
         <f t="shared" si="3"/>
-        <v>41283.804689999997</v>
+        <v>35932.350023999999</v>
       </c>
       <c r="M15" s="22">
         <f t="shared" si="4"/>
-        <v>80084.602979999996</v>
+        <v>149235.20720999999</v>
       </c>
       <c r="N15" s="22">
         <v>0</v>
       </c>
-      <c r="O15" s="139">
+      <c r="O15" s="138">
         <f t="shared" si="6"/>
-        <v>125922.40766999999</v>
-      </c>
-      <c r="Q15" s="136"/>
+        <v>191791.55723400001</v>
+      </c>
+      <c r="Q15" s="135"/>
     </row>
     <row r="16" spans="1:17" ht="15" customHeight="1">
       <c r="A16" s="48">
@@ -4452,25 +4522,25 @@
         <v>75</v>
       </c>
       <c r="D16" s="78" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E16" s="42">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="14">
-        <v>134013.25745</v>
-      </c>
-      <c r="G16" s="133">
-        <f>F16</f>
-        <v>134013.25745</v>
+        <v>162725.81667500001</v>
+      </c>
+      <c r="G16" s="132">
+        <f>120000+34000</f>
+        <v>154000</v>
       </c>
       <c r="H16" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8725.8166750000091</v>
       </c>
       <c r="I16" s="21">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>322.85521697500036</v>
       </c>
       <c r="J16" s="21">
         <f t="shared" si="1"/>
@@ -4478,25 +4548,25 @@
       </c>
       <c r="K16" s="62">
         <f t="shared" si="2"/>
-        <v>5885</v>
+        <v>8560</v>
       </c>
       <c r="L16" s="62">
         <f t="shared" si="3"/>
-        <v>53349.844225000001</v>
+        <v>46434.317059999994</v>
       </c>
       <c r="M16" s="22">
         <f t="shared" si="4"/>
-        <v>103490.97245</v>
+        <v>192852.26052499999</v>
       </c>
       <c r="N16" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O16" s="139">
+      <c r="O16" s="138">
         <f t="shared" si="6"/>
-        <v>162725.81667500001</v>
-      </c>
-      <c r="Q16" s="136"/>
+        <v>256895.249476975</v>
+      </c>
+      <c r="Q16" s="135"/>
     </row>
     <row r="17" spans="1:18" ht="15" customHeight="1">
       <c r="A17" s="48">
@@ -4509,22 +4579,25 @@
         <v>26</v>
       </c>
       <c r="D17" s="78" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E17" s="42">
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="14">
-        <v>96439.446949999998</v>
-      </c>
-      <c r="G17" s="133"/>
+        <v>217109.46241214999</v>
+      </c>
+      <c r="G17" s="132">
+        <f>F17</f>
+        <v>217109.46241214999</v>
+      </c>
       <c r="H17" s="21">
         <f t="shared" si="0"/>
-        <v>96439.446949999998</v>
+        <v>0</v>
       </c>
       <c r="I17" s="21">
         <f t="shared" si="7"/>
-        <v>3568.2595371500006</v>
+        <v>0</v>
       </c>
       <c r="J17" s="21">
         <f t="shared" si="1"/>
@@ -4532,28 +4605,28 @@
       </c>
       <c r="K17" s="62">
         <f t="shared" si="2"/>
-        <v>4235</v>
+        <v>6160</v>
       </c>
       <c r="L17" s="62">
         <f t="shared" si="3"/>
-        <v>38391.943975000002</v>
+        <v>33415.34966</v>
       </c>
       <c r="M17" s="22">
         <f t="shared" si="4"/>
-        <v>74474.811950000003</v>
+        <v>138781.53327499999</v>
       </c>
       <c r="N17" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O17" s="139">
+      <c r="O17" s="138">
         <f t="shared" si="6"/>
-        <v>217109.46241214999</v>
-      </c>
-      <c r="Q17" s="136"/>
+        <v>178356.882935</v>
+      </c>
+      <c r="Q17" s="135"/>
     </row>
     <row r="18" spans="1:18" ht="15" customHeight="1">
-      <c r="A18" s="125">
+      <c r="A18" s="124">
         <v>10</v>
       </c>
       <c r="B18" s="39" t="s">
@@ -4562,14 +4635,14 @@
       <c r="C18" s="80" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="127"/>
-      <c r="E18" s="128">
+      <c r="D18" s="126"/>
+      <c r="E18" s="127">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="84">
-        <v>-161079.21336708963</v>
-      </c>
-      <c r="G18" s="133"/>
+        <v>-51885.627972089635</v>
+      </c>
+      <c r="G18" s="132"/>
       <c r="H18" s="62">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
         <v>0</v>
@@ -4580,83 +4653,83 @@
       </c>
       <c r="J18" s="62">
         <f t="shared" si="1"/>
-        <v>161079.21336708963</v>
+        <v>51885.627972089635</v>
       </c>
       <c r="K18" s="62">
         <f t="shared" si="2"/>
-        <v>3949</v>
+        <v>5744</v>
       </c>
       <c r="L18" s="62">
         <f t="shared" si="3"/>
-        <v>35799.241264999997</v>
-      </c>
-      <c r="M18" s="129">
+        <v>31158.728643999999</v>
+      </c>
+      <c r="M18" s="128">
         <f t="shared" si="4"/>
-        <v>69445.344129999998</v>
-      </c>
-      <c r="N18" s="129">
+        <v>129409.273885</v>
+      </c>
+      <c r="N18" s="128">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O18" s="139">
+      <c r="O18" s="138">
         <f t="shared" si="6"/>
-        <v>-51885.627972089635</v>
-      </c>
-      <c r="Q18" s="136"/>
+        <v>114426.37455691038</v>
+      </c>
+      <c r="Q18" s="135"/>
     </row>
     <row r="19" spans="1:18" ht="15" customHeight="1">
-      <c r="A19" s="112">
+      <c r="A19" s="111">
         <v>11</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="118" t="s">
         <v>50</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="122" t="s">
-        <v>107</v>
-      </c>
-      <c r="E19" s="123">
+      <c r="D19" s="121" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="122">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F19" s="116">
-        <v>4499793.8620253969</v>
-      </c>
-      <c r="G19" s="134"/>
-      <c r="H19" s="117">
+      <c r="F19" s="115">
+        <v>4792208.6425903365</v>
+      </c>
+      <c r="G19" s="133"/>
+      <c r="H19" s="116">
         <f t="shared" si="0"/>
-        <v>4499793.8620253969</v>
-      </c>
-      <c r="I19" s="117">
+        <v>4792208.6425903365</v>
+      </c>
+      <c r="I19" s="116">
         <f t="shared" si="7"/>
-        <v>166492.3728949397</v>
-      </c>
-      <c r="J19" s="117">
+        <v>177311.71977584247</v>
+      </c>
+      <c r="J19" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K19" s="117">
+      <c r="K19" s="116">
         <f t="shared" si="2"/>
-        <v>4554</v>
-      </c>
-      <c r="L19" s="117">
+        <v>6624</v>
+      </c>
+      <c r="L19" s="116">
         <f t="shared" si="3"/>
-        <v>41283.804689999997</v>
-      </c>
-      <c r="M19" s="118">
+        <v>35932.350023999999</v>
+      </c>
+      <c r="M19" s="117">
         <f t="shared" si="4"/>
-        <v>80084.602979999996</v>
-      </c>
-      <c r="N19" s="118">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="N19" s="117">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O19" s="140">
+      <c r="O19" s="139">
         <f t="shared" si="6"/>
-        <v>4792208.6425903365</v>
-      </c>
-      <c r="Q19" s="136"/>
+        <v>5161311.9196001785</v>
+      </c>
+      <c r="Q19" s="135"/>
     </row>
     <row r="20" spans="1:18" ht="15" customHeight="1">
       <c r="A20" s="48">
@@ -4666,20 +4739,20 @@
         <v>51</v>
       </c>
       <c r="C20" s="86" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D20" s="82" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E20" s="43">
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="14">
-        <v>134013.25745</v>
-      </c>
-      <c r="G20" s="133">
+        <v>162725.81667500001</v>
+      </c>
+      <c r="G20" s="132">
         <f>F20</f>
-        <v>134013.25745</v>
+        <v>162725.81667500001</v>
       </c>
       <c r="H20" s="21">
         <f t="shared" si="0"/>
@@ -4695,79 +4768,79 @@
       </c>
       <c r="K20" s="62">
         <f t="shared" si="2"/>
-        <v>5885</v>
+        <v>8560</v>
       </c>
       <c r="L20" s="62">
         <f t="shared" si="3"/>
-        <v>53349.844225000001</v>
+        <v>46434.317059999994</v>
       </c>
       <c r="M20" s="22">
         <f t="shared" si="4"/>
-        <v>103490.97245</v>
+        <v>192852.26052499999</v>
       </c>
       <c r="N20" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O20" s="139">
+      <c r="O20" s="138">
         <f t="shared" si="6"/>
-        <v>162725.81667500001</v>
-      </c>
-      <c r="Q20" s="136"/>
+        <v>247846.57758499999</v>
+      </c>
+      <c r="Q20" s="135"/>
     </row>
     <row r="21" spans="1:18" ht="15" customHeight="1">
-      <c r="A21" s="112">
+      <c r="A21" s="111">
         <v>13</v>
       </c>
-      <c r="B21" s="119" t="s">
+      <c r="B21" s="118" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="119" t="s">
         <v>30</v>
       </c>
-      <c r="D21" s="120"/>
-      <c r="E21" s="121">
+      <c r="D21" s="119"/>
+      <c r="E21" s="120">
         <v>3.85E-2</v>
       </c>
-      <c r="F21" s="116">
-        <v>2161953.9345871457</v>
-      </c>
-      <c r="G21" s="135">
-        <v>0</v>
-      </c>
-      <c r="H21" s="117">
+      <c r="F21" s="115">
+        <v>2359047.9860918703</v>
+      </c>
+      <c r="G21" s="134">
+        <v>0</v>
+      </c>
+      <c r="H21" s="116">
         <f t="shared" si="0"/>
-        <v>2161953.9345871457</v>
-      </c>
-      <c r="I21" s="117">
+        <v>2359047.9860918703</v>
+      </c>
+      <c r="I21" s="116">
         <f t="shared" si="7"/>
-        <v>79992.295579724407</v>
-      </c>
-      <c r="J21" s="117">
+        <v>87284.775485399208</v>
+      </c>
+      <c r="J21" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K21" s="117">
+      <c r="K21" s="116">
         <f t="shared" si="2"/>
-        <v>4235</v>
-      </c>
-      <c r="L21" s="117">
+        <v>6160</v>
+      </c>
+      <c r="L21" s="116">
         <f t="shared" si="3"/>
-        <v>38391.943975000002</v>
-      </c>
-      <c r="M21" s="118">
+        <v>33415.34966</v>
+      </c>
+      <c r="M21" s="117">
         <f t="shared" si="4"/>
-        <v>74474.811950000003</v>
-      </c>
-      <c r="N21" s="118">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="N21" s="117">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O21" s="140">
+      <c r="O21" s="139">
         <f t="shared" si="6"/>
-        <v>2359047.9860918703</v>
-      </c>
-      <c r="Q21" s="136"/>
+        <v>2624689.6445122692</v>
+      </c>
+      <c r="Q21" s="135"/>
     </row>
     <row r="22" spans="1:18" ht="15" customHeight="1">
       <c r="A22" s="48">
@@ -4780,17 +4853,16 @@
         <v>31</v>
       </c>
       <c r="D22" s="79" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E22" s="44">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="14">
-        <v>89926.653129999992</v>
-      </c>
-      <c r="G22" s="133">
-        <f>F22+RESUMEN!H43</f>
-        <v>212626.65312999999</v>
+        <v>-13506.414605000005</v>
+      </c>
+      <c r="G22" s="132">
+        <v>0</v>
       </c>
       <c r="H22" s="21">
         <f t="shared" si="0"/>
@@ -4802,29 +4874,29 @@
       </c>
       <c r="J22" s="21">
         <f t="shared" si="1"/>
-        <v>122700</v>
+        <v>13506.414605000005</v>
       </c>
       <c r="K22" s="62">
         <f t="shared" si="2"/>
-        <v>3949</v>
+        <v>5744</v>
       </c>
       <c r="L22" s="62">
         <f t="shared" si="3"/>
-        <v>35799.241264999997</v>
+        <v>31158.728643999999</v>
       </c>
       <c r="M22" s="22">
         <f t="shared" si="4"/>
-        <v>69445.344129999998</v>
+        <v>129409.273885</v>
       </c>
       <c r="N22" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O22" s="139">
+      <c r="O22" s="138">
         <f t="shared" si="6"/>
-        <v>-13506.414605000005</v>
-      </c>
-      <c r="Q22" s="136"/>
+        <v>152805.58792399999</v>
+      </c>
+      <c r="Q22" s="135"/>
     </row>
     <row r="23" spans="1:18" ht="15" customHeight="1">
       <c r="A23" s="48">
@@ -4837,17 +4909,17 @@
         <v>32</v>
       </c>
       <c r="D23" s="80" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E23" s="45">
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="14">
-        <v>103703.71698</v>
-      </c>
-      <c r="G23" s="133">
+        <v>125922.40766999999</v>
+      </c>
+      <c r="G23" s="132">
         <f>F23</f>
-        <v>103703.71698</v>
+        <v>125922.40766999999</v>
       </c>
       <c r="H23" s="21">
         <f t="shared" si="0"/>
@@ -4863,25 +4935,25 @@
       </c>
       <c r="K23" s="62">
         <f t="shared" si="2"/>
-        <v>4554</v>
+        <v>6624</v>
       </c>
       <c r="L23" s="62">
         <f t="shared" si="3"/>
-        <v>41283.804689999997</v>
+        <v>35932.350023999999</v>
       </c>
       <c r="M23" s="22">
         <f t="shared" si="4"/>
-        <v>80084.602979999996</v>
+        <v>149235.20720999999</v>
       </c>
       <c r="N23" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O23" s="139">
+      <c r="O23" s="138">
         <f t="shared" si="6"/>
-        <v>125922.40766999999</v>
-      </c>
-      <c r="Q23" s="136"/>
+        <v>191791.55723400001</v>
+      </c>
+      <c r="Q23" s="135"/>
     </row>
     <row r="24" spans="1:18" ht="15" customHeight="1">
       <c r="A24" s="48">
@@ -4898,11 +4970,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="14">
-        <v>134013.25745</v>
-      </c>
-      <c r="G24" s="133">
-        <f>F24</f>
-        <v>134013.25745</v>
+        <v>162725.81667500001</v>
+      </c>
+      <c r="G24" s="132">
+        <f>F24+35135.89</f>
+        <v>197861.70667500002</v>
       </c>
       <c r="H24" s="21">
         <f t="shared" si="0"/>
@@ -4914,29 +4986,29 @@
       </c>
       <c r="J24" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>35135.890000000014</v>
       </c>
       <c r="K24" s="62">
         <f t="shared" si="2"/>
-        <v>5885</v>
+        <v>8560</v>
       </c>
       <c r="L24" s="62">
         <f t="shared" si="3"/>
-        <v>53349.844225000001</v>
+        <v>46434.317059999994</v>
       </c>
       <c r="M24" s="22">
         <f t="shared" si="4"/>
-        <v>103490.97245</v>
+        <v>192852.26052499999</v>
       </c>
       <c r="N24" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O24" s="139">
+      <c r="O24" s="138">
         <f t="shared" si="6"/>
-        <v>162725.81667500001</v>
-      </c>
-      <c r="Q24" s="136"/>
+        <v>212710.68758499998</v>
+      </c>
+      <c r="Q24" s="135"/>
     </row>
     <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="48">
@@ -4949,17 +5021,17 @@
         <v>90</v>
       </c>
       <c r="D25" s="81" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E25" s="46">
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="14">
-        <v>96439.446949999998</v>
-      </c>
-      <c r="G25" s="133">
-        <f>F25</f>
-        <v>96439.446949999998</v>
+        <v>117101.755925</v>
+      </c>
+      <c r="G25" s="132">
+        <f>74474.81+42627</f>
+        <v>117101.81</v>
       </c>
       <c r="H25" s="21">
         <f t="shared" si="0"/>
@@ -4971,29 +5043,29 @@
       </c>
       <c r="J25" s="21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>5.4074999992735684E-2</v>
       </c>
       <c r="K25" s="62">
         <f t="shared" si="2"/>
-        <v>4235</v>
+        <v>6160</v>
       </c>
       <c r="L25" s="62">
         <f t="shared" si="3"/>
-        <v>38391.943975000002</v>
+        <v>33415.34966</v>
       </c>
       <c r="M25" s="22">
         <f t="shared" si="4"/>
-        <v>74474.811950000003</v>
+        <v>138781.53327499999</v>
       </c>
       <c r="N25" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O25" s="139">
+      <c r="O25" s="138">
         <f t="shared" si="6"/>
-        <v>117101.755925</v>
-      </c>
-      <c r="Q25" s="137"/>
+        <v>178356.82886000001</v>
+      </c>
+      <c r="Q25" s="136"/>
     </row>
     <row r="26" spans="1:18" ht="15" customHeight="1">
       <c r="A26" s="48">
@@ -5010,11 +5082,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="14">
-        <v>89926.653129999992</v>
-      </c>
-      <c r="G26" s="133">
+        <v>109193.585395</v>
+      </c>
+      <c r="G26" s="132">
         <f>F26</f>
-        <v>89926.653129999992</v>
+        <v>109193.585395</v>
       </c>
       <c r="H26" s="21">
         <f t="shared" si="0"/>
@@ -5030,83 +5102,83 @@
       </c>
       <c r="K26" s="62">
         <f t="shared" si="2"/>
-        <v>3949</v>
+        <v>5744</v>
       </c>
       <c r="L26" s="62">
         <f t="shared" si="3"/>
-        <v>35799.241264999997</v>
+        <v>31158.728643999999</v>
       </c>
       <c r="M26" s="22">
         <f t="shared" si="4"/>
-        <v>69445.344129999998</v>
+        <v>129409.273885</v>
       </c>
       <c r="N26" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O26" s="139">
+      <c r="O26" s="138">
         <f t="shared" si="6"/>
-        <v>109193.585395</v>
-      </c>
-      <c r="Q26" s="136"/>
+        <v>166312.00252899999</v>
+      </c>
+      <c r="Q26" s="135"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1">
-      <c r="A27" s="112">
+      <c r="A27" s="111">
         <v>19</v>
       </c>
-      <c r="B27" s="113" t="s">
+      <c r="B27" s="112" t="s">
         <v>58</v>
       </c>
-      <c r="C27" s="114" t="s">
+      <c r="C27" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D27" s="114" t="s">
-        <v>121</v>
-      </c>
-      <c r="E27" s="115">
+      <c r="D27" s="113" t="s">
+        <v>120</v>
+      </c>
+      <c r="E27" s="114">
         <v>4.1399999999999999E-2</v>
       </c>
-      <c r="F27" s="116">
-        <v>3777486.1683688676</v>
-      </c>
-      <c r="G27" s="134">
-        <v>103703.6</v>
-      </c>
-      <c r="H27" s="131">
+      <c r="F27" s="115">
+        <v>3935634.9310685159</v>
+      </c>
+      <c r="G27" s="133">
+        <v>125922.6</v>
+      </c>
+      <c r="H27" s="130">
         <f t="shared" si="0"/>
-        <v>3673782.5683688675</v>
-      </c>
-      <c r="I27" s="117">
+        <v>3809712.3310685158</v>
+      </c>
+      <c r="I27" s="116">
         <f t="shared" si="7"/>
-        <v>135929.95502964812</v>
-      </c>
-      <c r="J27" s="117">
+        <v>140959.35624953511</v>
+      </c>
+      <c r="J27" s="116">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K27" s="117">
+      <c r="K27" s="116">
         <f t="shared" si="2"/>
-        <v>4554</v>
-      </c>
-      <c r="L27" s="117">
+        <v>6624</v>
+      </c>
+      <c r="L27" s="116">
         <f t="shared" si="3"/>
-        <v>41283.804689999997</v>
-      </c>
-      <c r="M27" s="118">
+        <v>35932.350023999999</v>
+      </c>
+      <c r="M27" s="117">
         <f t="shared" si="4"/>
-        <v>80084.602979999996</v>
-      </c>
-      <c r="N27" s="118">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="N27" s="117">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O27" s="140">
+      <c r="O27" s="139">
         <f t="shared" si="6"/>
-        <v>3935634.9310685159</v>
-      </c>
-      <c r="P27" s="138">
+        <v>4142463.2445520507</v>
+      </c>
+      <c r="P27" s="137">
         <f>M27+N27</f>
-        <v>80084.602979999996</v>
+        <v>149235.20720999999</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="17.25" customHeight="1">
@@ -5124,40 +5196,37 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="14">
-        <v>3648286.5570198223</v>
-      </c>
-      <c r="G28" s="133"/>
+        <v>3945998.9763045558</v>
+      </c>
+      <c r="G28" s="132"/>
       <c r="H28" s="62">
         <f t="shared" si="0"/>
-        <v>3648286.5570198223</v>
+        <v>3945998.9763045558</v>
       </c>
       <c r="I28" s="21">
         <f t="shared" si="7"/>
-        <v>134986.60260973344</v>
+        <v>146001.96212326857</v>
       </c>
       <c r="J28" s="21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="62">
-        <f t="shared" si="2"/>
-        <v>5885</v>
-      </c>
+      <c r="K28" s="62"/>
       <c r="L28" s="62">
         <f t="shared" si="3"/>
-        <v>53349.844225000001</v>
+        <v>46434.317059999994</v>
       </c>
       <c r="M28" s="22">
         <f t="shared" si="4"/>
-        <v>103490.97245</v>
+        <v>192852.26052499999</v>
       </c>
       <c r="N28" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O28" s="139">
+      <c r="O28" s="138">
         <f t="shared" si="6"/>
-        <v>3945998.9763045558</v>
+        <v>4331287.5160128251</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -5172,17 +5241,17 @@
         <v>99</v>
       </c>
       <c r="D29" s="81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E29" s="46">
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="14">
-        <v>96439.446949999998</v>
-      </c>
-      <c r="G29" s="133">
+        <v>117101.755925</v>
+      </c>
+      <c r="G29" s="132">
         <f>F29</f>
-        <v>96439.446949999998</v>
+        <v>117101.755925</v>
       </c>
       <c r="H29" s="21">
         <f t="shared" si="0"/>
@@ -5198,34 +5267,34 @@
       </c>
       <c r="K29" s="62">
         <f t="shared" si="2"/>
-        <v>4235</v>
+        <v>6160</v>
       </c>
       <c r="L29" s="62">
         <f t="shared" si="3"/>
-        <v>38391.943975000002</v>
+        <v>33415.34966</v>
       </c>
       <c r="M29" s="22">
         <f t="shared" si="4"/>
-        <v>74474.811950000003</v>
+        <v>138781.53327499999</v>
       </c>
       <c r="N29" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O29" s="139">
+      <c r="O29" s="138">
         <f t="shared" si="6"/>
-        <v>117101.755925</v>
+        <v>178356.882935</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
-        <v>37237.405975000001</v>
+        <v>69390.766637499997</v>
       </c>
       <c r="Q29" s="7">
         <f>SUM(Q15:Q28)</f>
         <v>0</v>
       </c>
       <c r="R29" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1">
@@ -5236,20 +5305,20 @@
         <v>61</v>
       </c>
       <c r="C30" s="81" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D30" s="81" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30" s="46">
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="14">
-        <v>89926.653129999992</v>
-      </c>
-      <c r="G30" s="133">
+        <v>109193.585395</v>
+      </c>
+      <c r="G30" s="132">
         <f>F30</f>
-        <v>89926.653129999992</v>
+        <v>109193.585395</v>
       </c>
       <c r="H30" s="21">
         <f t="shared" si="0"/>
@@ -5265,23 +5334,23 @@
       </c>
       <c r="K30" s="62">
         <f t="shared" si="2"/>
-        <v>3949</v>
+        <v>5744</v>
       </c>
       <c r="L30" s="62">
         <f t="shared" si="3"/>
-        <v>35799.241264999997</v>
+        <v>31158.728643999999</v>
       </c>
       <c r="M30" s="22">
         <f t="shared" si="4"/>
-        <v>69445.344129999998</v>
+        <v>129409.273885</v>
       </c>
       <c r="N30" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O30" s="139">
+      <c r="O30" s="138">
         <f t="shared" si="6"/>
-        <v>109193.585395</v>
+        <v>166312.00252899999</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -5299,11 +5368,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="14">
-        <v>103703.71698</v>
-      </c>
-      <c r="G31" s="133">
+        <v>125922.40766999999</v>
+      </c>
+      <c r="G31" s="132">
         <f>F31</f>
-        <v>103703.71698</v>
+        <v>125922.40766999999</v>
       </c>
       <c r="H31" s="21">
         <f t="shared" si="0"/>
@@ -5319,23 +5388,23 @@
       </c>
       <c r="K31" s="62">
         <f t="shared" si="2"/>
-        <v>4554</v>
+        <v>6624</v>
       </c>
       <c r="L31" s="62">
         <f t="shared" si="3"/>
-        <v>41283.804689999997</v>
+        <v>35932.350023999999</v>
       </c>
       <c r="M31" s="22">
         <f t="shared" si="4"/>
-        <v>80084.602979999996</v>
+        <v>149235.20720999999</v>
       </c>
       <c r="N31" s="22">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O31" s="139">
+      <c r="O31" s="138">
         <f t="shared" si="6"/>
-        <v>125922.40766999999</v>
+        <v>191791.55723400001</v>
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75">
@@ -5352,32 +5421,32 @@
       </c>
       <c r="F32" s="85">
         <f>SUM(F9:F31)</f>
-        <v>22272713.974063884</v>
+        <v>23912020.763122637</v>
       </c>
       <c r="G32" s="85">
         <f>SUM(G9:G31)</f>
-        <v>2157075.7076916099</v>
+        <v>2271965.5230871504</v>
       </c>
       <c r="H32" s="107">
         <f>SUM(H9:H31)</f>
-        <v>20399417.479739368</v>
+        <v>21740583.226687577</v>
       </c>
       <c r="I32" s="51">
         <f>SUM(I9:I31)</f>
-        <v>754778.4467503567</v>
+        <v>804401.57938744035</v>
       </c>
       <c r="J32" s="85">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>283779.21336708963</v>
+        <v>100527.98665208965</v>
       </c>
       <c r="K32" s="76">
         <f>SUM(K9:K31)</f>
-        <v>110000</v>
+        <v>151440</v>
       </c>
       <c r="L32" s="76"/>
       <c r="M32" s="51">
         <f>SUM(M9:M31)</f>
-        <v>1934410.7000000002</v>
+        <v>3604715.15</v>
       </c>
       <c r="N32" s="76">
         <f>SUM(N9:N31)</f>
@@ -5385,124 +5454,124 @@
       </c>
       <c r="O32" s="51">
         <f>SUM(O9:O31)</f>
-        <v>23912020.763122637</v>
+        <v>27068543.129422922</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="151"/>
-      <c r="C34" s="151"/>
-      <c r="D34" s="151"/>
-      <c r="E34" s="151"/>
-      <c r="F34" s="151"/>
-      <c r="G34" s="151"/>
-      <c r="H34" s="151"/>
-      <c r="I34" s="151"/>
-      <c r="J34" s="151"/>
-      <c r="K34" s="151"/>
-      <c r="L34" s="151"/>
-      <c r="M34" s="151"/>
-      <c r="N34" s="151"/>
-      <c r="O34" s="151"/>
+      <c r="B34" s="204"/>
+      <c r="C34" s="204"/>
+      <c r="D34" s="204"/>
+      <c r="E34" s="204"/>
+      <c r="F34" s="204"/>
+      <c r="G34" s="204"/>
+      <c r="H34" s="204"/>
+      <c r="I34" s="204"/>
+      <c r="J34" s="204"/>
+      <c r="K34" s="204"/>
+      <c r="L34" s="204"/>
+      <c r="M34" s="204"/>
+      <c r="N34" s="204"/>
+      <c r="O34" s="204"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="151"/>
-      <c r="C35" s="151"/>
-      <c r="D35" s="151"/>
-      <c r="E35" s="151"/>
-      <c r="F35" s="151"/>
-      <c r="G35" s="151"/>
-      <c r="H35" s="151"/>
-      <c r="I35" s="151"/>
-      <c r="J35" s="151"/>
-      <c r="K35" s="151"/>
-      <c r="L35" s="151"/>
-      <c r="M35" s="151"/>
-      <c r="N35" s="151"/>
-      <c r="O35" s="151"/>
+      <c r="B35" s="204"/>
+      <c r="C35" s="204"/>
+      <c r="D35" s="204"/>
+      <c r="E35" s="204"/>
+      <c r="F35" s="204"/>
+      <c r="G35" s="204"/>
+      <c r="H35" s="204"/>
+      <c r="I35" s="204"/>
+      <c r="J35" s="204"/>
+      <c r="K35" s="204"/>
+      <c r="L35" s="204"/>
+      <c r="M35" s="204"/>
+      <c r="N35" s="204"/>
+      <c r="O35" s="204"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="151"/>
-      <c r="C36" s="151"/>
-      <c r="D36" s="151"/>
-      <c r="E36" s="151"/>
-      <c r="F36" s="151"/>
-      <c r="G36" s="151"/>
-      <c r="H36" s="151"/>
-      <c r="I36" s="151"/>
-      <c r="J36" s="151"/>
-      <c r="K36" s="151"/>
-      <c r="L36" s="151"/>
-      <c r="M36" s="151"/>
-      <c r="N36" s="151"/>
-      <c r="O36" s="151"/>
+      <c r="B36" s="204"/>
+      <c r="C36" s="204"/>
+      <c r="D36" s="204"/>
+      <c r="E36" s="204"/>
+      <c r="F36" s="204"/>
+      <c r="G36" s="204"/>
+      <c r="H36" s="204"/>
+      <c r="I36" s="204"/>
+      <c r="J36" s="204"/>
+      <c r="K36" s="204"/>
+      <c r="L36" s="204"/>
+      <c r="M36" s="204"/>
+      <c r="N36" s="204"/>
+      <c r="O36" s="204"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="151"/>
-      <c r="C37" s="151"/>
-      <c r="D37" s="151"/>
-      <c r="E37" s="151"/>
-      <c r="F37" s="151"/>
-      <c r="G37" s="151"/>
-      <c r="H37" s="151"/>
-      <c r="I37" s="151"/>
-      <c r="J37" s="151"/>
-      <c r="K37" s="151"/>
-      <c r="L37" s="151"/>
-      <c r="M37" s="151"/>
-      <c r="N37" s="151"/>
-      <c r="O37" s="151"/>
+      <c r="B37" s="204"/>
+      <c r="C37" s="204"/>
+      <c r="D37" s="204"/>
+      <c r="E37" s="204"/>
+      <c r="F37" s="204"/>
+      <c r="G37" s="204"/>
+      <c r="H37" s="204"/>
+      <c r="I37" s="204"/>
+      <c r="J37" s="204"/>
+      <c r="K37" s="204"/>
+      <c r="L37" s="204"/>
+      <c r="M37" s="204"/>
+      <c r="N37" s="204"/>
+      <c r="O37" s="204"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="153"/>
-      <c r="B38" s="153"/>
-      <c r="C38" s="153"/>
-      <c r="D38" s="153"/>
-      <c r="E38" s="153"/>
-      <c r="F38" s="153"/>
-      <c r="G38" s="153"/>
-      <c r="H38" s="153"/>
-      <c r="I38" s="153"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="153"/>
-      <c r="L38" s="153"/>
-      <c r="M38" s="153"/>
-      <c r="N38" s="153"/>
-      <c r="O38" s="153"/>
+      <c r="A38" s="206"/>
+      <c r="B38" s="206"/>
+      <c r="C38" s="206"/>
+      <c r="D38" s="206"/>
+      <c r="E38" s="206"/>
+      <c r="F38" s="206"/>
+      <c r="G38" s="206"/>
+      <c r="H38" s="206"/>
+      <c r="I38" s="206"/>
+      <c r="J38" s="206"/>
+      <c r="K38" s="206"/>
+      <c r="L38" s="206"/>
+      <c r="M38" s="206"/>
+      <c r="N38" s="206"/>
+      <c r="O38" s="206"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="153"/>
-      <c r="B39" s="153"/>
-      <c r="C39" s="153"/>
-      <c r="D39" s="153"/>
-      <c r="E39" s="153"/>
-      <c r="F39" s="153"/>
-      <c r="G39" s="153"/>
-      <c r="H39" s="153"/>
-      <c r="I39" s="153"/>
-      <c r="J39" s="153"/>
-      <c r="K39" s="153"/>
-      <c r="L39" s="153"/>
-      <c r="M39" s="153"/>
-      <c r="N39" s="153"/>
-      <c r="O39" s="153"/>
+      <c r="A39" s="206"/>
+      <c r="B39" s="206"/>
+      <c r="C39" s="206"/>
+      <c r="D39" s="206"/>
+      <c r="E39" s="206"/>
+      <c r="F39" s="206"/>
+      <c r="G39" s="206"/>
+      <c r="H39" s="206"/>
+      <c r="I39" s="206"/>
+      <c r="J39" s="206"/>
+      <c r="K39" s="206"/>
+      <c r="L39" s="206"/>
+      <c r="M39" s="206"/>
+      <c r="N39" s="206"/>
+      <c r="O39" s="206"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="153"/>
-      <c r="B40" s="153"/>
-      <c r="C40" s="153"/>
-      <c r="D40" s="153"/>
-      <c r="E40" s="153"/>
-      <c r="F40" s="153"/>
-      <c r="G40" s="153"/>
-      <c r="H40" s="153"/>
-      <c r="I40" s="153"/>
-      <c r="J40" s="153"/>
-      <c r="K40" s="153"/>
-      <c r="L40" s="153"/>
-      <c r="M40" s="153"/>
-      <c r="N40" s="153"/>
-      <c r="O40" s="153"/>
+      <c r="A40" s="206"/>
+      <c r="B40" s="206"/>
+      <c r="C40" s="206"/>
+      <c r="D40" s="206"/>
+      <c r="E40" s="206"/>
+      <c r="F40" s="206"/>
+      <c r="G40" s="206"/>
+      <c r="H40" s="206"/>
+      <c r="I40" s="206"/>
+      <c r="J40" s="206"/>
+      <c r="K40" s="206"/>
+      <c r="L40" s="206"/>
+      <c r="M40" s="206"/>
+      <c r="N40" s="206"/>
+      <c r="O40" s="206"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5537,15 +5606,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="160" t="s">
+      <c r="A1" s="213" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="161"/>
-      <c r="C1" s="161"/>
-      <c r="D1" s="161"/>
-      <c r="E1" s="161"/>
-      <c r="F1" s="161"/>
-      <c r="G1" s="162"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="215"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="27"/>

--- a/2026/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
+++ b/2026/BRIN 3219/Septiembre/BRIN3219-EXPENSAS-Septiembre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Septiembre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC346251-CABA-481B-AE3D-0DAA043D19BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3372CA1-D452-4FDD-A86C-890657CE5BA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,8 +18,8 @@
     <sheet name="EXTRAORDINARIAS" sheetId="28" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$P$32</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$100</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="166">
   <si>
     <t>U.F.</t>
   </si>
@@ -536,6 +536,15 @@
   </si>
   <si>
     <t>Compra termotanque porteria - Cuota 1/12</t>
+  </si>
+  <si>
+    <t>Pago Juicio Sra. Elena Final ($2.591.824,45) Se prorrateara en 6 cuotas para recuperar la caja (6 cuotas de $431.970)</t>
+  </si>
+  <si>
+    <t>PLATA APORTADA POR LA ADMINISTRACION PARA ENFRENTAR LOS GATSOS.</t>
+  </si>
+  <si>
+    <t>Cuota 1/6</t>
   </si>
 </sst>
 </file>
@@ -831,7 +840,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1348,13 +1357,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="251">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1590,7 +1608,6 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="164" fontId="26" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1637,126 +1654,6 @@
     </xf>
     <xf numFmtId="8" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1764,59 +1661,143 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="21" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="16" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="44" fontId="21" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="44" fontId="21" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="20" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="31" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="31" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="31" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="31" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1825,6 +1806,48 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="42" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2272,7 +2295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -2297,92 +2320,92 @@
     </row>
     <row r="2" spans="1:11" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="192"/>
-      <c r="E2" s="193"/>
-      <c r="F2" s="193"/>
-      <c r="G2" s="193"/>
-      <c r="H2" s="194"/>
+      <c r="D2" s="211"/>
+      <c r="E2" s="212"/>
+      <c r="F2" s="212"/>
+      <c r="G2" s="212"/>
+      <c r="H2" s="213"/>
     </row>
     <row r="3" spans="1:11">
-      <c r="A3" s="142"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
+      <c r="A3" s="141"/>
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
       <c r="D3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="195">
+      <c r="E3" s="215">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="196"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
+      <c r="F3" s="215"/>
+      <c r="G3" s="215"/>
+      <c r="H3" s="216"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="142"/>
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
+      <c r="A4" s="141"/>
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
       <c r="D4" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="144" t="s">
+      <c r="E4" s="143" t="s">
         <v>65</v>
       </c>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="144"/>
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="142"/>
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
+      <c r="A5" s="141"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
       <c r="D5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="146">
+      <c r="E5" s="145">
         <v>30707328890</v>
       </c>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="145"/>
-      <c r="I5" s="143"/>
-      <c r="J5" s="143"/>
-      <c r="K5" s="143"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="142"/>
+      <c r="J5" s="142"/>
+      <c r="K5" s="142"/>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="142"/>
-      <c r="B6" s="143"/>
-      <c r="C6" s="143"/>
+      <c r="A6" s="141"/>
+      <c r="B6" s="142"/>
+      <c r="C6" s="142"/>
       <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="143"/>
-      <c r="F6" s="143"/>
-      <c r="G6" s="143" t="s">
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142" t="s">
         <v>110</v>
       </c>
-      <c r="H6" s="145"/>
-      <c r="I6" s="143"/>
-      <c r="J6" s="143"/>
-      <c r="K6" s="143"/>
+      <c r="H6" s="144"/>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="142"/>
-      <c r="B7" s="143"/>
-      <c r="C7" s="143"/>
-      <c r="D7" s="143"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="143"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="143"/>
-      <c r="K7" s="143"/>
+      <c r="A7" s="141"/>
+      <c r="B7" s="142"/>
+      <c r="C7" s="142"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="142"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="142"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="142"/>
     </row>
     <row r="8" spans="1:11" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="15" t="s">
@@ -2403,1502 +2426,1541 @@
       <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="147"/>
-      <c r="B9" s="148"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="148"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="143"/>
-      <c r="J9" s="143"/>
-      <c r="K9" s="143"/>
+      <c r="A9" s="146"/>
+      <c r="B9" s="147"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="147"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="147"/>
+      <c r="G9" s="147"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="142"/>
+      <c r="J9" s="142"/>
+      <c r="K9" s="142"/>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="143"/>
-      <c r="C10" s="143"/>
-      <c r="D10" s="143"/>
+      <c r="B10" s="142"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
       <c r="E10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="143"/>
-      <c r="G10" s="143"/>
-      <c r="H10" s="145"/>
-      <c r="I10" s="143"/>
-      <c r="J10" s="143"/>
-      <c r="K10" s="143"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="144"/>
+      <c r="I10" s="142"/>
+      <c r="J10" s="142"/>
+      <c r="K10" s="142"/>
     </row>
     <row r="11" spans="1:11" ht="14.25" customHeight="1">
       <c r="A11" s="12"/>
-      <c r="B11" s="143"/>
-      <c r="C11" s="143"/>
-      <c r="D11" s="143"/>
+      <c r="B11" s="142"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
       <c r="E11" s="11"/>
-      <c r="F11" s="143"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="143"/>
-      <c r="K11" s="143"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="142"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="142"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="142"/>
     </row>
     <row r="12" spans="1:11" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="201"/>
-      <c r="B12" s="176"/>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="176"/>
-      <c r="F12" s="176"/>
-      <c r="G12" s="176"/>
-      <c r="H12" s="202"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="143"/>
-      <c r="K12" s="143"/>
+      <c r="A12" s="223"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="195"/>
+      <c r="D12" s="195"/>
+      <c r="E12" s="195"/>
+      <c r="F12" s="195"/>
+      <c r="G12" s="195"/>
+      <c r="H12" s="224"/>
+      <c r="I12" s="142"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" ht="13.5" customHeight="1">
-      <c r="A13" s="150"/>
-      <c r="B13" s="151"/>
-      <c r="C13" s="151"/>
-      <c r="D13" s="151"/>
-      <c r="E13" s="151"/>
-      <c r="F13" s="151"/>
-      <c r="G13" s="151"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="143"/>
-      <c r="J13" s="143"/>
-      <c r="K13" s="143"/>
+      <c r="A13" s="149"/>
+      <c r="B13" s="150"/>
+      <c r="C13" s="150"/>
+      <c r="D13" s="150"/>
+      <c r="E13" s="150"/>
+      <c r="F13" s="150"/>
+      <c r="G13" s="150"/>
+      <c r="H13" s="151"/>
+      <c r="I13" s="142"/>
+      <c r="J13" s="142"/>
+      <c r="K13" s="142"/>
     </row>
     <row r="14" spans="1:11" ht="15.75">
-      <c r="A14" s="203" t="s">
+      <c r="A14" s="229" t="s">
         <v>148</v>
       </c>
-      <c r="B14" s="203"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-      <c r="F14" s="203"/>
-      <c r="G14" s="203"/>
-      <c r="H14" s="203"/>
-      <c r="I14" s="143"/>
-      <c r="J14" s="143"/>
-      <c r="K14" s="143"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="229"/>
+      <c r="D14" s="229"/>
+      <c r="E14" s="229"/>
+      <c r="F14" s="229"/>
+      <c r="G14" s="229"/>
+      <c r="H14" s="229"/>
+      <c r="I14" s="142"/>
+      <c r="J14" s="142"/>
+      <c r="K14" s="142"/>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="217" t="s">
+      <c r="A15" s="176" t="s">
         <v>132</v>
       </c>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
-      <c r="F15" s="218"/>
-      <c r="G15" s="218"/>
-      <c r="H15" s="219">
+      <c r="B15" s="177"/>
+      <c r="C15" s="177"/>
+      <c r="D15" s="177"/>
+      <c r="E15" s="177"/>
+      <c r="F15" s="177"/>
+      <c r="G15" s="177"/>
+      <c r="H15" s="178">
         <v>442956.59</v>
       </c>
-      <c r="I15" s="143"/>
-      <c r="J15" s="143"/>
-      <c r="K15" s="143"/>
+      <c r="I15" s="142"/>
+      <c r="J15" s="142"/>
+      <c r="K15" s="142"/>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="217" t="s">
+      <c r="A16" s="176" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="218"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
-      <c r="F16" s="218"/>
-      <c r="G16" s="218"/>
-      <c r="H16" s="219">
+      <c r="B16" s="177"/>
+      <c r="C16" s="177"/>
+      <c r="D16" s="177"/>
+      <c r="E16" s="177"/>
+      <c r="F16" s="177"/>
+      <c r="G16" s="177"/>
+      <c r="H16" s="178">
         <v>69765.59</v>
       </c>
-      <c r="I16" s="154"/>
-      <c r="J16" s="143"/>
-      <c r="K16" s="143"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="142"/>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="217" t="s">
+      <c r="A17" s="176" t="s">
         <v>113</v>
       </c>
-      <c r="B17" s="218"/>
-      <c r="C17" s="218"/>
-      <c r="D17" s="218"/>
-      <c r="E17" s="218"/>
-      <c r="F17" s="218"/>
-      <c r="G17" s="218"/>
-      <c r="H17" s="219">
-        <v>0</v>
-      </c>
-      <c r="I17" s="154"/>
-      <c r="J17" s="143"/>
-      <c r="K17" s="143"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="177"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="177"/>
+      <c r="F17" s="177"/>
+      <c r="G17" s="177"/>
+      <c r="H17" s="178">
+        <v>0</v>
+      </c>
+      <c r="I17" s="153"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="142"/>
     </row>
     <row r="18" spans="1:11">
-      <c r="A18" s="217" t="s">
+      <c r="A18" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="218"/>
-      <c r="C18" s="218"/>
-      <c r="D18" s="218"/>
-      <c r="E18" s="218"/>
-      <c r="F18" s="218"/>
-      <c r="G18" s="218"/>
-      <c r="H18" s="220">
+      <c r="B18" s="177"/>
+      <c r="C18" s="177"/>
+      <c r="D18" s="177"/>
+      <c r="E18" s="177"/>
+      <c r="F18" s="177"/>
+      <c r="G18" s="177"/>
+      <c r="H18" s="179">
         <f>SUM(H15:H17)</f>
         <v>512722.18000000005</v>
       </c>
-      <c r="I18" s="154"/>
-      <c r="J18" s="143"/>
-      <c r="K18" s="143"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="142"/>
+      <c r="K18" s="142"/>
     </row>
     <row r="19" spans="1:11" hidden="1">
-      <c r="A19" s="221" t="s">
+      <c r="A19" s="222" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="221"/>
-      <c r="C19" s="221"/>
-      <c r="D19" s="221"/>
-      <c r="E19" s="221"/>
-      <c r="F19" s="221"/>
-      <c r="G19" s="221"/>
-      <c r="H19" s="221"/>
-      <c r="I19" s="143"/>
-      <c r="J19" s="143"/>
-      <c r="K19" s="143"/>
+      <c r="B19" s="222"/>
+      <c r="C19" s="222"/>
+      <c r="D19" s="222"/>
+      <c r="E19" s="222"/>
+      <c r="F19" s="222"/>
+      <c r="G19" s="222"/>
+      <c r="H19" s="222"/>
+      <c r="I19" s="142"/>
+      <c r="J19" s="142"/>
+      <c r="K19" s="142"/>
     </row>
     <row r="20" spans="1:11" hidden="1">
-      <c r="A20" s="217" t="s">
+      <c r="A20" s="176" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="218"/>
-      <c r="C20" s="218"/>
-      <c r="D20" s="218"/>
-      <c r="E20" s="218"/>
-      <c r="F20" s="218"/>
-      <c r="G20" s="218"/>
-      <c r="H20" s="219">
-        <v>0</v>
-      </c>
-      <c r="I20" s="143"/>
-      <c r="J20" s="143"/>
-      <c r="K20" s="143"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="177"/>
+      <c r="D20" s="177"/>
+      <c r="E20" s="177"/>
+      <c r="F20" s="177"/>
+      <c r="G20" s="177"/>
+      <c r="H20" s="178">
+        <v>0</v>
+      </c>
+      <c r="I20" s="142"/>
+      <c r="J20" s="142"/>
+      <c r="K20" s="142"/>
     </row>
     <row r="21" spans="1:11" hidden="1">
-      <c r="A21" s="217" t="s">
+      <c r="A21" s="176" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="218"/>
-      <c r="C21" s="218"/>
-      <c r="D21" s="218"/>
-      <c r="E21" s="218"/>
-      <c r="F21" s="218"/>
-      <c r="G21" s="218"/>
-      <c r="H21" s="219">
-        <v>0</v>
-      </c>
-      <c r="I21" s="143"/>
-      <c r="J21" s="143"/>
-      <c r="K21" s="143"/>
+      <c r="B21" s="177"/>
+      <c r="C21" s="177"/>
+      <c r="D21" s="177"/>
+      <c r="E21" s="177"/>
+      <c r="F21" s="177"/>
+      <c r="G21" s="177"/>
+      <c r="H21" s="178">
+        <v>0</v>
+      </c>
+      <c r="I21" s="142"/>
+      <c r="J21" s="142"/>
+      <c r="K21" s="142"/>
     </row>
     <row r="22" spans="1:11" hidden="1">
-      <c r="A22" s="217" t="s">
+      <c r="A22" s="176" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="218"/>
-      <c r="C22" s="218"/>
-      <c r="D22" s="218"/>
-      <c r="E22" s="218"/>
-      <c r="F22" s="218"/>
-      <c r="G22" s="218"/>
-      <c r="H22" s="220">
+      <c r="B22" s="177"/>
+      <c r="C22" s="177"/>
+      <c r="D22" s="177"/>
+      <c r="E22" s="177"/>
+      <c r="F22" s="177"/>
+      <c r="G22" s="177"/>
+      <c r="H22" s="179">
         <f>SUM(H20:H21)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="143"/>
-      <c r="J22" s="143"/>
-      <c r="K22" s="143"/>
+      <c r="I22" s="142"/>
+      <c r="J22" s="142"/>
+      <c r="K22" s="142"/>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="222" t="s">
+      <c r="A23" s="221" t="s">
         <v>123</v>
       </c>
-      <c r="B23" s="222"/>
-      <c r="C23" s="222"/>
-      <c r="D23" s="222"/>
-      <c r="E23" s="222"/>
-      <c r="F23" s="222"/>
-      <c r="G23" s="222"/>
-      <c r="H23" s="222"/>
-      <c r="I23" s="143"/>
-      <c r="J23" s="143"/>
-      <c r="K23" s="143"/>
+      <c r="B23" s="221"/>
+      <c r="C23" s="221"/>
+      <c r="D23" s="221"/>
+      <c r="E23" s="221"/>
+      <c r="F23" s="221"/>
+      <c r="G23" s="221"/>
+      <c r="H23" s="221"/>
+      <c r="I23" s="142"/>
+      <c r="J23" s="142"/>
+      <c r="K23" s="142"/>
     </row>
     <row r="24" spans="1:11">
-      <c r="A24" s="218" t="s">
+      <c r="A24" s="177" t="s">
         <v>130</v>
       </c>
-      <c r="B24" s="218"/>
-      <c r="C24" s="218"/>
-      <c r="D24" s="218"/>
-      <c r="E24" s="218"/>
-      <c r="F24" s="218"/>
-      <c r="G24" s="218"/>
-      <c r="H24" s="219">
+      <c r="B24" s="177"/>
+      <c r="C24" s="177"/>
+      <c r="D24" s="177"/>
+      <c r="E24" s="177"/>
+      <c r="F24" s="177"/>
+      <c r="G24" s="177"/>
+      <c r="H24" s="178">
         <f>(17000+32000)/2</f>
         <v>24500</v>
       </c>
-      <c r="I24" s="143"/>
-      <c r="J24" s="143"/>
-      <c r="K24" s="143"/>
+      <c r="I24" s="142"/>
+      <c r="J24" s="142"/>
+      <c r="K24" s="142"/>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="218"/>
-      <c r="B25" s="218"/>
-      <c r="C25" s="218"/>
-      <c r="D25" s="218"/>
-      <c r="E25" s="218"/>
-      <c r="F25" s="218"/>
-      <c r="G25" s="218"/>
-      <c r="H25" s="219"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
+      <c r="A25" s="177"/>
+      <c r="B25" s="177"/>
+      <c r="C25" s="177"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="177"/>
+      <c r="F25" s="177"/>
+      <c r="G25" s="177"/>
+      <c r="H25" s="178"/>
+      <c r="I25" s="142"/>
+      <c r="J25" s="142"/>
+      <c r="K25" s="142"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="218" t="s">
+      <c r="A26" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="218"/>
-      <c r="C26" s="218"/>
-      <c r="D26" s="218"/>
-      <c r="E26" s="218"/>
-      <c r="F26" s="218"/>
-      <c r="G26" s="218"/>
-      <c r="H26" s="220">
+      <c r="B26" s="177"/>
+      <c r="C26" s="177"/>
+      <c r="D26" s="177"/>
+      <c r="E26" s="177"/>
+      <c r="F26" s="177"/>
+      <c r="G26" s="177"/>
+      <c r="H26" s="179">
         <f>SUM(H24:H25)</f>
         <v>24500</v>
       </c>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
+      <c r="I26" s="142"/>
+      <c r="J26" s="142"/>
+      <c r="K26" s="142"/>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="223" t="s">
+      <c r="A27" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="223"/>
-      <c r="C27" s="223"/>
-      <c r="D27" s="223"/>
-      <c r="E27" s="223"/>
-      <c r="F27" s="223"/>
-      <c r="G27" s="223"/>
-      <c r="H27" s="223"/>
-      <c r="I27" s="143"/>
-      <c r="J27" s="143"/>
-      <c r="K27" s="143"/>
+      <c r="B27" s="214"/>
+      <c r="C27" s="214"/>
+      <c r="D27" s="214"/>
+      <c r="E27" s="214"/>
+      <c r="F27" s="214"/>
+      <c r="G27" s="214"/>
+      <c r="H27" s="214"/>
+      <c r="I27" s="142"/>
+      <c r="J27" s="142"/>
+      <c r="K27" s="142"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="217"/>
-      <c r="B28" s="218"/>
-      <c r="C28" s="218"/>
-      <c r="D28" s="218"/>
-      <c r="E28" s="218"/>
-      <c r="F28" s="218"/>
-      <c r="G28" s="218"/>
-      <c r="H28" s="219"/>
-      <c r="I28" s="143"/>
-      <c r="J28" s="143"/>
-      <c r="K28" s="143"/>
+      <c r="A28" s="176"/>
+      <c r="B28" s="177"/>
+      <c r="C28" s="177"/>
+      <c r="D28" s="177"/>
+      <c r="E28" s="177"/>
+      <c r="F28" s="177"/>
+      <c r="G28" s="177"/>
+      <c r="H28" s="178"/>
+      <c r="I28" s="142"/>
+      <c r="J28" s="142"/>
+      <c r="K28" s="142"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="217" t="s">
+      <c r="A29" s="176" t="s">
         <v>147</v>
       </c>
-      <c r="B29" s="224"/>
-      <c r="C29" s="218"/>
-      <c r="D29" s="218"/>
-      <c r="E29" s="218"/>
-      <c r="F29" s="218"/>
-      <c r="G29" s="218"/>
-      <c r="H29" s="219">
+      <c r="B29" s="180"/>
+      <c r="C29" s="177"/>
+      <c r="D29" s="177"/>
+      <c r="E29" s="177"/>
+      <c r="F29" s="177"/>
+      <c r="G29" s="177"/>
+      <c r="H29" s="178">
         <f>19505.61+2167.29+34214.38</f>
         <v>55887.28</v>
       </c>
-      <c r="I29" s="143"/>
-      <c r="J29" s="143"/>
-      <c r="K29" s="143"/>
+      <c r="I29" s="142"/>
+      <c r="J29" s="142"/>
+      <c r="K29" s="142"/>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="218" t="s">
+      <c r="A30" s="177" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="218"/>
-      <c r="C30" s="218"/>
-      <c r="D30" s="218"/>
-      <c r="E30" s="218"/>
-      <c r="F30" s="218"/>
-      <c r="G30" s="218"/>
-      <c r="H30" s="219">
-        <v>0</v>
-      </c>
-      <c r="I30" s="143"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="143"/>
+      <c r="B30" s="177"/>
+      <c r="C30" s="177"/>
+      <c r="D30" s="177"/>
+      <c r="E30" s="177"/>
+      <c r="F30" s="177"/>
+      <c r="G30" s="177"/>
+      <c r="H30" s="178">
+        <v>0</v>
+      </c>
+      <c r="I30" s="142"/>
+      <c r="J30" s="142"/>
+      <c r="K30" s="142"/>
     </row>
     <row r="31" spans="1:11">
-      <c r="A31" s="218" t="s">
+      <c r="A31" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="218"/>
-      <c r="C31" s="218"/>
-      <c r="D31" s="218"/>
-      <c r="E31" s="218"/>
-      <c r="F31" s="218"/>
-      <c r="G31" s="218"/>
-      <c r="H31" s="220">
+      <c r="B31" s="177"/>
+      <c r="C31" s="177"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="177"/>
+      <c r="F31" s="177"/>
+      <c r="G31" s="177"/>
+      <c r="H31" s="179">
         <f>SUM(H28:H30)</f>
         <v>55887.28</v>
       </c>
-      <c r="I31" s="143"/>
-      <c r="J31" s="143"/>
-      <c r="K31" s="143"/>
+      <c r="I31" s="142"/>
+      <c r="J31" s="142"/>
+      <c r="K31" s="142"/>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="223" t="s">
+      <c r="A32" s="214" t="s">
         <v>124</v>
       </c>
-      <c r="B32" s="223"/>
-      <c r="C32" s="223"/>
-      <c r="D32" s="223"/>
-      <c r="E32" s="223"/>
-      <c r="F32" s="223"/>
-      <c r="G32" s="223"/>
-      <c r="H32" s="223"/>
-      <c r="I32" s="143"/>
-      <c r="J32" s="143"/>
-      <c r="K32" s="143"/>
+      <c r="B32" s="214"/>
+      <c r="C32" s="214"/>
+      <c r="D32" s="214"/>
+      <c r="E32" s="214"/>
+      <c r="F32" s="214"/>
+      <c r="G32" s="214"/>
+      <c r="H32" s="214"/>
+      <c r="I32" s="142"/>
+      <c r="J32" s="142"/>
+      <c r="K32" s="142"/>
     </row>
     <row r="33" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A33" s="218" t="s">
+      <c r="A33" s="177" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="218"/>
-      <c r="C33" s="218"/>
-      <c r="D33" s="218"/>
-      <c r="E33" s="218"/>
-      <c r="F33" s="218"/>
-      <c r="G33" s="218"/>
-      <c r="H33" s="219">
+      <c r="B33" s="177"/>
+      <c r="C33" s="177"/>
+      <c r="D33" s="177"/>
+      <c r="E33" s="177"/>
+      <c r="F33" s="177"/>
+      <c r="G33" s="177"/>
+      <c r="H33" s="178">
         <v>1555264.54</v>
       </c>
-      <c r="I33" s="143"/>
-      <c r="J33" s="143"/>
-      <c r="K33" s="143"/>
+      <c r="I33" s="142"/>
+      <c r="J33" s="142"/>
+      <c r="K33" s="142"/>
     </row>
     <row r="34" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A34" s="218" t="s">
+      <c r="A34" s="177" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="218"/>
-      <c r="C34" s="218"/>
-      <c r="D34" s="218"/>
-      <c r="E34" s="218"/>
-      <c r="F34" s="218"/>
-      <c r="G34" s="218"/>
-      <c r="H34" s="219">
+      <c r="B34" s="177"/>
+      <c r="C34" s="177"/>
+      <c r="D34" s="177"/>
+      <c r="E34" s="177"/>
+      <c r="F34" s="177"/>
+      <c r="G34" s="177"/>
+      <c r="H34" s="178">
         <v>95000</v>
       </c>
-      <c r="I34" s="143"/>
-      <c r="J34" s="143"/>
-      <c r="K34" s="143"/>
+      <c r="I34" s="142"/>
+      <c r="J34" s="142"/>
+      <c r="K34" s="142"/>
     </row>
     <row r="35" spans="1:11">
-      <c r="A35" s="225" t="s">
+      <c r="A35" s="181" t="s">
         <v>97</v>
       </c>
-      <c r="B35" s="218"/>
-      <c r="C35" s="218"/>
-      <c r="D35" s="218"/>
-      <c r="E35" s="218"/>
-      <c r="F35" s="218"/>
-      <c r="G35" s="218"/>
-      <c r="H35" s="219">
+      <c r="B35" s="177"/>
+      <c r="C35" s="177"/>
+      <c r="D35" s="177"/>
+      <c r="E35" s="177"/>
+      <c r="F35" s="177"/>
+      <c r="G35" s="177"/>
+      <c r="H35" s="178">
         <v>88487.35</v>
       </c>
-      <c r="I35" s="143"/>
-      <c r="J35" s="143"/>
-      <c r="K35" s="143"/>
+      <c r="I35" s="142"/>
+      <c r="J35" s="142"/>
+      <c r="K35" s="142"/>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="218" t="s">
+      <c r="A36" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B36" s="218"/>
-      <c r="C36" s="218"/>
-      <c r="D36" s="218"/>
-      <c r="E36" s="218"/>
-      <c r="F36" s="218"/>
-      <c r="G36" s="218"/>
-      <c r="H36" s="226">
+      <c r="B36" s="177"/>
+      <c r="C36" s="177"/>
+      <c r="D36" s="177"/>
+      <c r="E36" s="177"/>
+      <c r="F36" s="177"/>
+      <c r="G36" s="177"/>
+      <c r="H36" s="182">
         <f>SUM(H33:H35)</f>
         <v>1738751.8900000001</v>
       </c>
-      <c r="I36" s="143"/>
-      <c r="J36" s="143"/>
-      <c r="K36" s="143"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
     </row>
     <row r="37" spans="1:11">
-      <c r="A37" s="227" t="s">
+      <c r="A37" s="225" t="s">
         <v>125</v>
       </c>
-      <c r="B37" s="227"/>
-      <c r="C37" s="227"/>
-      <c r="D37" s="227"/>
-      <c r="E37" s="227"/>
-      <c r="F37" s="227"/>
-      <c r="G37" s="227"/>
-      <c r="H37" s="227"/>
-      <c r="I37" s="143"/>
-      <c r="J37" s="143"/>
-      <c r="K37" s="143"/>
+      <c r="B37" s="225"/>
+      <c r="C37" s="225"/>
+      <c r="D37" s="225"/>
+      <c r="E37" s="225"/>
+      <c r="F37" s="225"/>
+      <c r="G37" s="225"/>
+      <c r="H37" s="225"/>
+      <c r="I37" s="142"/>
+      <c r="J37" s="142"/>
+      <c r="K37" s="142"/>
     </row>
     <row r="38" spans="1:11">
-      <c r="A38" s="228" t="s">
+      <c r="A38" s="183" t="s">
         <v>68</v>
       </c>
-      <c r="B38" s="218"/>
-      <c r="C38" s="218"/>
-      <c r="D38" s="218"/>
-      <c r="E38" s="218"/>
-      <c r="F38" s="218"/>
-      <c r="G38" s="218"/>
-      <c r="H38" s="219">
+      <c r="B38" s="177"/>
+      <c r="C38" s="177"/>
+      <c r="D38" s="177"/>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="178">
         <v>102500</v>
       </c>
-      <c r="I38" s="143"/>
-      <c r="J38" s="143"/>
-      <c r="K38" s="143"/>
+      <c r="I38" s="142"/>
+      <c r="J38" s="142"/>
+      <c r="K38" s="142"/>
     </row>
     <row r="39" spans="1:11">
-      <c r="A39" s="218" t="s">
+      <c r="A39" s="177" t="s">
         <v>69</v>
       </c>
-      <c r="B39" s="218"/>
-      <c r="C39" s="218"/>
-      <c r="D39" s="218"/>
-      <c r="E39" s="218"/>
-      <c r="F39" s="218"/>
-      <c r="G39" s="218"/>
-      <c r="H39" s="219">
+      <c r="B39" s="177"/>
+      <c r="C39" s="177"/>
+      <c r="D39" s="177"/>
+      <c r="E39" s="177"/>
+      <c r="F39" s="177"/>
+      <c r="G39" s="177"/>
+      <c r="H39" s="178">
         <v>36480.69</v>
       </c>
-      <c r="I39" s="143"/>
-      <c r="J39" s="143"/>
-      <c r="K39" s="143"/>
+      <c r="I39" s="142"/>
+      <c r="J39" s="142"/>
+      <c r="K39" s="142"/>
     </row>
     <row r="40" spans="1:11">
-      <c r="A40" s="229" t="s">
+      <c r="A40" s="184" t="s">
         <v>162</v>
       </c>
-      <c r="B40" s="230"/>
-      <c r="C40" s="230"/>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="219">
+      <c r="B40" s="185"/>
+      <c r="C40" s="185"/>
+      <c r="D40" s="185"/>
+      <c r="E40" s="185"/>
+      <c r="F40" s="185"/>
+      <c r="G40" s="186"/>
+      <c r="H40" s="178">
         <v>29600</v>
       </c>
-      <c r="I40" s="143"/>
-      <c r="J40" s="143"/>
-      <c r="K40" s="143"/>
+      <c r="I40" s="142"/>
+      <c r="J40" s="142"/>
+      <c r="K40" s="142"/>
     </row>
     <row r="41" spans="1:11">
-      <c r="A41" s="229" t="s">
+      <c r="A41" s="184" t="s">
         <v>154</v>
       </c>
-      <c r="B41" s="230"/>
-      <c r="C41" s="230"/>
-      <c r="D41" s="230"/>
-      <c r="E41" s="230"/>
-      <c r="F41" s="230"/>
-      <c r="G41" s="231"/>
-      <c r="H41" s="219">
+      <c r="B41" s="185"/>
+      <c r="C41" s="185"/>
+      <c r="D41" s="185"/>
+      <c r="E41" s="185"/>
+      <c r="F41" s="185"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="178">
         <v>160000</v>
       </c>
-      <c r="I41" s="143"/>
-      <c r="J41" s="143"/>
-      <c r="K41" s="143"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
     </row>
     <row r="42" spans="1:11">
-      <c r="A42" s="229" t="s">
+      <c r="A42" s="184" t="s">
         <v>156</v>
       </c>
-      <c r="B42" s="230"/>
-      <c r="C42" s="230"/>
-      <c r="D42" s="230"/>
-      <c r="E42" s="230"/>
-      <c r="F42" s="230"/>
-      <c r="G42" s="231"/>
-      <c r="H42" s="219">
+      <c r="B42" s="185"/>
+      <c r="C42" s="185"/>
+      <c r="D42" s="185"/>
+      <c r="E42" s="185"/>
+      <c r="F42" s="185"/>
+      <c r="G42" s="186"/>
+      <c r="H42" s="178">
         <v>280000</v>
       </c>
-      <c r="I42" s="143"/>
-      <c r="J42" s="143"/>
-      <c r="K42" s="143"/>
+      <c r="I42" s="142"/>
+      <c r="J42" s="142"/>
+      <c r="K42" s="142"/>
     </row>
     <row r="43" spans="1:11">
-      <c r="A43" s="229" t="s">
+      <c r="A43" s="184" t="s">
         <v>155</v>
       </c>
-      <c r="B43" s="230"/>
-      <c r="C43" s="230"/>
-      <c r="D43" s="230"/>
-      <c r="E43" s="230"/>
-      <c r="F43" s="230"/>
-      <c r="G43" s="231"/>
-      <c r="H43" s="219">
+      <c r="B43" s="185"/>
+      <c r="C43" s="185"/>
+      <c r="D43" s="185"/>
+      <c r="E43" s="185"/>
+      <c r="F43" s="185"/>
+      <c r="G43" s="186"/>
+      <c r="H43" s="178">
         <v>215000</v>
       </c>
-      <c r="I43" s="143"/>
-      <c r="J43" s="143"/>
-      <c r="K43" s="143"/>
+      <c r="I43" s="142"/>
+      <c r="J43" s="142"/>
+      <c r="K43" s="142"/>
     </row>
     <row r="44" spans="1:11">
-      <c r="A44" s="232" t="s">
+      <c r="A44" s="187" t="s">
         <v>153</v>
       </c>
-      <c r="B44" s="230"/>
-      <c r="C44" s="230"/>
-      <c r="D44" s="230"/>
-      <c r="E44" s="230"/>
-      <c r="F44" s="230"/>
-      <c r="G44" s="231"/>
-      <c r="H44" s="219">
+      <c r="B44" s="185"/>
+      <c r="C44" s="185"/>
+      <c r="D44" s="185"/>
+      <c r="E44" s="185"/>
+      <c r="F44" s="185"/>
+      <c r="G44" s="186"/>
+      <c r="H44" s="178">
         <v>31939.11</v>
       </c>
-      <c r="I44" s="143"/>
-      <c r="J44" s="143"/>
-      <c r="K44" s="143"/>
+      <c r="I44" s="142"/>
+      <c r="J44" s="142"/>
+      <c r="K44" s="142"/>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="232" t="s">
+      <c r="A45" s="187" t="s">
         <v>157</v>
       </c>
-      <c r="B45" s="230"/>
-      <c r="C45" s="230"/>
-      <c r="D45" s="230"/>
-      <c r="E45" s="230"/>
-      <c r="F45" s="230"/>
-      <c r="G45" s="231"/>
-      <c r="H45" s="219">
+      <c r="B45" s="185"/>
+      <c r="C45" s="185"/>
+      <c r="D45" s="185"/>
+      <c r="E45" s="185"/>
+      <c r="F45" s="185"/>
+      <c r="G45" s="186"/>
+      <c r="H45" s="178">
         <v>14500</v>
       </c>
-      <c r="I45" s="143"/>
-      <c r="J45" s="143"/>
-      <c r="K45" s="143"/>
+      <c r="I45" s="142"/>
+      <c r="J45" s="142"/>
+      <c r="K45" s="142"/>
     </row>
     <row r="46" spans="1:11">
-      <c r="A46" s="218" t="s">
+      <c r="A46" s="177" t="s">
         <v>151</v>
       </c>
-      <c r="B46" s="218"/>
-      <c r="C46" s="218"/>
-      <c r="D46" s="218"/>
-      <c r="E46" s="218"/>
-      <c r="F46" s="218"/>
-      <c r="G46" s="218"/>
-      <c r="H46" s="219">
+      <c r="B46" s="177"/>
+      <c r="C46" s="177"/>
+      <c r="D46" s="177"/>
+      <c r="E46" s="177"/>
+      <c r="F46" s="177"/>
+      <c r="G46" s="177"/>
+      <c r="H46" s="178">
         <v>75000</v>
       </c>
-      <c r="I46" s="143"/>
-      <c r="J46" s="143"/>
-      <c r="K46" s="143"/>
+      <c r="I46" s="142"/>
+      <c r="J46" s="142"/>
+      <c r="K46" s="142"/>
     </row>
     <row r="47" spans="1:11">
-      <c r="A47" s="218" t="s">
+      <c r="A47" s="177" t="s">
         <v>158</v>
       </c>
-      <c r="B47" s="218"/>
-      <c r="C47" s="218"/>
-      <c r="D47" s="218"/>
-      <c r="E47" s="218"/>
-      <c r="F47" s="218"/>
-      <c r="G47" s="218"/>
-      <c r="H47" s="219">
+      <c r="B47" s="177"/>
+      <c r="C47" s="177"/>
+      <c r="D47" s="177"/>
+      <c r="E47" s="177"/>
+      <c r="F47" s="177"/>
+      <c r="G47" s="177"/>
+      <c r="H47" s="178">
         <v>200000</v>
       </c>
-      <c r="I47" s="143"/>
-      <c r="J47" s="143"/>
-      <c r="K47" s="143"/>
+      <c r="I47" s="142"/>
+      <c r="J47" s="142"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11">
-      <c r="A48" s="218" t="s">
+      <c r="A48" s="177" t="s">
         <v>159</v>
       </c>
-      <c r="B48" s="218"/>
-      <c r="C48" s="218"/>
-      <c r="D48" s="218"/>
-      <c r="E48" s="218"/>
-      <c r="F48" s="218"/>
-      <c r="G48" s="218"/>
-      <c r="H48" s="219">
+      <c r="B48" s="177"/>
+      <c r="C48" s="177"/>
+      <c r="D48" s="177"/>
+      <c r="E48" s="177"/>
+      <c r="F48" s="177"/>
+      <c r="G48" s="177"/>
+      <c r="H48" s="178">
         <f>120000+55000+23500+41500</f>
         <v>240000</v>
       </c>
-      <c r="I48" s="143"/>
-      <c r="J48" s="143"/>
-      <c r="K48" s="143"/>
+      <c r="I48" s="142"/>
+      <c r="J48" s="142"/>
+      <c r="K48" s="142"/>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="218" t="s">
+      <c r="A49" s="177" t="s">
         <v>73</v>
       </c>
-      <c r="B49" s="218"/>
-      <c r="C49" s="218"/>
-      <c r="D49" s="218"/>
-      <c r="E49" s="218"/>
-      <c r="F49" s="218"/>
-      <c r="G49" s="218"/>
-      <c r="H49" s="220">
+      <c r="B49" s="177"/>
+      <c r="C49" s="177"/>
+      <c r="D49" s="177"/>
+      <c r="E49" s="177"/>
+      <c r="F49" s="177"/>
+      <c r="G49" s="177"/>
+      <c r="H49" s="179">
         <f>SUM(H38:H47)</f>
         <v>1145019.7999999998</v>
       </c>
-      <c r="I49" s="143"/>
-      <c r="J49" s="143"/>
-      <c r="K49" s="143"/>
+      <c r="I49" s="142"/>
+      <c r="J49" s="142"/>
+      <c r="K49" s="142"/>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="227" t="s">
+      <c r="A50" s="225" t="s">
         <v>126</v>
       </c>
-      <c r="B50" s="227"/>
-      <c r="C50" s="227"/>
-      <c r="D50" s="227"/>
-      <c r="E50" s="227"/>
-      <c r="F50" s="227"/>
-      <c r="G50" s="227"/>
-      <c r="H50" s="227"/>
-      <c r="I50" s="143"/>
-      <c r="J50" s="143"/>
-      <c r="K50" s="143"/>
+      <c r="B50" s="225"/>
+      <c r="C50" s="225"/>
+      <c r="D50" s="225"/>
+      <c r="E50" s="225"/>
+      <c r="F50" s="225"/>
+      <c r="G50" s="225"/>
+      <c r="H50" s="225"/>
+      <c r="I50" s="142"/>
+      <c r="J50" s="142"/>
+      <c r="K50" s="142"/>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="228" t="s">
+      <c r="A51" s="183" t="s">
         <v>70</v>
       </c>
-      <c r="B51" s="228"/>
-      <c r="C51" s="228"/>
-      <c r="D51" s="228"/>
-      <c r="E51" s="228"/>
-      <c r="F51" s="228"/>
-      <c r="G51" s="228"/>
-      <c r="H51" s="219">
+      <c r="B51" s="183"/>
+      <c r="C51" s="183"/>
+      <c r="D51" s="183"/>
+      <c r="E51" s="183"/>
+      <c r="F51" s="183"/>
+      <c r="G51" s="183"/>
+      <c r="H51" s="178">
         <v>209000</v>
       </c>
-      <c r="I51" s="143"/>
-      <c r="J51" s="143" t="s">
+      <c r="I51" s="142"/>
+      <c r="J51" s="142" t="s">
         <v>146</v>
       </c>
-      <c r="K51" s="143"/>
+      <c r="K51" s="142"/>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="228" t="s">
+      <c r="A52" s="183" t="s">
         <v>112</v>
       </c>
-      <c r="B52" s="228"/>
-      <c r="C52" s="228"/>
-      <c r="D52" s="228"/>
-      <c r="E52" s="228"/>
-      <c r="F52" s="228"/>
-      <c r="G52" s="228"/>
-      <c r="H52" s="219">
+      <c r="B52" s="183"/>
+      <c r="C52" s="183"/>
+      <c r="D52" s="183"/>
+      <c r="E52" s="183"/>
+      <c r="F52" s="183"/>
+      <c r="G52" s="183"/>
+      <c r="H52" s="178">
         <v>50000</v>
       </c>
-      <c r="I52" s="143"/>
-      <c r="J52" s="143"/>
-      <c r="K52" s="143"/>
+      <c r="I52" s="142"/>
+      <c r="J52" s="142"/>
+      <c r="K52" s="142"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="218" t="s">
+      <c r="A53" s="177" t="s">
         <v>72</v>
       </c>
-      <c r="B53" s="218"/>
-      <c r="C53" s="218"/>
-      <c r="D53" s="218"/>
-      <c r="E53" s="218"/>
-      <c r="F53" s="218"/>
-      <c r="G53" s="218"/>
-      <c r="H53" s="226">
+      <c r="B53" s="177"/>
+      <c r="C53" s="177"/>
+      <c r="D53" s="177"/>
+      <c r="E53" s="177"/>
+      <c r="F53" s="177"/>
+      <c r="G53" s="177"/>
+      <c r="H53" s="182">
         <f>SUM(H51:H52)</f>
         <v>259000</v>
       </c>
-      <c r="I53" s="143"/>
-      <c r="J53" s="143"/>
-      <c r="K53" s="154"/>
+      <c r="I53" s="142"/>
+      <c r="J53" s="142"/>
+      <c r="K53" s="153"/>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
-      <c r="A54" s="233" t="s">
+      <c r="A54" s="226" t="s">
         <v>127</v>
       </c>
-      <c r="B54" s="234"/>
-      <c r="C54" s="234"/>
-      <c r="D54" s="234"/>
-      <c r="E54" s="234"/>
-      <c r="F54" s="234"/>
-      <c r="G54" s="234"/>
-      <c r="H54" s="235"/>
-      <c r="I54" s="159"/>
-      <c r="J54" s="159"/>
-      <c r="K54" s="159"/>
+      <c r="B54" s="227"/>
+      <c r="C54" s="227"/>
+      <c r="D54" s="227"/>
+      <c r="E54" s="227"/>
+      <c r="F54" s="227"/>
+      <c r="G54" s="227"/>
+      <c r="H54" s="228"/>
+      <c r="I54" s="158"/>
+      <c r="J54" s="158"/>
+      <c r="K54" s="158"/>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1">
-      <c r="A55" s="228" t="s">
+      <c r="A55" s="183" t="s">
         <v>114</v>
       </c>
-      <c r="B55" s="228"/>
-      <c r="C55" s="228"/>
-      <c r="D55" s="228"/>
-      <c r="E55" s="228"/>
-      <c r="F55" s="228"/>
-      <c r="G55" s="228"/>
-      <c r="H55" s="219">
+      <c r="B55" s="183"/>
+      <c r="C55" s="183"/>
+      <c r="D55" s="183"/>
+      <c r="E55" s="183"/>
+      <c r="F55" s="183"/>
+      <c r="G55" s="183"/>
+      <c r="H55" s="178">
         <v>28834</v>
       </c>
-      <c r="I55" s="160"/>
-      <c r="J55" s="159"/>
-      <c r="K55" s="159"/>
+      <c r="I55" s="159"/>
+      <c r="J55" s="158"/>
+      <c r="K55" s="158"/>
     </row>
     <row r="56" spans="1:11" s="6" customFormat="1">
-      <c r="A56" s="228" t="s">
+      <c r="A56" s="183" t="s">
         <v>73</v>
       </c>
-      <c r="B56" s="228"/>
-      <c r="C56" s="228"/>
-      <c r="D56" s="228"/>
-      <c r="E56" s="228"/>
-      <c r="F56" s="228"/>
-      <c r="G56" s="228"/>
-      <c r="H56" s="220">
+      <c r="B56" s="183"/>
+      <c r="C56" s="183"/>
+      <c r="D56" s="183"/>
+      <c r="E56" s="183"/>
+      <c r="F56" s="183"/>
+      <c r="G56" s="183"/>
+      <c r="H56" s="179">
         <f>SUM(H55)</f>
         <v>28834</v>
       </c>
-      <c r="I56" s="159"/>
-      <c r="J56" s="159"/>
-      <c r="K56" s="159"/>
+      <c r="I56" s="158"/>
+      <c r="J56" s="158"/>
+      <c r="K56" s="158"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1">
-      <c r="A57" s="227" t="s">
+      <c r="A57" s="225" t="s">
         <v>128</v>
       </c>
-      <c r="B57" s="227"/>
-      <c r="C57" s="227"/>
-      <c r="D57" s="227"/>
-      <c r="E57" s="227"/>
-      <c r="F57" s="227"/>
-      <c r="G57" s="227"/>
-      <c r="H57" s="227"/>
-      <c r="I57" s="159"/>
-      <c r="J57" s="159"/>
-      <c r="K57" s="159"/>
+      <c r="B57" s="225"/>
+      <c r="C57" s="225"/>
+      <c r="D57" s="225"/>
+      <c r="E57" s="225"/>
+      <c r="F57" s="225"/>
+      <c r="G57" s="225"/>
+      <c r="H57" s="225"/>
+      <c r="I57" s="158"/>
+      <c r="J57" s="158"/>
+      <c r="K57" s="158"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1">
-      <c r="A58" s="228" t="s">
+      <c r="A58" s="183" t="s">
         <v>161</v>
       </c>
-      <c r="B58" s="228"/>
-      <c r="C58" s="228"/>
-      <c r="D58" s="228"/>
-      <c r="E58" s="228"/>
-      <c r="F58" s="228"/>
-      <c r="G58" s="228"/>
-      <c r="H58" s="219">
+      <c r="B58" s="183"/>
+      <c r="C58" s="183"/>
+      <c r="D58" s="183"/>
+      <c r="E58" s="183"/>
+      <c r="F58" s="183"/>
+      <c r="G58" s="183"/>
+      <c r="H58" s="178">
         <v>160000</v>
       </c>
-      <c r="I58" s="159"/>
-      <c r="J58" s="159"/>
-      <c r="K58" s="159"/>
-    </row>
-    <row r="59" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
-      <c r="A59" s="228" t="s">
+      <c r="I58" s="158"/>
+      <c r="J58" s="158"/>
+      <c r="K58" s="158"/>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1">
+      <c r="A59" s="183" t="s">
+        <v>163</v>
+      </c>
+      <c r="B59" s="183"/>
+      <c r="C59" s="183"/>
+      <c r="D59" s="183"/>
+      <c r="E59" s="183"/>
+      <c r="F59" s="183"/>
+      <c r="G59" s="183"/>
+      <c r="H59" s="178">
+        <v>2591824.4500000002</v>
+      </c>
+      <c r="I59" s="158"/>
+      <c r="J59" s="158"/>
+      <c r="K59" s="158"/>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A60" s="183" t="s">
         <v>74</v>
       </c>
-      <c r="B59" s="228"/>
-      <c r="C59" s="228"/>
-      <c r="D59" s="228"/>
-      <c r="E59" s="228"/>
-      <c r="F59" s="228"/>
-      <c r="G59" s="228"/>
-      <c r="H59" s="220">
-        <f>SUM(H58:H58)</f>
-        <v>160000</v>
-      </c>
-      <c r="I59" s="160"/>
-      <c r="J59" s="159"/>
-      <c r="K59" s="159"/>
-    </row>
-    <row r="60" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A60" s="233"/>
-      <c r="B60" s="234"/>
-      <c r="C60" s="234"/>
-      <c r="D60" s="234"/>
-      <c r="E60" s="234"/>
-      <c r="F60" s="234"/>
-      <c r="G60" s="234"/>
-      <c r="H60" s="235"/>
+      <c r="B60" s="183"/>
+      <c r="C60" s="183"/>
+      <c r="D60" s="183"/>
+      <c r="E60" s="183"/>
+      <c r="F60" s="183"/>
+      <c r="G60" s="183"/>
+      <c r="H60" s="179">
+        <f>SUM(H58:H59)</f>
+        <v>2751824.45</v>
+      </c>
       <c r="I60" s="159"/>
-      <c r="J60" s="159"/>
-      <c r="K60" s="159"/>
-    </row>
-    <row r="61" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A61" s="229"/>
-      <c r="B61" s="230"/>
-      <c r="C61" s="230"/>
-      <c r="D61" s="230"/>
-      <c r="E61" s="230"/>
-      <c r="F61" s="230"/>
-      <c r="G61" s="230"/>
-      <c r="H61" s="236">
-        <v>0</v>
-      </c>
-      <c r="I61" s="159"/>
-      <c r="J61" s="159"/>
-      <c r="K61" s="159"/>
-    </row>
-    <row r="62" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A62" s="237"/>
-      <c r="B62" s="238"/>
-      <c r="C62" s="238"/>
-      <c r="D62" s="238"/>
-      <c r="E62" s="238"/>
-      <c r="F62" s="238"/>
-      <c r="G62" s="238"/>
-      <c r="H62" s="239">
-        <v>0</v>
-      </c>
-      <c r="I62" s="159"/>
-      <c r="J62" s="159"/>
-      <c r="K62" s="159"/>
-    </row>
-    <row r="63" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A63" s="232"/>
-      <c r="B63" s="240"/>
-      <c r="C63" s="240"/>
-      <c r="D63" s="240"/>
-      <c r="E63" s="240"/>
-      <c r="F63" s="240"/>
-      <c r="G63" s="240"/>
-      <c r="H63" s="236">
-        <f>H61+H62</f>
-        <v>0</v>
-      </c>
-      <c r="I63" s="159"/>
-      <c r="J63" s="159"/>
-      <c r="K63" s="159"/>
+      <c r="J60" s="158"/>
+      <c r="K60" s="158"/>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A61" s="226"/>
+      <c r="B61" s="227"/>
+      <c r="C61" s="227"/>
+      <c r="D61" s="227"/>
+      <c r="E61" s="227"/>
+      <c r="F61" s="227"/>
+      <c r="G61" s="227"/>
+      <c r="H61" s="228"/>
+      <c r="I61" s="158"/>
+      <c r="J61" s="158"/>
+      <c r="K61" s="158"/>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A62" s="184"/>
+      <c r="B62" s="185"/>
+      <c r="C62" s="185"/>
+      <c r="D62" s="185"/>
+      <c r="E62" s="185"/>
+      <c r="F62" s="185"/>
+      <c r="G62" s="185"/>
+      <c r="H62" s="188">
+        <v>0</v>
+      </c>
+      <c r="I62" s="158"/>
+      <c r="J62" s="158"/>
+      <c r="K62" s="158"/>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A63" s="189"/>
+      <c r="B63" s="190"/>
+      <c r="C63" s="190"/>
+      <c r="D63" s="190"/>
+      <c r="E63" s="190"/>
+      <c r="F63" s="190"/>
+      <c r="G63" s="190"/>
+      <c r="H63" s="191">
+        <v>0</v>
+      </c>
+      <c r="I63" s="158"/>
+      <c r="J63" s="158"/>
+      <c r="K63" s="158"/>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A64" s="241" t="s">
+      <c r="A64" s="187"/>
+      <c r="B64" s="192"/>
+      <c r="C64" s="192"/>
+      <c r="D64" s="192"/>
+      <c r="E64" s="192"/>
+      <c r="F64" s="192"/>
+      <c r="G64" s="192"/>
+      <c r="H64" s="188">
+        <f>H62+H63</f>
+        <v>0</v>
+      </c>
+      <c r="I64" s="158"/>
+      <c r="J64" s="158"/>
+      <c r="K64" s="158"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A65" s="230" t="s">
         <v>79</v>
       </c>
-      <c r="B64" s="242"/>
-      <c r="C64" s="242"/>
-      <c r="D64" s="242"/>
-      <c r="E64" s="242"/>
-      <c r="F64" s="242"/>
-      <c r="G64" s="242"/>
-      <c r="H64" s="243">
-        <f>H59</f>
-        <v>160000</v>
-      </c>
-      <c r="I64" s="159"/>
-      <c r="J64" s="159"/>
-      <c r="K64" s="159"/>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A65" s="244"/>
-      <c r="B65" s="244"/>
-      <c r="C65" s="244"/>
-      <c r="D65" s="244"/>
-      <c r="E65" s="244"/>
-      <c r="F65" s="244"/>
-      <c r="G65" s="244"/>
-      <c r="H65" s="244"/>
-      <c r="I65" s="159"/>
-      <c r="J65" s="159"/>
-      <c r="K65" s="159"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A66" s="245"/>
-      <c r="B66" s="245"/>
-      <c r="C66" s="245"/>
-      <c r="D66" s="245"/>
-      <c r="E66" s="245"/>
-      <c r="F66" s="245"/>
-      <c r="G66" s="245"/>
-      <c r="H66" s="245"/>
-      <c r="I66" s="159"/>
-      <c r="J66" s="159"/>
-      <c r="K66" s="159"/>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A67" s="246" t="s">
+      <c r="B65" s="231"/>
+      <c r="C65" s="231"/>
+      <c r="D65" s="231"/>
+      <c r="E65" s="231"/>
+      <c r="F65" s="231"/>
+      <c r="G65" s="231"/>
+      <c r="H65" s="193">
+        <f>H60</f>
+        <v>2751824.45</v>
+      </c>
+      <c r="I65" s="158"/>
+      <c r="J65" s="158"/>
+      <c r="K65" s="158"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="233"/>
+      <c r="B66" s="233"/>
+      <c r="C66" s="233"/>
+      <c r="D66" s="233"/>
+      <c r="E66" s="233"/>
+      <c r="F66" s="233"/>
+      <c r="G66" s="233"/>
+      <c r="H66" s="233"/>
+      <c r="I66" s="158"/>
+      <c r="J66" s="158"/>
+      <c r="K66" s="158"/>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A67" s="234"/>
+      <c r="B67" s="234"/>
+      <c r="C67" s="234"/>
+      <c r="D67" s="234"/>
+      <c r="E67" s="234"/>
+      <c r="F67" s="234"/>
+      <c r="G67" s="234"/>
+      <c r="H67" s="234"/>
+      <c r="I67" s="158"/>
+      <c r="J67" s="158"/>
+      <c r="K67" s="158"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A68" s="232" t="s">
         <v>81</v>
       </c>
-      <c r="B67" s="246"/>
-      <c r="C67" s="246"/>
-      <c r="D67" s="246"/>
-      <c r="E67" s="246"/>
-      <c r="F67" s="246"/>
-      <c r="G67" s="246"/>
-      <c r="H67" s="247"/>
-      <c r="I67" s="159"/>
-      <c r="J67" s="159"/>
-      <c r="K67" s="159"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
-      <c r="A68" s="248" t="s">
+      <c r="B68" s="232"/>
+      <c r="C68" s="232"/>
+      <c r="D68" s="232"/>
+      <c r="E68" s="232"/>
+      <c r="F68" s="232"/>
+      <c r="G68" s="232"/>
+      <c r="H68" s="194"/>
+      <c r="I68" s="158"/>
+      <c r="J68" s="158"/>
+      <c r="K68" s="158"/>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18.75" customHeight="1">
+      <c r="A69" s="235" t="s">
         <v>145</v>
       </c>
-      <c r="B68" s="249"/>
-      <c r="C68" s="249"/>
-      <c r="D68" s="249"/>
-      <c r="E68" s="249"/>
-      <c r="F68" s="249"/>
-      <c r="G68" s="250"/>
-      <c r="H68" s="219">
+      <c r="B69" s="236"/>
+      <c r="C69" s="236"/>
+      <c r="D69" s="236"/>
+      <c r="E69" s="236"/>
+      <c r="F69" s="236"/>
+      <c r="G69" s="237"/>
+      <c r="H69" s="178">
         <f>108397.71+759533.45</f>
         <v>867931.15999999992</v>
       </c>
-      <c r="I68" s="159"/>
-      <c r="J68" s="159"/>
-      <c r="K68" s="159"/>
-    </row>
-    <row r="69" spans="1:11" s="6" customFormat="1">
-      <c r="A69" s="161" t="s">
+      <c r="I69" s="158"/>
+      <c r="J69" s="158"/>
+      <c r="K69" s="158"/>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1">
+      <c r="A70" s="160" t="s">
         <v>73</v>
       </c>
-      <c r="B69" s="156"/>
-      <c r="C69" s="156"/>
-      <c r="D69" s="156"/>
-      <c r="E69" s="156"/>
-      <c r="F69" s="156"/>
-      <c r="G69" s="156"/>
-      <c r="H69" s="155">
-        <f>SUM(H68)</f>
+      <c r="B70" s="155"/>
+      <c r="C70" s="155"/>
+      <c r="D70" s="155"/>
+      <c r="E70" s="155"/>
+      <c r="F70" s="155"/>
+      <c r="G70" s="155"/>
+      <c r="H70" s="154">
+        <f>SUM(H69)</f>
         <v>867931.15999999992</v>
       </c>
-      <c r="I69" s="159"/>
-      <c r="J69" s="159"/>
-      <c r="K69" s="159"/>
-    </row>
-    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="159"/>
-      <c r="B70" s="159"/>
-      <c r="C70" s="159"/>
-      <c r="D70" s="159"/>
-      <c r="E70" s="159"/>
-      <c r="F70" s="159"/>
-      <c r="G70" s="159"/>
-      <c r="H70" s="162"/>
-      <c r="I70" s="159"/>
-      <c r="J70" s="159"/>
-      <c r="K70" s="159"/>
+      <c r="I70" s="158"/>
+      <c r="J70" s="158"/>
+      <c r="K70" s="158"/>
     </row>
     <row r="71" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A71" s="183" t="s">
+      <c r="A71" s="158"/>
+      <c r="B71" s="158"/>
+      <c r="C71" s="158"/>
+      <c r="D71" s="158"/>
+      <c r="E71" s="158"/>
+      <c r="F71" s="158"/>
+      <c r="G71" s="158"/>
+      <c r="H71" s="161"/>
+      <c r="I71" s="158"/>
+      <c r="J71" s="158"/>
+      <c r="K71" s="158"/>
+    </row>
+    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A72" s="202" t="s">
         <v>80</v>
       </c>
-      <c r="B71" s="184"/>
-      <c r="C71" s="184"/>
-      <c r="D71" s="184"/>
-      <c r="E71" s="184"/>
-      <c r="F71" s="184"/>
-      <c r="G71" s="184"/>
-      <c r="H71" s="163">
-        <f>H69</f>
+      <c r="B72" s="203"/>
+      <c r="C72" s="203"/>
+      <c r="D72" s="203"/>
+      <c r="E72" s="203"/>
+      <c r="F72" s="203"/>
+      <c r="G72" s="203"/>
+      <c r="H72" s="162">
+        <f>H70</f>
         <v>867931.15999999992</v>
       </c>
-      <c r="I71" s="159"/>
-      <c r="J71" s="159"/>
-      <c r="K71" s="159"/>
-    </row>
-    <row r="72" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A72" s="198" t="s">
+      <c r="I72" s="158"/>
+      <c r="J72" s="158"/>
+      <c r="K72" s="158"/>
+    </row>
+    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A73" s="218" t="s">
         <v>86</v>
       </c>
-      <c r="B72" s="199"/>
-      <c r="C72" s="199"/>
-      <c r="D72" s="199"/>
-      <c r="E72" s="199"/>
-      <c r="F72" s="199"/>
-      <c r="G72" s="200"/>
-      <c r="H72" s="163">
-        <v>0</v>
-      </c>
-      <c r="I72" s="159"/>
-      <c r="J72" s="159"/>
-      <c r="K72" s="159"/>
-    </row>
-    <row r="73" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A73" s="198" t="s">
+      <c r="B73" s="219"/>
+      <c r="C73" s="219"/>
+      <c r="D73" s="219"/>
+      <c r="E73" s="219"/>
+      <c r="F73" s="219"/>
+      <c r="G73" s="220"/>
+      <c r="H73" s="162">
+        <v>0</v>
+      </c>
+      <c r="I73" s="158"/>
+      <c r="J73" s="158"/>
+      <c r="K73" s="158"/>
+    </row>
+    <row r="74" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A74" s="218" t="s">
         <v>91</v>
       </c>
-      <c r="B73" s="199"/>
-      <c r="C73" s="199"/>
-      <c r="D73" s="199"/>
-      <c r="E73" s="199"/>
-      <c r="F73" s="199"/>
-      <c r="G73" s="200"/>
-      <c r="H73" s="163"/>
-      <c r="I73" s="159"/>
-      <c r="J73" s="159"/>
-      <c r="K73" s="159"/>
-    </row>
-    <row r="74" spans="1:11" ht="18.75">
-      <c r="A74" s="183" t="s">
+      <c r="B74" s="219"/>
+      <c r="C74" s="219"/>
+      <c r="D74" s="219"/>
+      <c r="E74" s="219"/>
+      <c r="F74" s="219"/>
+      <c r="G74" s="220"/>
+      <c r="H74" s="162"/>
+      <c r="I74" s="158"/>
+      <c r="J74" s="158"/>
+      <c r="K74" s="158"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75">
+      <c r="A75" s="202" t="s">
         <v>87</v>
       </c>
-      <c r="B74" s="184"/>
-      <c r="C74" s="184"/>
-      <c r="D74" s="184"/>
-      <c r="E74" s="184"/>
-      <c r="F74" s="184"/>
-      <c r="G74" s="184"/>
-      <c r="H74" s="163">
+      <c r="B75" s="203"/>
+      <c r="C75" s="203"/>
+      <c r="D75" s="203"/>
+      <c r="E75" s="203"/>
+      <c r="F75" s="203"/>
+      <c r="G75" s="203"/>
+      <c r="H75" s="162">
         <f>H26+H36+H49+H53+H56+H31+H18+H22</f>
         <v>3764715.15</v>
       </c>
-      <c r="I74" s="143"/>
-      <c r="J74" s="164"/>
-      <c r="K74" s="165"/>
-    </row>
-    <row r="75" spans="1:11" ht="18.75">
-      <c r="A75" s="189" t="s">
+      <c r="I75" s="142"/>
+      <c r="J75" s="163"/>
+      <c r="K75" s="164"/>
+    </row>
+    <row r="76" spans="1:11" ht="18.75">
+      <c r="A76" s="208" t="s">
         <v>117</v>
       </c>
-      <c r="B75" s="190"/>
-      <c r="C75" s="190"/>
-      <c r="D75" s="190"/>
-      <c r="E75" s="190"/>
-      <c r="F75" s="190"/>
-      <c r="G75" s="191"/>
-      <c r="H75" s="166">
-        <f>H72+H74</f>
+      <c r="B76" s="209"/>
+      <c r="C76" s="209"/>
+      <c r="D76" s="209"/>
+      <c r="E76" s="209"/>
+      <c r="F76" s="209"/>
+      <c r="G76" s="210"/>
+      <c r="H76" s="165">
+        <f>H73+H75</f>
         <v>3764715.15</v>
       </c>
-      <c r="I75" s="110"/>
-      <c r="J75" s="197"/>
-      <c r="K75" s="197"/>
-    </row>
-    <row r="76" spans="1:11" ht="18.75">
-      <c r="A76" s="189" t="s">
+      <c r="I76" s="110"/>
+      <c r="J76" s="217"/>
+      <c r="K76" s="217"/>
+    </row>
+    <row r="77" spans="1:11" ht="18.75">
+      <c r="A77" s="208" t="s">
         <v>92</v>
       </c>
-      <c r="B76" s="190"/>
-      <c r="C76" s="190"/>
-      <c r="D76" s="190"/>
-      <c r="E76" s="190"/>
-      <c r="F76" s="190"/>
-      <c r="G76" s="191"/>
-      <c r="H76" s="167">
-        <f>H73+H71</f>
+      <c r="B77" s="209"/>
+      <c r="C77" s="209"/>
+      <c r="D77" s="209"/>
+      <c r="E77" s="209"/>
+      <c r="F77" s="209"/>
+      <c r="G77" s="210"/>
+      <c r="H77" s="166">
+        <f>H74+H72</f>
         <v>867931.15999999992</v>
       </c>
-      <c r="I76" s="143"/>
-      <c r="J76" s="165"/>
-      <c r="K76" s="143"/>
-    </row>
-    <row r="77" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A77" s="187" t="s">
+      <c r="I77" s="142"/>
+      <c r="J77" s="164"/>
+      <c r="K77" s="142"/>
+    </row>
+    <row r="78" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A78" s="206" t="s">
         <v>82</v>
       </c>
-      <c r="B77" s="188"/>
-      <c r="C77" s="188"/>
-      <c r="D77" s="188"/>
-      <c r="E77" s="188"/>
-      <c r="F77" s="188"/>
-      <c r="G77" s="188"/>
-      <c r="H77" s="168">
-        <f>H74+H71</f>
+      <c r="B78" s="207"/>
+      <c r="C78" s="207"/>
+      <c r="D78" s="207"/>
+      <c r="E78" s="207"/>
+      <c r="F78" s="207"/>
+      <c r="G78" s="207"/>
+      <c r="H78" s="167">
+        <f>H75+H72</f>
         <v>4632646.3099999996</v>
       </c>
-      <c r="I77" s="143"/>
-      <c r="J77" s="154"/>
-      <c r="K77" s="143"/>
-    </row>
-    <row r="78" spans="1:11" ht="18.75" hidden="1">
-      <c r="A78" s="185" t="s">
+      <c r="I78" s="142"/>
+      <c r="J78" s="153"/>
+      <c r="K78" s="142"/>
+    </row>
+    <row r="79" spans="1:11" ht="18.75" hidden="1">
+      <c r="A79" s="204" t="s">
         <v>17</v>
       </c>
-      <c r="B78" s="186"/>
-      <c r="C78" s="186"/>
-      <c r="D78" s="186"/>
-      <c r="E78" s="186"/>
-      <c r="F78" s="186"/>
-      <c r="G78" s="186"/>
-      <c r="H78" s="169">
-        <f>H63</f>
-        <v>0</v>
-      </c>
-      <c r="I78" s="143"/>
-      <c r="J78" s="154"/>
-      <c r="K78" s="143"/>
-    </row>
-    <row r="79" spans="1:11" ht="18.75" hidden="1">
-      <c r="A79" s="170"/>
-      <c r="B79" s="170"/>
-      <c r="C79" s="170"/>
-      <c r="D79" s="170"/>
-      <c r="E79" s="170"/>
-      <c r="F79" s="170"/>
-      <c r="G79" s="170"/>
-      <c r="H79" s="171"/>
-      <c r="I79" s="143"/>
-      <c r="J79" s="154"/>
-      <c r="K79" s="143"/>
+      <c r="B79" s="205"/>
+      <c r="C79" s="205"/>
+      <c r="D79" s="205"/>
+      <c r="E79" s="205"/>
+      <c r="F79" s="205"/>
+      <c r="G79" s="205"/>
+      <c r="H79" s="168">
+        <f>H64</f>
+        <v>0</v>
+      </c>
+      <c r="I79" s="142"/>
+      <c r="J79" s="153"/>
+      <c r="K79" s="142"/>
     </row>
     <row r="80" spans="1:11" ht="18.75" hidden="1">
-      <c r="A80" s="170"/>
-      <c r="B80" s="170"/>
-      <c r="C80" s="170"/>
-      <c r="D80" s="170"/>
-      <c r="E80" s="170"/>
-      <c r="F80" s="170"/>
-      <c r="G80" s="170"/>
-      <c r="H80" s="171"/>
-      <c r="I80" s="143"/>
-      <c r="J80" s="154"/>
-      <c r="K80" s="143"/>
+      <c r="A80" s="169"/>
+      <c r="B80" s="169"/>
+      <c r="C80" s="169"/>
+      <c r="D80" s="169"/>
+      <c r="E80" s="169"/>
+      <c r="F80" s="169"/>
+      <c r="G80" s="169"/>
+      <c r="H80" s="170"/>
+      <c r="I80" s="142"/>
+      <c r="J80" s="153"/>
+      <c r="K80" s="142"/>
     </row>
     <row r="81" spans="1:11" ht="18.75" hidden="1">
-      <c r="A81" s="170"/>
-      <c r="B81" s="170"/>
-      <c r="C81" s="170"/>
-      <c r="D81" s="170"/>
-      <c r="E81" s="170"/>
-      <c r="F81" s="170"/>
-      <c r="G81" s="170"/>
-      <c r="H81" s="171"/>
-      <c r="I81" s="143"/>
-      <c r="J81" s="154"/>
-      <c r="K81" s="143"/>
-    </row>
-    <row r="82" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A82" s="153"/>
-      <c r="B82" s="153"/>
-      <c r="C82" s="153"/>
-      <c r="D82" s="153"/>
-      <c r="E82" s="153"/>
-      <c r="F82" s="153"/>
-      <c r="G82" s="153"/>
-      <c r="H82" s="153"/>
-      <c r="I82" s="143"/>
-      <c r="J82" s="143"/>
-      <c r="K82" s="143"/>
-    </row>
-    <row r="83" spans="1:11" ht="18.75">
-      <c r="A83" s="180" t="s">
+      <c r="A81" s="169"/>
+      <c r="B81" s="169"/>
+      <c r="C81" s="169"/>
+      <c r="D81" s="169"/>
+      <c r="E81" s="169"/>
+      <c r="F81" s="169"/>
+      <c r="G81" s="169"/>
+      <c r="H81" s="170"/>
+      <c r="I81" s="142"/>
+      <c r="J81" s="153"/>
+      <c r="K81" s="142"/>
+    </row>
+    <row r="82" spans="1:11" ht="18.75" hidden="1">
+      <c r="A82" s="169"/>
+      <c r="B82" s="169"/>
+      <c r="C82" s="169"/>
+      <c r="D82" s="169"/>
+      <c r="E82" s="169"/>
+      <c r="F82" s="169"/>
+      <c r="G82" s="169"/>
+      <c r="H82" s="170"/>
+      <c r="I82" s="142"/>
+      <c r="J82" s="153"/>
+      <c r="K82" s="142"/>
+    </row>
+    <row r="83" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A83" s="152"/>
+      <c r="B83" s="152"/>
+      <c r="C83" s="152"/>
+      <c r="D83" s="152"/>
+      <c r="E83" s="152"/>
+      <c r="F83" s="152"/>
+      <c r="G83" s="152"/>
+      <c r="H83" s="152"/>
+      <c r="I83" s="142"/>
+      <c r="J83" s="142"/>
+      <c r="K83" s="142"/>
+    </row>
+    <row r="84" spans="1:11" ht="18.75">
+      <c r="A84" s="199" t="s">
         <v>10</v>
       </c>
-      <c r="B83" s="181"/>
-      <c r="C83" s="181"/>
-      <c r="D83" s="181"/>
-      <c r="E83" s="181"/>
-      <c r="F83" s="181"/>
-      <c r="G83" s="181"/>
-      <c r="H83" s="182"/>
-      <c r="I83" s="143"/>
-      <c r="J83" s="143"/>
-      <c r="K83" s="143"/>
-    </row>
-    <row r="84" spans="1:11" ht="18.75">
-      <c r="A84" s="172" t="s">
+      <c r="B84" s="200"/>
+      <c r="C84" s="200"/>
+      <c r="D84" s="200"/>
+      <c r="E84" s="200"/>
+      <c r="F84" s="200"/>
+      <c r="G84" s="200"/>
+      <c r="H84" s="201"/>
+      <c r="I84" s="142"/>
+      <c r="J84" s="142"/>
+      <c r="K84" s="142"/>
+    </row>
+    <row r="85" spans="1:11" ht="18.75">
+      <c r="A85" s="171" t="s">
         <v>12</v>
       </c>
-      <c r="B84" s="173"/>
-      <c r="C84" s="173"/>
-      <c r="D84" s="173"/>
-      <c r="E84" s="173"/>
-      <c r="F84" s="173"/>
-      <c r="G84" s="173"/>
-      <c r="H84" s="174">
+      <c r="B85" s="172"/>
+      <c r="C85" s="172"/>
+      <c r="D85" s="172"/>
+      <c r="E85" s="172"/>
+      <c r="F85" s="172"/>
+      <c r="G85" s="172"/>
+      <c r="H85" s="173">
         <v>4157321.54</v>
       </c>
-      <c r="I84" s="143"/>
-      <c r="J84" s="143"/>
-      <c r="K84" s="143"/>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" s="157" t="s">
+      <c r="I85" s="142"/>
+      <c r="J85" s="142"/>
+      <c r="K85" s="142"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="156" t="s">
         <v>141</v>
       </c>
-      <c r="B85" s="158"/>
-      <c r="C85" s="158"/>
-      <c r="D85" s="158"/>
-      <c r="E85" s="158"/>
-      <c r="F85" s="158"/>
-      <c r="G85" s="158"/>
-      <c r="H85" s="18">
+      <c r="B86" s="157"/>
+      <c r="C86" s="157"/>
+      <c r="D86" s="157"/>
+      <c r="E86" s="157"/>
+      <c r="F86" s="157"/>
+      <c r="G86" s="157"/>
+      <c r="H86" s="18">
         <f>Planilla!G32</f>
         <v>2271965.5230871504</v>
       </c>
-      <c r="I85" s="143"/>
-      <c r="J85" s="143"/>
-      <c r="K85" s="143"/>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" s="150" t="s">
+      <c r="I86" s="142"/>
+      <c r="J86" s="142"/>
+      <c r="K86" s="142"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="149" t="s">
         <v>152</v>
       </c>
-      <c r="B86" s="151"/>
-      <c r="C86" s="151"/>
-      <c r="D86" s="151"/>
-      <c r="E86" s="151"/>
-      <c r="F86" s="151"/>
-      <c r="G86" s="151"/>
-      <c r="H86" s="14">
-        <f>-(H77)</f>
+      <c r="B87" s="150"/>
+      <c r="C87" s="150"/>
+      <c r="D87" s="150"/>
+      <c r="E87" s="150"/>
+      <c r="F87" s="150"/>
+      <c r="G87" s="150"/>
+      <c r="H87" s="14">
+        <f>-(H78)</f>
         <v>-4632646.3099999996</v>
       </c>
-      <c r="I86" s="143"/>
-      <c r="J86" s="143"/>
-      <c r="K86" s="143"/>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" s="150" t="s">
+      <c r="I87" s="142"/>
+      <c r="J87" s="142"/>
+      <c r="K87" s="142"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="149" t="s">
         <v>83</v>
       </c>
-      <c r="B87" s="151"/>
-      <c r="C87" s="151"/>
-      <c r="D87" s="151"/>
-      <c r="E87" s="151"/>
-      <c r="F87" s="151"/>
-      <c r="G87" s="151"/>
-      <c r="H87" s="14">
-        <f>-H64</f>
-        <v>-160000</v>
-      </c>
-      <c r="I87" s="143"/>
-      <c r="J87" s="143"/>
-      <c r="K87" s="159"/>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" s="150" t="s">
+      <c r="B88" s="150"/>
+      <c r="C88" s="150"/>
+      <c r="D88" s="150"/>
+      <c r="E88" s="150"/>
+      <c r="F88" s="150"/>
+      <c r="G88" s="150"/>
+      <c r="H88" s="14">
+        <f>-H65</f>
+        <v>-2751824.45</v>
+      </c>
+      <c r="I88" s="142"/>
+      <c r="J88" s="142"/>
+      <c r="K88" s="158"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="149" t="s">
         <v>140</v>
       </c>
-      <c r="B88" s="151"/>
-      <c r="C88" s="151"/>
-      <c r="D88" s="151"/>
-      <c r="E88" s="151"/>
-      <c r="F88" s="151"/>
-      <c r="G88" s="151"/>
-      <c r="H88" s="84">
-        <f>217300-H89</f>
+      <c r="B89" s="150"/>
+      <c r="C89" s="150"/>
+      <c r="D89" s="150"/>
+      <c r="E89" s="150"/>
+      <c r="F89" s="150"/>
+      <c r="G89" s="150"/>
+      <c r="H89" s="84">
+        <f>217300-H90</f>
         <v>154086</v>
       </c>
-      <c r="I88" s="143"/>
-      <c r="J88" s="154"/>
-      <c r="K88" s="143"/>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" s="150" t="s">
+      <c r="I89" s="142"/>
+      <c r="J89" s="153"/>
+      <c r="K89" s="142"/>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" s="149" t="s">
         <v>71</v>
       </c>
-      <c r="B89" s="151"/>
-      <c r="C89" s="151"/>
-      <c r="D89" s="151"/>
-      <c r="E89" s="151"/>
-      <c r="F89" s="151"/>
-      <c r="G89" s="151"/>
-      <c r="H89" s="84">
+      <c r="B90" s="150"/>
+      <c r="C90" s="150"/>
+      <c r="D90" s="150"/>
+      <c r="E90" s="150"/>
+      <c r="F90" s="150"/>
+      <c r="G90" s="150"/>
+      <c r="H90" s="84">
         <v>63214</v>
       </c>
-      <c r="I89" s="165"/>
-      <c r="J89" s="154"/>
-      <c r="K89" s="143"/>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="150" t="s">
+      <c r="I90" s="164"/>
+      <c r="J90" s="153"/>
+      <c r="K90" s="142"/>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" s="149" t="s">
         <v>115</v>
       </c>
-      <c r="B90" s="175"/>
-      <c r="C90" s="151"/>
-      <c r="D90" s="151"/>
-      <c r="E90" s="151"/>
-      <c r="F90" s="151"/>
-      <c r="G90" s="151"/>
-      <c r="H90" s="84"/>
-      <c r="I90" s="143"/>
-      <c r="J90" s="143"/>
-      <c r="K90" s="143"/>
-    </row>
-    <row r="91" spans="1:11" ht="18.75">
-      <c r="A91" s="19" t="s">
+      <c r="B91" s="174"/>
+      <c r="C91" s="150"/>
+      <c r="D91" s="150"/>
+      <c r="E91" s="150"/>
+      <c r="F91" s="150"/>
+      <c r="G91" s="150"/>
+      <c r="H91" s="84"/>
+      <c r="I91" s="142"/>
+      <c r="J91" s="142"/>
+      <c r="K91" s="142"/>
+    </row>
+    <row r="92" spans="1:11" ht="18.75">
+      <c r="A92" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B91" s="20"/>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20"/>
-      <c r="E91" s="20"/>
-      <c r="F91" s="20"/>
-      <c r="G91" s="20"/>
-      <c r="H91" s="70">
-        <f>SUM(H84:H90)</f>
-        <v>1853940.7530871509</v>
-      </c>
-      <c r="I91" s="143"/>
-      <c r="J91" s="143"/>
-      <c r="K91" s="143"/>
-    </row>
-    <row r="92" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="93" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A93" s="177" t="s">
+      <c r="B92" s="20"/>
+      <c r="C92" s="20"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+      <c r="F92" s="20"/>
+      <c r="G92" s="20"/>
+      <c r="H92" s="70">
+        <f>SUM(H85:H91)</f>
+        <v>-737883.69691284932</v>
+      </c>
+      <c r="I92" s="142"/>
+      <c r="J92" s="142"/>
+      <c r="K92" s="142"/>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" s="250" t="s">
+        <v>164</v>
+      </c>
+      <c r="B93" s="250"/>
+      <c r="C93" s="250"/>
+      <c r="D93" s="250"/>
+      <c r="E93" s="250"/>
+      <c r="F93" s="250"/>
+      <c r="G93" s="250"/>
+      <c r="H93" s="250"/>
+    </row>
+    <row r="94" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A94" s="251"/>
+      <c r="B94" s="251"/>
+      <c r="C94" s="251"/>
+      <c r="D94" s="251"/>
+      <c r="E94" s="251"/>
+      <c r="F94" s="251"/>
+      <c r="G94" s="251"/>
+      <c r="H94" s="251"/>
+    </row>
+    <row r="95" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A95" s="196" t="s">
         <v>96</v>
       </c>
-      <c r="B93" s="178"/>
-      <c r="C93" s="178"/>
-      <c r="D93" s="178"/>
-      <c r="E93" s="178"/>
-      <c r="F93" s="178"/>
-      <c r="G93" s="178"/>
-      <c r="H93" s="179"/>
-    </row>
-    <row r="94" spans="1:11" ht="15.75">
-      <c r="A94" s="73" t="s">
+      <c r="B95" s="197"/>
+      <c r="C95" s="197"/>
+      <c r="D95" s="197"/>
+      <c r="E95" s="197"/>
+      <c r="F95" s="197"/>
+      <c r="G95" s="197"/>
+      <c r="H95" s="198"/>
+    </row>
+    <row r="96" spans="1:11" ht="15.75">
+      <c r="A96" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B94" s="73"/>
-      <c r="C94" s="73"/>
-      <c r="D94" s="73"/>
-      <c r="E94" s="73"/>
-      <c r="F94" s="73"/>
-      <c r="G94" s="73"/>
-      <c r="H94" s="74">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" s="55" t="s">
+      <c r="B96" s="73"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="73"/>
+      <c r="E96" s="73"/>
+      <c r="F96" s="73"/>
+      <c r="G96" s="73"/>
+      <c r="H96" s="74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" s="55" t="s">
         <v>116</v>
       </c>
-      <c r="B95" s="77"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="55"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="55"/>
-      <c r="G95" s="55"/>
-      <c r="H95" s="109"/>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" s="55"/>
-      <c r="B96" s="83"/>
-      <c r="C96" s="55"/>
-      <c r="D96" s="55"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="55"/>
-      <c r="G96" s="55"/>
-      <c r="H96" s="18"/>
-    </row>
-    <row r="97" spans="1:8">
-      <c r="A97" s="55"/>
-      <c r="B97" s="55"/>
-      <c r="C97" s="55"/>
+      <c r="B97" s="77"/>
+      <c r="C97" s="4"/>
       <c r="D97" s="55"/>
       <c r="E97" s="55"/>
       <c r="F97" s="55"/>
       <c r="G97" s="55"/>
-      <c r="H97" s="18"/>
+      <c r="H97" s="109"/>
     </row>
     <row r="98" spans="1:8">
-      <c r="A98" s="71" t="s">
+      <c r="A98" s="55"/>
+      <c r="B98" s="83"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="18"/>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" s="55"/>
+      <c r="B99" s="55"/>
+      <c r="C99" s="55"/>
+      <c r="D99" s="55"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="55"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="18"/>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="B98" s="71"/>
-      <c r="C98" s="71"/>
-      <c r="D98" s="71"/>
-      <c r="E98" s="71"/>
-      <c r="F98" s="71"/>
-      <c r="G98" s="71"/>
-      <c r="H98" s="72">
-        <f>SUM(H94:H97)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="176"/>
-      <c r="B101" s="176"/>
-      <c r="C101" s="176"/>
-      <c r="D101" s="176"/>
-      <c r="E101" s="176"/>
-      <c r="F101" s="176"/>
-      <c r="G101" s="176"/>
-      <c r="H101" s="176"/>
-    </row>
-    <row r="102" spans="1:8" hidden="1">
-      <c r="A102" s="176"/>
-      <c r="B102" s="176"/>
-      <c r="C102" s="176"/>
-      <c r="D102" s="176"/>
-      <c r="E102" s="176"/>
-      <c r="F102" s="176"/>
-      <c r="G102" s="176"/>
-      <c r="H102" s="176"/>
+      <c r="B100" s="71"/>
+      <c r="C100" s="71"/>
+      <c r="D100" s="71"/>
+      <c r="E100" s="71"/>
+      <c r="F100" s="71"/>
+      <c r="G100" s="71"/>
+      <c r="H100" s="72">
+        <f>SUM(H96:H99)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="103" spans="1:8" hidden="1">
-      <c r="A103" s="176"/>
-      <c r="B103" s="176"/>
-      <c r="C103" s="176"/>
-      <c r="D103" s="176"/>
-      <c r="E103" s="176"/>
-      <c r="F103" s="176"/>
-      <c r="G103" s="176"/>
-      <c r="H103" s="176"/>
+      <c r="A103" s="195"/>
+      <c r="B103" s="195"/>
+      <c r="C103" s="195"/>
+      <c r="D103" s="195"/>
+      <c r="E103" s="195"/>
+      <c r="F103" s="195"/>
+      <c r="G103" s="195"/>
+      <c r="H103" s="195"/>
     </row>
     <row r="104" spans="1:8" hidden="1">
-      <c r="A104" s="176"/>
-      <c r="B104" s="176"/>
-      <c r="C104" s="176"/>
-      <c r="D104" s="176"/>
-      <c r="E104" s="176"/>
-      <c r="F104" s="176"/>
-      <c r="G104" s="176"/>
-      <c r="H104" s="176"/>
+      <c r="A104" s="195"/>
+      <c r="B104" s="195"/>
+      <c r="C104" s="195"/>
+      <c r="D104" s="195"/>
+      <c r="E104" s="195"/>
+      <c r="F104" s="195"/>
+      <c r="G104" s="195"/>
+      <c r="H104" s="195"/>
+    </row>
+    <row r="105" spans="1:8" hidden="1">
+      <c r="A105" s="195"/>
+      <c r="B105" s="195"/>
+      <c r="C105" s="195"/>
+      <c r="D105" s="195"/>
+      <c r="E105" s="195"/>
+      <c r="F105" s="195"/>
+      <c r="G105" s="195"/>
+      <c r="H105" s="195"/>
+    </row>
+    <row r="106" spans="1:8" hidden="1">
+      <c r="A106" s="195"/>
+      <c r="B106" s="195"/>
+      <c r="C106" s="195"/>
+      <c r="D106" s="195"/>
+      <c r="E106" s="195"/>
+      <c r="F106" s="195"/>
+      <c r="G106" s="195"/>
+      <c r="H106" s="195"/>
     </row>
   </sheetData>
-  <mergeCells count="29">
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A65:H66"/>
+  <mergeCells count="30">
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A66:H67"/>
+    <mergeCell ref="A69:G69"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J75:K75"/>
-    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="J76:K76"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
     <mergeCell ref="A12:H12"/>
     <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A50:H50"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A101:H104"/>
-    <mergeCell ref="A93:H93"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A103:H106"/>
+    <mergeCell ref="A95:H95"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A79:G79"/>
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="A77:G77"/>
     <mergeCell ref="A76:G76"/>
-    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A93:H94"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3908,7 +3970,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.5703125" customWidth="1"/>
@@ -3920,16 +3982,16 @@
     <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
     <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
-    <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.28515625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" customWidth="1"/>
+    <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.25" customHeight="1">
+    <row r="1" spans="1:18" ht="26.25" customHeight="1">
       <c r="A1" s="88"/>
       <c r="B1" s="89"/>
       <c r="C1" s="89"/>
@@ -3952,9 +4014,10 @@
       <c r="L1" s="89"/>
       <c r="M1" s="89"/>
       <c r="N1" s="89"/>
-      <c r="O1" s="93"/>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="O1" s="89"/>
+      <c r="P1" s="93"/>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="55"/>
       <c r="B2" s="55"/>
       <c r="C2" s="108">
@@ -3969,11 +4032,12 @@
       <c r="J2" s="100"/>
       <c r="K2" s="100"/>
       <c r="L2" s="100"/>
-      <c r="M2" s="55"/>
+      <c r="M2" s="100"/>
       <c r="N2" s="55"/>
       <c r="O2" s="55"/>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="P2" s="55"/>
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="101"/>
       <c r="B3" s="102"/>
       <c r="C3" s="87">
@@ -3981,7 +4045,7 @@
       </c>
       <c r="D3" s="55"/>
       <c r="E3" s="55"/>
-      <c r="F3" s="141">
+      <c r="F3" s="140">
         <v>867931.15999999992</v>
       </c>
       <c r="G3" s="103"/>
@@ -3989,14 +4053,15 @@
       <c r="I3" s="103"/>
       <c r="J3" s="103"/>
       <c r="K3" s="103"/>
-      <c r="L3" s="55" t="s">
+      <c r="L3" s="103"/>
+      <c r="M3" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="M3" s="55"/>
       <c r="N3" s="55"/>
       <c r="O3" s="55"/>
-    </row>
-    <row r="4" spans="1:17" ht="18.75" customHeight="1">
+      <c r="P3" s="55"/>
+    </row>
+    <row r="4" spans="1:18" ht="18.75" customHeight="1">
       <c r="A4" s="104"/>
       <c r="B4" s="105" t="s">
         <v>137</v>
@@ -4006,7 +4071,7 @@
       <c r="E4" s="105" t="s">
         <v>78</v>
       </c>
-      <c r="F4" s="140">
+      <c r="F4" s="139">
         <f>278067+10000+9000-3000-520+225+12</f>
         <v>293784</v>
       </c>
@@ -4015,75 +4080,82 @@
       <c r="I4" s="103"/>
       <c r="J4" s="103"/>
       <c r="K4" s="103"/>
-      <c r="L4" s="55" t="s">
+      <c r="L4" s="103"/>
+      <c r="M4" s="55" t="s">
         <v>76</v>
       </c>
-      <c r="M4" s="55"/>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
-    </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+      <c r="P4" s="55"/>
+    </row>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1">
       <c r="A5" s="106"/>
-      <c r="B5" s="205">
+      <c r="B5" s="239">
         <f>C2-E5</f>
         <v>3604715.15</v>
       </c>
-      <c r="C5" s="205"/>
+      <c r="C5" s="239"/>
       <c r="D5" s="18"/>
-      <c r="E5" s="211">
+      <c r="E5" s="245">
+        <f>160000</f>
         <v>160000</v>
       </c>
-      <c r="F5" s="212"/>
+      <c r="F5" s="246"/>
       <c r="G5" s="100"/>
       <c r="H5" s="100"/>
       <c r="I5" s="100"/>
       <c r="J5" s="100"/>
       <c r="K5" s="100"/>
       <c r="L5" s="100"/>
-      <c r="M5" s="55"/>
+      <c r="M5" s="100"/>
       <c r="N5" s="55"/>
       <c r="O5" s="55"/>
-    </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+      <c r="P5" s="55"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75" customHeight="1">
       <c r="A6" s="106"/>
-      <c r="B6" s="207"/>
-      <c r="C6" s="208"/>
+      <c r="B6" s="241"/>
+      <c r="C6" s="242"/>
       <c r="D6" s="18"/>
-      <c r="E6" s="207" t="s">
+      <c r="E6" s="241" t="s">
         <v>142</v>
       </c>
-      <c r="F6" s="208"/>
+      <c r="F6" s="242"/>
       <c r="G6" s="100"/>
       <c r="H6" s="100"/>
       <c r="I6" s="100"/>
       <c r="J6" s="100"/>
       <c r="K6" s="100"/>
       <c r="L6" s="100"/>
-      <c r="M6" s="55"/>
+      <c r="M6" s="100"/>
       <c r="N6" s="55"/>
       <c r="O6" s="55"/>
-    </row>
-    <row r="7" spans="1:17" ht="18.75" customHeight="1">
+      <c r="P6" s="55"/>
+    </row>
+    <row r="7" spans="1:18" ht="18.75" customHeight="1">
       <c r="A7" s="106"/>
-      <c r="B7" s="205"/>
-      <c r="C7" s="205"/>
+      <c r="B7" s="239">
+        <v>431970</v>
+      </c>
+      <c r="C7" s="239"/>
       <c r="D7" s="18"/>
-      <c r="E7" s="209">
+      <c r="E7" s="243">
         <f>F3</f>
         <v>867931.15999999992</v>
       </c>
-      <c r="F7" s="210"/>
+      <c r="F7" s="244"/>
       <c r="G7" s="100"/>
       <c r="H7" s="100"/>
       <c r="I7" s="100"/>
       <c r="J7" s="100"/>
       <c r="K7" s="100"/>
       <c r="L7" s="100"/>
-      <c r="M7" s="55"/>
+      <c r="M7" s="100"/>
       <c r="N7" s="55"/>
       <c r="O7" s="55"/>
-    </row>
-    <row r="8" spans="1:17" ht="53.25" customHeight="1" thickBot="1">
+      <c r="P7" s="55"/>
+    </row>
+    <row r="8" spans="1:18" ht="53.25" customHeight="1" thickBot="1">
       <c r="A8" s="94" t="s">
         <v>0</v>
       </c>
@@ -4114,23 +4186,26 @@
       <c r="J8" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="K8" s="216" t="s">
+      <c r="K8" s="175" t="s">
         <v>121</v>
       </c>
-      <c r="L8" s="95" t="s">
+      <c r="L8" s="175" t="s">
+        <v>165</v>
+      </c>
+      <c r="M8" s="95" t="s">
         <v>81</v>
       </c>
-      <c r="M8" s="95" t="s">
+      <c r="N8" s="95" t="s">
         <v>7</v>
       </c>
-      <c r="N8" s="95" t="s">
+      <c r="O8" s="95" t="s">
         <v>136</v>
       </c>
-      <c r="O8" s="99" t="s">
+      <c r="P8" s="99" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1">
+    <row r="9" spans="1:18" ht="15" customHeight="1">
       <c r="A9" s="129">
         <v>1</v>
       </c>
@@ -4170,23 +4245,27 @@
         <v>6480</v>
       </c>
       <c r="L9" s="62">
+        <f>B$7*E9</f>
+        <v>17494.785</v>
+      </c>
+      <c r="M9" s="62">
         <f>E$7*E9</f>
         <v>35151.21198</v>
       </c>
-      <c r="M9" s="128">
+      <c r="N9" s="128">
         <f>B$5*E9</f>
         <v>145990.963575</v>
       </c>
-      <c r="N9" s="128">
+      <c r="O9" s="128">
         <f>B$7*E9</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="138">
-        <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>187622.17555499999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" customHeight="1">
+        <v>17494.785</v>
+      </c>
+      <c r="P9" s="138">
+        <f>H9+I9-J9+K9+N9+O9+M9+L9</f>
+        <v>222611.745555</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1">
       <c r="A10" s="48">
         <v>2</v>
       </c>
@@ -4224,23 +4303,27 @@
         <v>10368</v>
       </c>
       <c r="L10" s="62">
-        <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
+        <f t="shared" ref="L10:L31" si="3">B$7*E10</f>
+        <v>27991.655999999999</v>
+      </c>
+      <c r="M10" s="62">
+        <f t="shared" ref="M10:M31" si="4">E$7*E10</f>
         <v>56241.93916799999</v>
       </c>
-      <c r="M10" s="22">
-        <f t="shared" ref="M10:M31" si="4">B$5*E10</f>
+      <c r="N10" s="22">
+        <f t="shared" ref="N10:N31" si="5">B$5*E10</f>
         <v>233585.54171999998</v>
       </c>
-      <c r="N10" s="22">
-        <f t="shared" ref="N10:N31" si="5">B$7*E10</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="138">
-        <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>300195.48088799999</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" customHeight="1">
+      <c r="O10" s="22">
+        <f t="shared" ref="O10:O31" si="6">B$7*E10</f>
+        <v>27991.655999999999</v>
+      </c>
+      <c r="P10" s="138">
+        <f t="shared" ref="P10:P31" si="7">H10+I10-J10+K10+N10+O10+M10+L10</f>
+        <v>356178.79288800003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1">
       <c r="A11" s="124">
         <v>3</v>
       </c>
@@ -4268,7 +4351,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="62">
-        <f t="shared" ref="I11:I31" si="7">H11*3.7%</f>
+        <f t="shared" ref="I11:I31" si="8">H11*3.7%</f>
         <v>0</v>
       </c>
       <c r="J11" s="62">
@@ -4281,23 +4364,27 @@
       </c>
       <c r="L11" s="62">
         <f t="shared" si="3"/>
+        <v>20820.954000000002</v>
+      </c>
+      <c r="M11" s="62">
+        <f t="shared" si="4"/>
         <v>41834.281911999999</v>
-      </c>
-      <c r="M11" s="128">
-        <f t="shared" si="4"/>
-        <v>173747.27022999999</v>
       </c>
       <c r="N11" s="128">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O11" s="138">
+        <v>173747.27022999999</v>
+      </c>
+      <c r="O11" s="128">
         <f t="shared" si="6"/>
-        <v>223293.552142</v>
-      </c>
-      <c r="P11" s="131"/>
-    </row>
-    <row r="12" spans="1:17" ht="15" customHeight="1">
+        <v>20820.954000000002</v>
+      </c>
+      <c r="P11" s="138">
+        <f t="shared" si="7"/>
+        <v>264935.460142</v>
+      </c>
+      <c r="Q11" s="131"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" customHeight="1">
       <c r="A12" s="111">
         <v>4</v>
       </c>
@@ -4322,7 +4409,7 @@
         <v>6715695.8885622956</v>
       </c>
       <c r="I12" s="116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>248480.74787680496</v>
       </c>
       <c r="J12" s="116">
@@ -4333,24 +4420,28 @@
         <f t="shared" si="2"/>
         <v>8560</v>
       </c>
-      <c r="L12" s="116">
+      <c r="L12" s="62">
         <f t="shared" si="3"/>
+        <v>23110.395</v>
+      </c>
+      <c r="M12" s="116">
+        <f t="shared" si="4"/>
         <v>46434.317059999994</v>
-      </c>
-      <c r="M12" s="117">
-        <f t="shared" si="4"/>
-        <v>192852.26052499999</v>
       </c>
       <c r="N12" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O12" s="139">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="O12" s="117">
         <f t="shared" si="6"/>
-        <v>7212023.2140241014</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" customHeight="1">
+        <v>23110.395</v>
+      </c>
+      <c r="P12" s="138">
+        <f t="shared" si="7"/>
+        <v>7258244.0040241005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" customHeight="1">
       <c r="A13" s="48">
         <v>5</v>
       </c>
@@ -4376,7 +4467,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J13" s="21">
@@ -4389,22 +4480,26 @@
       </c>
       <c r="L13" s="62">
         <f t="shared" si="3"/>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="M13" s="62">
+        <f t="shared" si="4"/>
         <v>33415.34966</v>
-      </c>
-      <c r="M13" s="22">
-        <f t="shared" si="4"/>
-        <v>138781.53327499999</v>
       </c>
       <c r="N13" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O13" s="138">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="O13" s="22">
         <f t="shared" si="6"/>
-        <v>178356.882935</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1">
+        <v>16630.845000000001</v>
+      </c>
+      <c r="P13" s="138">
+        <f t="shared" si="7"/>
+        <v>211618.572935</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1">
       <c r="A14" s="48">
         <v>6</v>
       </c>
@@ -4429,7 +4524,7 @@
         <v>109193.585395</v>
       </c>
       <c r="I14" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>4040.1626596150008</v>
       </c>
       <c r="J14" s="21">
@@ -4442,22 +4537,26 @@
       </c>
       <c r="L14" s="62">
         <f t="shared" si="3"/>
+        <v>15507.723</v>
+      </c>
+      <c r="M14" s="62">
+        <f t="shared" si="4"/>
         <v>31158.728643999999</v>
-      </c>
-      <c r="M14" s="22">
-        <f t="shared" si="4"/>
-        <v>129409.273885</v>
       </c>
       <c r="N14" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O14" s="138">
+        <v>129409.273885</v>
+      </c>
+      <c r="O14" s="22">
         <f t="shared" si="6"/>
-        <v>279545.75058361504</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1">
+        <v>15507.723</v>
+      </c>
+      <c r="P14" s="138">
+        <f t="shared" si="7"/>
+        <v>310561.19658361503</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1">
       <c r="A15" s="48">
         <v>7</v>
       </c>
@@ -4483,7 +4582,7 @@
         <v>0</v>
       </c>
       <c r="I15" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J15" s="21">
@@ -4496,22 +4595,26 @@
       </c>
       <c r="L15" s="62">
         <f t="shared" si="3"/>
+        <v>17883.558000000001</v>
+      </c>
+      <c r="M15" s="62">
+        <f t="shared" si="4"/>
         <v>35932.350023999999</v>
       </c>
-      <c r="M15" s="22">
-        <f t="shared" si="4"/>
+      <c r="N15" s="22">
+        <f t="shared" si="5"/>
         <v>149235.20720999999</v>
       </c>
-      <c r="N15" s="22">
-        <v>0</v>
-      </c>
-      <c r="O15" s="138">
-        <f t="shared" si="6"/>
-        <v>191791.55723400001</v>
-      </c>
-      <c r="Q15" s="135"/>
-    </row>
-    <row r="16" spans="1:17" ht="15" customHeight="1">
+      <c r="O15" s="22">
+        <v>0</v>
+      </c>
+      <c r="P15" s="138">
+        <f t="shared" si="7"/>
+        <v>209675.115234</v>
+      </c>
+      <c r="R15" s="135"/>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1">
       <c r="A16" s="48">
         <v>8</v>
       </c>
@@ -4539,7 +4642,7 @@
         <v>8725.8166750000091</v>
       </c>
       <c r="I16" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>322.85521697500036</v>
       </c>
       <c r="J16" s="21">
@@ -4552,23 +4655,27 @@
       </c>
       <c r="L16" s="62">
         <f t="shared" si="3"/>
+        <v>23110.395</v>
+      </c>
+      <c r="M16" s="62">
+        <f t="shared" si="4"/>
         <v>46434.317059999994</v>
-      </c>
-      <c r="M16" s="22">
-        <f t="shared" si="4"/>
-        <v>192852.26052499999</v>
       </c>
       <c r="N16" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O16" s="138">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="O16" s="22">
         <f t="shared" si="6"/>
-        <v>256895.249476975</v>
-      </c>
-      <c r="Q16" s="135"/>
-    </row>
-    <row r="17" spans="1:18" ht="15" customHeight="1">
+        <v>23110.395</v>
+      </c>
+      <c r="P16" s="138">
+        <f t="shared" si="7"/>
+        <v>303116.03947697498</v>
+      </c>
+      <c r="R16" s="135"/>
+    </row>
+    <row r="17" spans="1:19" ht="15" customHeight="1">
       <c r="A17" s="48">
         <v>9</v>
       </c>
@@ -4596,7 +4703,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J17" s="21">
@@ -4609,23 +4716,27 @@
       </c>
       <c r="L17" s="62">
         <f t="shared" si="3"/>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="M17" s="62">
+        <f t="shared" si="4"/>
         <v>33415.34966</v>
-      </c>
-      <c r="M17" s="22">
-        <f t="shared" si="4"/>
-        <v>138781.53327499999</v>
       </c>
       <c r="N17" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O17" s="138">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="O17" s="22">
         <f t="shared" si="6"/>
-        <v>178356.882935</v>
-      </c>
-      <c r="Q17" s="135"/>
-    </row>
-    <row r="18" spans="1:18" ht="15" customHeight="1">
+        <v>16630.845000000001</v>
+      </c>
+      <c r="P17" s="138">
+        <f t="shared" si="7"/>
+        <v>211618.572935</v>
+      </c>
+      <c r="R17" s="135"/>
+    </row>
+    <row r="18" spans="1:19" ht="15" customHeight="1">
       <c r="A18" s="124">
         <v>10</v>
       </c>
@@ -4648,7 +4759,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="62">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J18" s="62">
@@ -4661,23 +4772,27 @@
       </c>
       <c r="L18" s="62">
         <f t="shared" si="3"/>
+        <v>15507.723</v>
+      </c>
+      <c r="M18" s="62">
+        <f t="shared" si="4"/>
         <v>31158.728643999999</v>
-      </c>
-      <c r="M18" s="128">
-        <f t="shared" si="4"/>
-        <v>129409.273885</v>
       </c>
       <c r="N18" s="128">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="138">
+        <v>129409.273885</v>
+      </c>
+      <c r="O18" s="128">
         <f t="shared" si="6"/>
-        <v>114426.37455691038</v>
-      </c>
-      <c r="Q18" s="135"/>
-    </row>
-    <row r="19" spans="1:18" ht="15" customHeight="1">
+        <v>15507.723</v>
+      </c>
+      <c r="P18" s="138">
+        <f t="shared" si="7"/>
+        <v>145441.82055691039</v>
+      </c>
+      <c r="R18" s="135"/>
+    </row>
+    <row r="19" spans="1:19" ht="15" customHeight="1">
       <c r="A19" s="111">
         <v>11</v>
       </c>
@@ -4702,7 +4817,7 @@
         <v>4792208.6425903365</v>
       </c>
       <c r="I19" s="116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>177311.71977584247</v>
       </c>
       <c r="J19" s="116">
@@ -4713,25 +4828,29 @@
         <f t="shared" si="2"/>
         <v>6624</v>
       </c>
-      <c r="L19" s="116">
+      <c r="L19" s="62">
         <f t="shared" si="3"/>
+        <v>17883.558000000001</v>
+      </c>
+      <c r="M19" s="116">
+        <f t="shared" si="4"/>
         <v>35932.350023999999</v>
-      </c>
-      <c r="M19" s="117">
-        <f t="shared" si="4"/>
-        <v>149235.20720999999</v>
       </c>
       <c r="N19" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="139">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="O19" s="117">
         <f t="shared" si="6"/>
-        <v>5161311.9196001785</v>
-      </c>
-      <c r="Q19" s="135"/>
-    </row>
-    <row r="20" spans="1:18" ht="15" customHeight="1">
+        <v>17883.558000000001</v>
+      </c>
+      <c r="P19" s="138">
+        <f t="shared" si="7"/>
+        <v>5197079.0356001789</v>
+      </c>
+      <c r="R19" s="135"/>
+    </row>
+    <row r="20" spans="1:19" ht="15" customHeight="1">
       <c r="A20" s="48">
         <v>12</v>
       </c>
@@ -4759,7 +4878,7 @@
         <v>0</v>
       </c>
       <c r="I20" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J20" s="21">
@@ -4772,23 +4891,27 @@
       </c>
       <c r="L20" s="62">
         <f t="shared" si="3"/>
+        <v>23110.395</v>
+      </c>
+      <c r="M20" s="62">
+        <f t="shared" si="4"/>
         <v>46434.317059999994</v>
-      </c>
-      <c r="M20" s="22">
-        <f t="shared" si="4"/>
-        <v>192852.26052499999</v>
       </c>
       <c r="N20" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="138">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="O20" s="22">
         <f t="shared" si="6"/>
-        <v>247846.57758499999</v>
-      </c>
-      <c r="Q20" s="135"/>
-    </row>
-    <row r="21" spans="1:18" ht="15" customHeight="1">
+        <v>23110.395</v>
+      </c>
+      <c r="P20" s="138">
+        <f t="shared" si="7"/>
+        <v>294067.367585</v>
+      </c>
+      <c r="R20" s="135"/>
+    </row>
+    <row r="21" spans="1:19" ht="15" customHeight="1">
       <c r="A21" s="111">
         <v>13</v>
       </c>
@@ -4813,7 +4936,7 @@
         <v>2359047.9860918703</v>
       </c>
       <c r="I21" s="116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>87284.775485399208</v>
       </c>
       <c r="J21" s="116">
@@ -4824,25 +4947,29 @@
         <f t="shared" si="2"/>
         <v>6160</v>
       </c>
-      <c r="L21" s="116">
+      <c r="L21" s="62">
         <f t="shared" si="3"/>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="M21" s="116">
+        <f t="shared" si="4"/>
         <v>33415.34966</v>
-      </c>
-      <c r="M21" s="117">
-        <f t="shared" si="4"/>
-        <v>138781.53327499999</v>
       </c>
       <c r="N21" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O21" s="139">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="O21" s="117">
         <f t="shared" si="6"/>
-        <v>2624689.6445122692</v>
-      </c>
-      <c r="Q21" s="135"/>
-    </row>
-    <row r="22" spans="1:18" ht="15" customHeight="1">
+        <v>16630.845000000001</v>
+      </c>
+      <c r="P21" s="138">
+        <f t="shared" si="7"/>
+        <v>2657951.3345122696</v>
+      </c>
+      <c r="R21" s="135"/>
+    </row>
+    <row r="22" spans="1:19" ht="15" customHeight="1">
       <c r="A22" s="48">
         <v>14</v>
       </c>
@@ -4869,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="I22" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J22" s="21">
@@ -4882,23 +5009,27 @@
       </c>
       <c r="L22" s="62">
         <f t="shared" si="3"/>
+        <v>15507.723</v>
+      </c>
+      <c r="M22" s="62">
+        <f t="shared" si="4"/>
         <v>31158.728643999999</v>
-      </c>
-      <c r="M22" s="22">
-        <f t="shared" si="4"/>
-        <v>129409.273885</v>
       </c>
       <c r="N22" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O22" s="138">
+        <v>129409.273885</v>
+      </c>
+      <c r="O22" s="22">
         <f t="shared" si="6"/>
-        <v>152805.58792399999</v>
-      </c>
-      <c r="Q22" s="135"/>
-    </row>
-    <row r="23" spans="1:18" ht="15" customHeight="1">
+        <v>15507.723</v>
+      </c>
+      <c r="P22" s="138">
+        <f t="shared" si="7"/>
+        <v>183821.03392399999</v>
+      </c>
+      <c r="R22" s="135"/>
+    </row>
+    <row r="23" spans="1:19" ht="15" customHeight="1">
       <c r="A23" s="48">
         <v>15</v>
       </c>
@@ -4926,7 +5057,7 @@
         <v>0</v>
       </c>
       <c r="I23" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J23" s="21">
@@ -4939,23 +5070,27 @@
       </c>
       <c r="L23" s="62">
         <f t="shared" si="3"/>
+        <v>17883.558000000001</v>
+      </c>
+      <c r="M23" s="62">
+        <f t="shared" si="4"/>
         <v>35932.350023999999</v>
-      </c>
-      <c r="M23" s="22">
-        <f t="shared" si="4"/>
-        <v>149235.20720999999</v>
       </c>
       <c r="N23" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O23" s="138">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="O23" s="22">
         <f t="shared" si="6"/>
-        <v>191791.55723400001</v>
-      </c>
-      <c r="Q23" s="135"/>
-    </row>
-    <row r="24" spans="1:18" ht="15" customHeight="1">
+        <v>17883.558000000001</v>
+      </c>
+      <c r="P23" s="138">
+        <f t="shared" si="7"/>
+        <v>227558.67323399996</v>
+      </c>
+      <c r="R23" s="135"/>
+    </row>
+    <row r="24" spans="1:19" ht="15" customHeight="1">
       <c r="A24" s="48">
         <v>16</v>
       </c>
@@ -4981,7 +5116,7 @@
         <v>0</v>
       </c>
       <c r="I24" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J24" s="21">
@@ -4994,23 +5129,27 @@
       </c>
       <c r="L24" s="62">
         <f t="shared" si="3"/>
+        <v>23110.395</v>
+      </c>
+      <c r="M24" s="62">
+        <f t="shared" si="4"/>
         <v>46434.317059999994</v>
-      </c>
-      <c r="M24" s="22">
-        <f t="shared" si="4"/>
-        <v>192852.26052499999</v>
       </c>
       <c r="N24" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O24" s="138">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="O24" s="22">
         <f t="shared" si="6"/>
-        <v>212710.68758499998</v>
-      </c>
-      <c r="Q24" s="135"/>
-    </row>
-    <row r="25" spans="1:18" s="1" customFormat="1" ht="15.75" customHeight="1">
+        <v>23110.395</v>
+      </c>
+      <c r="P24" s="138">
+        <f t="shared" si="7"/>
+        <v>258931.47758499996</v>
+      </c>
+      <c r="R24" s="135"/>
+    </row>
+    <row r="25" spans="1:19" s="1" customFormat="1" ht="15.75" customHeight="1">
       <c r="A25" s="48">
         <v>17</v>
       </c>
@@ -5038,7 +5177,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J25" s="21">
@@ -5051,23 +5190,27 @@
       </c>
       <c r="L25" s="62">
         <f t="shared" si="3"/>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="M25" s="62">
+        <f t="shared" si="4"/>
         <v>33415.34966</v>
-      </c>
-      <c r="M25" s="22">
-        <f t="shared" si="4"/>
-        <v>138781.53327499999</v>
       </c>
       <c r="N25" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O25" s="138">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="O25" s="22">
         <f t="shared" si="6"/>
-        <v>178356.82886000001</v>
-      </c>
-      <c r="Q25" s="136"/>
-    </row>
-    <row r="26" spans="1:18" ht="15" customHeight="1">
+        <v>16630.845000000001</v>
+      </c>
+      <c r="P25" s="138">
+        <f t="shared" si="7"/>
+        <v>211618.51886000001</v>
+      </c>
+      <c r="R25" s="136"/>
+    </row>
+    <row r="26" spans="1:19" ht="15" customHeight="1">
       <c r="A26" s="48">
         <v>18</v>
       </c>
@@ -5093,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="I26" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J26" s="21">
@@ -5106,23 +5249,27 @@
       </c>
       <c r="L26" s="62">
         <f t="shared" si="3"/>
+        <v>15507.723</v>
+      </c>
+      <c r="M26" s="62">
+        <f t="shared" si="4"/>
         <v>31158.728643999999</v>
-      </c>
-      <c r="M26" s="22">
-        <f t="shared" si="4"/>
-        <v>129409.273885</v>
       </c>
       <c r="N26" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O26" s="138">
+        <v>129409.273885</v>
+      </c>
+      <c r="O26" s="22">
         <f t="shared" si="6"/>
-        <v>166312.00252899999</v>
-      </c>
-      <c r="Q26" s="135"/>
-    </row>
-    <row r="27" spans="1:18" ht="15" customHeight="1">
+        <v>15507.723</v>
+      </c>
+      <c r="P26" s="138">
+        <f t="shared" si="7"/>
+        <v>197327.44852899999</v>
+      </c>
+      <c r="R26" s="135"/>
+    </row>
+    <row r="27" spans="1:19" ht="15" customHeight="1">
       <c r="A27" s="111">
         <v>19</v>
       </c>
@@ -5149,7 +5296,7 @@
         <v>3809712.3310685158</v>
       </c>
       <c r="I27" s="116">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>140959.35624953511</v>
       </c>
       <c r="J27" s="116">
@@ -5160,28 +5307,32 @@
         <f t="shared" si="2"/>
         <v>6624</v>
       </c>
-      <c r="L27" s="116">
+      <c r="L27" s="62">
         <f t="shared" si="3"/>
+        <v>17883.558000000001</v>
+      </c>
+      <c r="M27" s="116">
+        <f t="shared" si="4"/>
         <v>35932.350023999999</v>
-      </c>
-      <c r="M27" s="117">
-        <f t="shared" si="4"/>
-        <v>149235.20720999999</v>
       </c>
       <c r="N27" s="117">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O27" s="139">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="O27" s="117">
         <f t="shared" si="6"/>
-        <v>4142463.2445520507</v>
-      </c>
-      <c r="P27" s="137">
-        <f>M27+N27</f>
-        <v>149235.20720999999</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="17.25" customHeight="1">
+        <v>17883.558000000001</v>
+      </c>
+      <c r="P27" s="138">
+        <f t="shared" si="7"/>
+        <v>4178230.3605520511</v>
+      </c>
+      <c r="Q27" s="137">
+        <f>N27+O27</f>
+        <v>167118.76520999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="17.25" customHeight="1">
       <c r="A28" s="48">
         <v>20</v>
       </c>
@@ -5204,7 +5355,7 @@
         <v>3945998.9763045558</v>
       </c>
       <c r="I28" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>146001.96212326857</v>
       </c>
       <c r="J28" s="21">
@@ -5214,23 +5365,27 @@
       <c r="K28" s="62"/>
       <c r="L28" s="62">
         <f t="shared" si="3"/>
+        <v>23110.395</v>
+      </c>
+      <c r="M28" s="62">
+        <f t="shared" si="4"/>
         <v>46434.317059999994</v>
-      </c>
-      <c r="M28" s="22">
-        <f t="shared" si="4"/>
-        <v>192852.26052499999</v>
       </c>
       <c r="N28" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O28" s="138">
+        <v>192852.26052499999</v>
+      </c>
+      <c r="O28" s="22">
         <f t="shared" si="6"/>
-        <v>4331287.5160128251</v>
-      </c>
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="1:18" ht="15" customHeight="1">
+        <v>23110.395</v>
+      </c>
+      <c r="P28" s="138">
+        <f t="shared" si="7"/>
+        <v>4377508.3060128242</v>
+      </c>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" spans="1:19" ht="15" customHeight="1">
       <c r="A29" s="48">
         <v>21</v>
       </c>
@@ -5258,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J29" s="21">
@@ -5271,33 +5426,37 @@
       </c>
       <c r="L29" s="62">
         <f t="shared" si="3"/>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="M29" s="62">
+        <f t="shared" si="4"/>
         <v>33415.34966</v>
-      </c>
-      <c r="M29" s="22">
-        <f t="shared" si="4"/>
-        <v>138781.53327499999</v>
       </c>
       <c r="N29" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O29" s="138">
+        <v>138781.53327499999</v>
+      </c>
+      <c r="O29" s="22">
         <f t="shared" si="6"/>
-        <v>178356.882935</v>
-      </c>
-      <c r="P29" s="7">
-        <f>M29/2</f>
+        <v>16630.845000000001</v>
+      </c>
+      <c r="P29" s="138">
+        <f t="shared" si="7"/>
+        <v>211618.572935</v>
+      </c>
+      <c r="Q29" s="7">
+        <f>N29/2</f>
         <v>69390.766637499997</v>
       </c>
-      <c r="Q29" s="7">
-        <f>SUM(Q15:Q28)</f>
-        <v>0</v>
-      </c>
-      <c r="R29" t="s">
+      <c r="R29" s="7">
+        <f>SUM(R15:R28)</f>
+        <v>0</v>
+      </c>
+      <c r="S29" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15" customHeight="1">
+    <row r="30" spans="1:19" ht="15" customHeight="1">
       <c r="A30" s="48">
         <v>22</v>
       </c>
@@ -5325,7 +5484,7 @@
         <v>0</v>
       </c>
       <c r="I30" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J30" s="21">
@@ -5338,22 +5497,26 @@
       </c>
       <c r="L30" s="62">
         <f t="shared" si="3"/>
+        <v>15507.723</v>
+      </c>
+      <c r="M30" s="62">
+        <f t="shared" si="4"/>
         <v>31158.728643999999</v>
-      </c>
-      <c r="M30" s="22">
-        <f t="shared" si="4"/>
-        <v>129409.273885</v>
       </c>
       <c r="N30" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O30" s="138">
+        <v>129409.273885</v>
+      </c>
+      <c r="O30" s="22">
         <f t="shared" si="6"/>
-        <v>166312.00252899999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15" customHeight="1">
+        <v>15507.723</v>
+      </c>
+      <c r="P30" s="138">
+        <f t="shared" si="7"/>
+        <v>197327.44852899999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" customHeight="1">
       <c r="A31" s="48">
         <v>23</v>
       </c>
@@ -5379,7 +5542,7 @@
         <v>0</v>
       </c>
       <c r="I31" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="J31" s="21">
@@ -5392,22 +5555,26 @@
       </c>
       <c r="L31" s="62">
         <f t="shared" si="3"/>
+        <v>17883.558000000001</v>
+      </c>
+      <c r="M31" s="62">
+        <f t="shared" si="4"/>
         <v>35932.350023999999</v>
-      </c>
-      <c r="M31" s="22">
-        <f t="shared" si="4"/>
-        <v>149235.20720999999</v>
       </c>
       <c r="N31" s="22">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="O31" s="138">
+        <v>149235.20720999999</v>
+      </c>
+      <c r="O31" s="22">
         <f t="shared" si="6"/>
-        <v>191791.55723400001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.75">
+        <v>17883.558000000001</v>
+      </c>
+      <c r="P31" s="138">
+        <f t="shared" si="7"/>
+        <v>227558.67323399996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="15.75">
       <c r="A32" s="34"/>
       <c r="B32" s="49">
         <f>SUM(B9:B31)</f>
@@ -5436,7 +5603,7 @@
         <v>804401.57938744035</v>
       </c>
       <c r="J32" s="85">
-        <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
+        <f t="shared" ref="J32" si="9">SUM(J9:J31)</f>
         <v>100527.98665208965</v>
       </c>
       <c r="K32" s="76">
@@ -5444,144 +5611,152 @@
         <v>151440</v>
       </c>
       <c r="L32" s="76"/>
-      <c r="M32" s="51">
-        <f>SUM(M9:M31)</f>
+      <c r="M32" s="76"/>
+      <c r="N32" s="51">
+        <f>SUM(N9:N31)</f>
         <v>3604715.15</v>
       </c>
-      <c r="N32" s="76">
-        <f>SUM(N9:N31)</f>
-        <v>0</v>
-      </c>
-      <c r="O32" s="51">
+      <c r="O32" s="76">
         <f>SUM(O9:O31)</f>
-        <v>27068543.129422922</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
-    <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="204"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="204"/>
-      <c r="L34" s="204"/>
-      <c r="M34" s="204"/>
-      <c r="N34" s="204"/>
-      <c r="O34" s="204"/>
-    </row>
-    <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="204"/>
-      <c r="C35" s="204"/>
-      <c r="D35" s="204"/>
-      <c r="E35" s="204"/>
-      <c r="F35" s="204"/>
-      <c r="G35" s="204"/>
-      <c r="H35" s="204"/>
-      <c r="I35" s="204"/>
-      <c r="J35" s="204"/>
-      <c r="K35" s="204"/>
-      <c r="L35" s="204"/>
-      <c r="M35" s="204"/>
-      <c r="N35" s="204"/>
-      <c r="O35" s="204"/>
-    </row>
-    <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="204"/>
-      <c r="C36" s="204"/>
-      <c r="D36" s="204"/>
-      <c r="E36" s="204"/>
-      <c r="F36" s="204"/>
-      <c r="G36" s="204"/>
-      <c r="H36" s="204"/>
-      <c r="I36" s="204"/>
-      <c r="J36" s="204"/>
-      <c r="K36" s="204"/>
-      <c r="L36" s="204"/>
-      <c r="M36" s="204"/>
-      <c r="N36" s="204"/>
-      <c r="O36" s="204"/>
-    </row>
-    <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="204"/>
-      <c r="C37" s="204"/>
-      <c r="D37" s="204"/>
-      <c r="E37" s="204"/>
-      <c r="F37" s="204"/>
-      <c r="G37" s="204"/>
-      <c r="H37" s="204"/>
-      <c r="I37" s="204"/>
-      <c r="J37" s="204"/>
-      <c r="K37" s="204"/>
-      <c r="L37" s="204"/>
-      <c r="M37" s="204"/>
-      <c r="N37" s="204"/>
-      <c r="O37" s="204"/>
-    </row>
-    <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="206"/>
-      <c r="B38" s="206"/>
-      <c r="C38" s="206"/>
-      <c r="D38" s="206"/>
-      <c r="E38" s="206"/>
-      <c r="F38" s="206"/>
-      <c r="G38" s="206"/>
-      <c r="H38" s="206"/>
-      <c r="I38" s="206"/>
-      <c r="J38" s="206"/>
-      <c r="K38" s="206"/>
-      <c r="L38" s="206"/>
-      <c r="M38" s="206"/>
-      <c r="N38" s="206"/>
-      <c r="O38" s="206"/>
-    </row>
-    <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="206"/>
-      <c r="B39" s="206"/>
-      <c r="C39" s="206"/>
-      <c r="D39" s="206"/>
-      <c r="E39" s="206"/>
-      <c r="F39" s="206"/>
-      <c r="G39" s="206"/>
-      <c r="H39" s="206"/>
-      <c r="I39" s="206"/>
-      <c r="J39" s="206"/>
-      <c r="K39" s="206"/>
-      <c r="L39" s="206"/>
-      <c r="M39" s="206"/>
-      <c r="N39" s="206"/>
-      <c r="O39" s="206"/>
-    </row>
-    <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="206"/>
-      <c r="B40" s="206"/>
-      <c r="C40" s="206"/>
-      <c r="D40" s="206"/>
-      <c r="E40" s="206"/>
-      <c r="F40" s="206"/>
-      <c r="G40" s="206"/>
-      <c r="H40" s="206"/>
-      <c r="I40" s="206"/>
-      <c r="J40" s="206"/>
-      <c r="K40" s="206"/>
-      <c r="L40" s="206"/>
-      <c r="M40" s="206"/>
-      <c r="N40" s="206"/>
-      <c r="O40" s="206"/>
-    </row>
-    <row r="41" spans="1:15">
-      <c r="O41" s="7"/>
+        <v>414086.4420000001</v>
+      </c>
+      <c r="P32" s="51">
+        <f>SUM(P9:P31)</f>
+        <v>27914599.571422931</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" ht="14.25" customHeight="1"/>
+    <row r="34" spans="1:16" hidden="1">
+      <c r="B34" s="238"/>
+      <c r="C34" s="238"/>
+      <c r="D34" s="238"/>
+      <c r="E34" s="238"/>
+      <c r="F34" s="238"/>
+      <c r="G34" s="238"/>
+      <c r="H34" s="238"/>
+      <c r="I34" s="238"/>
+      <c r="J34" s="238"/>
+      <c r="K34" s="238"/>
+      <c r="L34" s="238"/>
+      <c r="M34" s="238"/>
+      <c r="N34" s="238"/>
+      <c r="O34" s="238"/>
+      <c r="P34" s="238"/>
+    </row>
+    <row r="35" spans="1:16" hidden="1">
+      <c r="B35" s="238"/>
+      <c r="C35" s="238"/>
+      <c r="D35" s="238"/>
+      <c r="E35" s="238"/>
+      <c r="F35" s="238"/>
+      <c r="G35" s="238"/>
+      <c r="H35" s="238"/>
+      <c r="I35" s="238"/>
+      <c r="J35" s="238"/>
+      <c r="K35" s="238"/>
+      <c r="L35" s="238"/>
+      <c r="M35" s="238"/>
+      <c r="N35" s="238"/>
+      <c r="O35" s="238"/>
+      <c r="P35" s="238"/>
+    </row>
+    <row r="36" spans="1:16" hidden="1">
+      <c r="B36" s="238"/>
+      <c r="C36" s="238"/>
+      <c r="D36" s="238"/>
+      <c r="E36" s="238"/>
+      <c r="F36" s="238"/>
+      <c r="G36" s="238"/>
+      <c r="H36" s="238"/>
+      <c r="I36" s="238"/>
+      <c r="J36" s="238"/>
+      <c r="K36" s="238"/>
+      <c r="L36" s="238"/>
+      <c r="M36" s="238"/>
+      <c r="N36" s="238"/>
+      <c r="O36" s="238"/>
+      <c r="P36" s="238"/>
+    </row>
+    <row r="37" spans="1:16" hidden="1">
+      <c r="B37" s="238"/>
+      <c r="C37" s="238"/>
+      <c r="D37" s="238"/>
+      <c r="E37" s="238"/>
+      <c r="F37" s="238"/>
+      <c r="G37" s="238"/>
+      <c r="H37" s="238"/>
+      <c r="I37" s="238"/>
+      <c r="J37" s="238"/>
+      <c r="K37" s="238"/>
+      <c r="L37" s="238"/>
+      <c r="M37" s="238"/>
+      <c r="N37" s="238"/>
+      <c r="O37" s="238"/>
+      <c r="P37" s="238"/>
+    </row>
+    <row r="38" spans="1:16" hidden="1">
+      <c r="A38" s="240"/>
+      <c r="B38" s="240"/>
+      <c r="C38" s="240"/>
+      <c r="D38" s="240"/>
+      <c r="E38" s="240"/>
+      <c r="F38" s="240"/>
+      <c r="G38" s="240"/>
+      <c r="H38" s="240"/>
+      <c r="I38" s="240"/>
+      <c r="J38" s="240"/>
+      <c r="K38" s="240"/>
+      <c r="L38" s="240"/>
+      <c r="M38" s="240"/>
+      <c r="N38" s="240"/>
+      <c r="O38" s="240"/>
+      <c r="P38" s="240"/>
+    </row>
+    <row r="39" spans="1:16" hidden="1">
+      <c r="A39" s="240"/>
+      <c r="B39" s="240"/>
+      <c r="C39" s="240"/>
+      <c r="D39" s="240"/>
+      <c r="E39" s="240"/>
+      <c r="F39" s="240"/>
+      <c r="G39" s="240"/>
+      <c r="H39" s="240"/>
+      <c r="I39" s="240"/>
+      <c r="J39" s="240"/>
+      <c r="K39" s="240"/>
+      <c r="L39" s="240"/>
+      <c r="M39" s="240"/>
+      <c r="N39" s="240"/>
+      <c r="O39" s="240"/>
+      <c r="P39" s="240"/>
+    </row>
+    <row r="40" spans="1:16" hidden="1">
+      <c r="A40" s="240"/>
+      <c r="B40" s="240"/>
+      <c r="C40" s="240"/>
+      <c r="D40" s="240"/>
+      <c r="E40" s="240"/>
+      <c r="F40" s="240"/>
+      <c r="G40" s="240"/>
+      <c r="H40" s="240"/>
+      <c r="I40" s="240"/>
+      <c r="J40" s="240"/>
+      <c r="K40" s="240"/>
+      <c r="L40" s="240"/>
+      <c r="M40" s="240"/>
+      <c r="N40" s="240"/>
+      <c r="O40" s="240"/>
+      <c r="P40" s="240"/>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="P41" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="B34:O37"/>
+    <mergeCell ref="B34:P37"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
-    <mergeCell ref="A38:O40"/>
+    <mergeCell ref="A38:P40"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E7:F7"/>
@@ -5606,15 +5781,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="213" t="s">
+      <c r="A1" s="247" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="214"/>
-      <c r="C1" s="214"/>
-      <c r="D1" s="214"/>
-      <c r="E1" s="214"/>
-      <c r="F1" s="214"/>
-      <c r="G1" s="215"/>
+      <c r="B1" s="248"/>
+      <c r="C1" s="248"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="249"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="27"/>
